--- a/data/harvesting_records.xlsx
+++ b/data/harvesting_records.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -8204,7 +8204,7 @@
         <v>31</v>
       </c>
       <c r="D293">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="E293">
         <v>39</v>
@@ -8230,7 +8230,7 @@
         <v>31</v>
       </c>
       <c r="D294">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="E294">
         <v>41</v>
@@ -8256,7 +8256,7 @@
         <v>31</v>
       </c>
       <c r="D295">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="E295">
         <v>37</v>
@@ -8282,7 +8282,7 @@
         <v>31</v>
       </c>
       <c r="D296">
-        <v>4</v>
+        <v>4.63</v>
       </c>
       <c r="E296">
         <v>71</v>
@@ -8308,7 +8308,7 @@
         <v>53</v>
       </c>
       <c r="D297">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="E297">
         <v>61</v>
@@ -8360,7 +8360,7 @@
         <v>31</v>
       </c>
       <c r="D299">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="E299">
         <v>36</v>
@@ -8386,7 +8386,7 @@
         <v>31</v>
       </c>
       <c r="D300">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="E300">
         <v>44</v>
@@ -8412,7 +8412,7 @@
         <v>31</v>
       </c>
       <c r="D301">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="E301">
         <v>35</v>
@@ -8438,7 +8438,7 @@
         <v>31</v>
       </c>
       <c r="D302">
-        <v>0.68</v>
+        <v>0.88</v>
       </c>
       <c r="E302">
         <v>11</v>
@@ -8464,7 +8464,7 @@
         <v>25</v>
       </c>
       <c r="D303">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="E303">
         <v>31</v>
@@ -8490,7 +8490,7 @@
         <v>25</v>
       </c>
       <c r="D304">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="E304">
         <v>31</v>
@@ -8516,7 +8516,7 @@
         <v>206</v>
       </c>
       <c r="D305">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="E305">
         <v>47</v>
@@ -8542,7 +8542,7 @@
         <v>206</v>
       </c>
       <c r="D306">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="E306">
         <v>37</v>
@@ -8568,7 +8568,7 @@
         <v>206</v>
       </c>
       <c r="D307">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="E307">
         <v>41</v>
@@ -8594,7 +8594,7 @@
         <v>206</v>
       </c>
       <c r="D308">
-        <v>2.3199999999999998</v>
+        <v>1.48</v>
       </c>
       <c r="E308">
         <v>27</v>
@@ -8620,7 +8620,7 @@
         <v>206</v>
       </c>
       <c r="D309">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="E309">
         <v>49</v>
@@ -8646,7 +8646,7 @@
         <v>206</v>
       </c>
       <c r="D310">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="E310">
         <v>42</v>
@@ -8672,7 +8672,7 @@
         <v>206</v>
       </c>
       <c r="D311">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="E311">
         <v>39</v>
@@ -8698,7 +8698,7 @@
         <v>206</v>
       </c>
       <c r="D312">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="E312">
         <v>40</v>
@@ -8724,7 +8724,7 @@
         <v>206</v>
       </c>
       <c r="D313">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="E313">
         <v>41</v>
@@ -8750,7 +8750,7 @@
         <v>206</v>
       </c>
       <c r="D314">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="E314">
         <v>40</v>
@@ -8776,7 +8776,7 @@
         <v>206</v>
       </c>
       <c r="D315">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="E315">
         <v>47</v>
@@ -8802,7 +8802,7 @@
         <v>206</v>
       </c>
       <c r="D316">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="E316">
         <v>46</v>
@@ -8828,7 +8828,7 @@
         <v>206</v>
       </c>
       <c r="D317">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="E317">
         <v>47</v>
@@ -8854,7 +8854,7 @@
         <v>206</v>
       </c>
       <c r="D318">
-        <v>4</v>
+        <v>3.04</v>
       </c>
       <c r="E318">
         <v>54</v>
@@ -8880,7 +8880,7 @@
         <v>206</v>
       </c>
       <c r="D319">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="E319">
         <v>8</v>
@@ -8906,7 +8906,7 @@
         <v>31</v>
       </c>
       <c r="D320">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="E320">
         <v>43</v>
@@ -8932,7 +8932,7 @@
         <v>31</v>
       </c>
       <c r="D321">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="E321">
         <v>42</v>
@@ -8958,7 +8958,7 @@
         <v>31</v>
       </c>
       <c r="D322">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="E322">
         <v>41</v>
@@ -8984,7 +8984,7 @@
         <v>31</v>
       </c>
       <c r="D323">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="E323">
         <v>44</v>
@@ -9088,7 +9088,7 @@
         <v>31</v>
       </c>
       <c r="D327">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="E327">
         <v>39</v>
@@ -9114,7 +9114,7 @@
         <v>31</v>
       </c>
       <c r="D328">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="E328">
         <v>37</v>
@@ -9140,7 +9140,7 @@
         <v>31</v>
       </c>
       <c r="D329">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="E329">
         <v>40</v>
@@ -9166,7 +9166,7 @@
         <v>31</v>
       </c>
       <c r="D330">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="E330">
         <v>13</v>

--- a/data/harvesting_records.xlsx
+++ b/data/harvesting_records.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="350">
   <si>
     <t>Date</t>
   </si>
@@ -1425,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S527"/>
+  <dimension ref="A1:S530"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -22045,6 +22045,183 @@
         <v>5</v>
       </c>
     </row>
+    <row r="528" spans="1:19">
+      <c r="A528" t="s">
+        <v>43</v>
+      </c>
+      <c r="B528" t="s">
+        <v>306</v>
+      </c>
+      <c r="C528" t="s">
+        <v>344</v>
+      </c>
+      <c r="D528">
+        <v>3.12</v>
+      </c>
+      <c r="E528">
+        <v>42</v>
+      </c>
+      <c r="F528">
+        <v>252</v>
+      </c>
+      <c r="G528">
+        <v>109</v>
+      </c>
+      <c r="H528" t="s">
+        <v>349</v>
+      </c>
+      <c r="I528">
+        <v>1</v>
+      </c>
+      <c r="J528">
+        <v>2</v>
+      </c>
+      <c r="K528">
+        <v>4</v>
+      </c>
+      <c r="L528">
+        <v>4</v>
+      </c>
+      <c r="M528">
+        <v>5</v>
+      </c>
+      <c r="N528">
+        <v>2</v>
+      </c>
+      <c r="O528">
+        <v>1</v>
+      </c>
+      <c r="P528">
+        <v>84</v>
+      </c>
+      <c r="Q528">
+        <v>1</v>
+      </c>
+      <c r="R528">
+        <v>0</v>
+      </c>
+      <c r="S528">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="529" spans="1:19">
+      <c r="A529" t="s">
+        <v>43</v>
+      </c>
+      <c r="B529" t="s">
+        <v>307</v>
+      </c>
+      <c r="C529" t="s">
+        <v>344</v>
+      </c>
+      <c r="D529">
+        <v>3.14</v>
+      </c>
+      <c r="E529">
+        <v>43</v>
+      </c>
+      <c r="F529">
+        <v>258</v>
+      </c>
+      <c r="G529">
+        <v>114</v>
+      </c>
+      <c r="H529" t="s">
+        <v>349</v>
+      </c>
+      <c r="I529">
+        <v>0</v>
+      </c>
+      <c r="J529">
+        <v>9</v>
+      </c>
+      <c r="K529">
+        <v>4</v>
+      </c>
+      <c r="L529">
+        <v>4</v>
+      </c>
+      <c r="M529">
+        <v>4</v>
+      </c>
+      <c r="N529">
+        <v>2</v>
+      </c>
+      <c r="O529">
+        <v>1</v>
+      </c>
+      <c r="P529">
+        <v>82</v>
+      </c>
+      <c r="Q529">
+        <v>1</v>
+      </c>
+      <c r="R529">
+        <v>1</v>
+      </c>
+      <c r="S529">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="530" spans="1:19">
+      <c r="A530" t="s">
+        <v>43</v>
+      </c>
+      <c r="B530" t="s">
+        <v>308</v>
+      </c>
+      <c r="C530" t="s">
+        <v>344</v>
+      </c>
+      <c r="D530">
+        <v>3.14</v>
+      </c>
+      <c r="E530">
+        <v>44</v>
+      </c>
+      <c r="F530">
+        <v>264</v>
+      </c>
+      <c r="G530">
+        <v>107</v>
+      </c>
+      <c r="H530" t="s">
+        <v>349</v>
+      </c>
+      <c r="I530">
+        <v>0</v>
+      </c>
+      <c r="J530">
+        <v>2</v>
+      </c>
+      <c r="K530">
+        <v>4</v>
+      </c>
+      <c r="L530">
+        <v>4</v>
+      </c>
+      <c r="M530">
+        <v>4</v>
+      </c>
+      <c r="N530">
+        <v>2</v>
+      </c>
+      <c r="O530">
+        <v>1</v>
+      </c>
+      <c r="P530">
+        <v>82</v>
+      </c>
+      <c r="Q530">
+        <v>1</v>
+      </c>
+      <c r="R530">
+        <v>1</v>
+      </c>
+      <c r="S530">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/harvesting_records.xlsx
+++ b/data/harvesting_records.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1186,11 +1191,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1254,6 +1259,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1300,7 +1313,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1332,9 +1345,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1366,6 +1380,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1541,11 +1556,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S623"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1604,7 +1619,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>45455</v>
       </c>
@@ -1627,7 +1642,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>45455</v>
       </c>
@@ -1638,7 +1653,7 @@
         <v>380</v>
       </c>
       <c r="D3">
-        <v>3.087</v>
+        <v>3.0870000000000002</v>
       </c>
       <c r="E3">
         <v>42</v>
@@ -1650,7 +1665,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>45455</v>
       </c>
@@ -1661,7 +1676,7 @@
         <v>380</v>
       </c>
       <c r="D4">
-        <v>3.042</v>
+        <v>3.0419999999999998</v>
       </c>
       <c r="E4">
         <v>41</v>
@@ -1673,7 +1688,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>45455</v>
       </c>
@@ -1684,7 +1699,7 @@
         <v>380</v>
       </c>
       <c r="D5">
-        <v>3.022</v>
+        <v>3.0219999999999998</v>
       </c>
       <c r="E5">
         <v>46</v>
@@ -1696,7 +1711,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>45455</v>
       </c>
@@ -1707,7 +1722,7 @@
         <v>380</v>
       </c>
       <c r="D6">
-        <v>3.042</v>
+        <v>3.0419999999999998</v>
       </c>
       <c r="E6">
         <v>52</v>
@@ -1719,7 +1734,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>45455</v>
       </c>
@@ -1742,7 +1757,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>45455</v>
       </c>
@@ -1753,7 +1768,7 @@
         <v>380</v>
       </c>
       <c r="D8">
-        <v>1.445</v>
+        <v>1.4450000000000001</v>
       </c>
       <c r="E8">
         <v>24</v>
@@ -1765,7 +1780,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>45461</v>
       </c>
@@ -1776,7 +1791,7 @@
         <v>381</v>
       </c>
       <c r="D9">
-        <v>3.054</v>
+        <v>3.0539999999999998</v>
       </c>
       <c r="E9">
         <v>38</v>
@@ -1788,7 +1803,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>45461</v>
       </c>
@@ -1799,7 +1814,7 @@
         <v>381</v>
       </c>
       <c r="D10">
-        <v>3.031</v>
+        <v>3.0310000000000001</v>
       </c>
       <c r="E10">
         <v>31</v>
@@ -1811,7 +1826,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>45461</v>
       </c>
@@ -1834,7 +1849,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>45620</v>
       </c>
@@ -1845,7 +1860,7 @@
         <v>382</v>
       </c>
       <c r="D12">
-        <v>3.025</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="E12">
         <v>36</v>
@@ -1857,7 +1872,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>45620</v>
       </c>
@@ -1868,7 +1883,7 @@
         <v>382</v>
       </c>
       <c r="D13">
-        <v>3.035</v>
+        <v>3.0350000000000001</v>
       </c>
       <c r="E13">
         <v>33</v>
@@ -1880,7 +1895,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>45620</v>
       </c>
@@ -1903,7 +1918,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>45620</v>
       </c>
@@ -1914,7 +1929,7 @@
         <v>382</v>
       </c>
       <c r="D15">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="E15">
         <v>35</v>
@@ -1926,7 +1941,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>45434</v>
       </c>
@@ -1949,7 +1964,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>45434</v>
       </c>
@@ -1972,7 +1987,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>45434</v>
       </c>
@@ -1995,7 +2010,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>45434</v>
       </c>
@@ -2012,13 +2027,13 @@
         <v>28</v>
       </c>
       <c r="F19">
-        <v>128.14</v>
+        <v>128.13999999999999</v>
       </c>
       <c r="H19" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>45434</v>
       </c>
@@ -2029,7 +2044,7 @@
         <v>383</v>
       </c>
       <c r="D20">
-        <v>3.064</v>
+        <v>3.0640000000000001</v>
       </c>
       <c r="E20">
         <v>33</v>
@@ -2041,7 +2056,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>45434</v>
       </c>
@@ -2052,7 +2067,7 @@
         <v>383</v>
       </c>
       <c r="D21">
-        <v>0.884</v>
+        <v>0.88400000000000001</v>
       </c>
       <c r="E21">
         <v>10</v>
@@ -2064,7 +2079,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>45619</v>
       </c>
@@ -2075,7 +2090,7 @@
         <v>381</v>
       </c>
       <c r="D22">
-        <v>3.023</v>
+        <v>3.0230000000000001</v>
       </c>
       <c r="E22">
         <v>49</v>
@@ -2087,7 +2102,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>45619</v>
       </c>
@@ -2098,7 +2113,7 @@
         <v>381</v>
       </c>
       <c r="D23">
-        <v>3.039</v>
+        <v>3.0390000000000001</v>
       </c>
       <c r="E23">
         <v>40</v>
@@ -2110,7 +2125,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>45619</v>
       </c>
@@ -2121,19 +2136,19 @@
         <v>381</v>
       </c>
       <c r="D24">
-        <v>3.001</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E24">
         <v>40</v>
       </c>
       <c r="F24">
-        <v>296.54</v>
+        <v>296.54000000000002</v>
       </c>
       <c r="H24" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>45619</v>
       </c>
@@ -2144,7 +2159,7 @@
         <v>381</v>
       </c>
       <c r="D25">
-        <v>3.037</v>
+        <v>3.0369999999999999</v>
       </c>
       <c r="E25">
         <v>39</v>
@@ -2156,7 +2171,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>45619</v>
       </c>
@@ -2167,19 +2182,19 @@
         <v>381</v>
       </c>
       <c r="D26">
-        <v>3.001</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E26">
         <v>40</v>
       </c>
       <c r="F26">
-        <v>289.96</v>
+        <v>289.95999999999998</v>
       </c>
       <c r="H26" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>45619</v>
       </c>
@@ -2190,19 +2205,19 @@
         <v>381</v>
       </c>
       <c r="D27">
-        <v>2.227</v>
+        <v>2.2269999999999999</v>
       </c>
       <c r="E27">
         <v>17</v>
       </c>
       <c r="F27">
-        <v>91.59999999999999</v>
+        <v>91.6</v>
       </c>
       <c r="H27" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>45479</v>
       </c>
@@ -2225,7 +2240,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>45479</v>
       </c>
@@ -2236,7 +2251,7 @@
         <v>382</v>
       </c>
       <c r="D29">
-        <v>3.026</v>
+        <v>3.0259999999999998</v>
       </c>
       <c r="E29">
         <v>34</v>
@@ -2248,7 +2263,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>45479</v>
       </c>
@@ -2259,7 +2274,7 @@
         <v>382</v>
       </c>
       <c r="D30">
-        <v>3.043</v>
+        <v>3.0430000000000001</v>
       </c>
       <c r="E30">
         <v>37</v>
@@ -2271,7 +2286,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>45479</v>
       </c>
@@ -2294,7 +2309,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>45479</v>
       </c>
@@ -2317,7 +2332,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>45479</v>
       </c>
@@ -2328,7 +2343,7 @@
         <v>382</v>
       </c>
       <c r="D33">
-        <v>0.238</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="E33">
         <v>4</v>
@@ -2340,7 +2355,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>45534</v>
       </c>
@@ -2363,7 +2378,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>45534</v>
       </c>
@@ -2374,7 +2389,7 @@
         <v>384</v>
       </c>
       <c r="D35">
-        <v>3.023</v>
+        <v>3.0230000000000001</v>
       </c>
       <c r="E35">
         <v>36</v>
@@ -2386,7 +2401,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>45534</v>
       </c>
@@ -2409,7 +2424,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>45534</v>
       </c>
@@ -2420,7 +2435,7 @@
         <v>384</v>
       </c>
       <c r="D37">
-        <v>3.033</v>
+        <v>3.0329999999999999</v>
       </c>
       <c r="E37">
         <v>31</v>
@@ -2432,7 +2447,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>45534</v>
       </c>
@@ -2443,19 +2458,19 @@
         <v>384</v>
       </c>
       <c r="D38">
-        <v>3.014</v>
+        <v>3.0139999999999998</v>
       </c>
       <c r="E38">
         <v>31</v>
       </c>
       <c r="F38">
-        <v>283.54</v>
+        <v>283.54000000000002</v>
       </c>
       <c r="H38" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>45534</v>
       </c>
@@ -2466,7 +2481,7 @@
         <v>384</v>
       </c>
       <c r="D39">
-        <v>3.007</v>
+        <v>3.0070000000000001</v>
       </c>
       <c r="E39">
         <v>36</v>
@@ -2478,7 +2493,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>45462</v>
       </c>
@@ -2501,7 +2516,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>45462</v>
       </c>
@@ -2512,7 +2527,7 @@
         <v>382</v>
       </c>
       <c r="D41">
-        <v>3.047</v>
+        <v>3.0470000000000002</v>
       </c>
       <c r="E41">
         <v>49</v>
@@ -2524,7 +2539,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>45462</v>
       </c>
@@ -2541,13 +2556,13 @@
         <v>41</v>
       </c>
       <c r="F42">
-        <v>320.16</v>
+        <v>320.16000000000003</v>
       </c>
       <c r="H42" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>45462</v>
       </c>
@@ -2558,7 +2573,7 @@
         <v>382</v>
       </c>
       <c r="D43">
-        <v>3.047</v>
+        <v>3.0470000000000002</v>
       </c>
       <c r="E43">
         <v>40</v>
@@ -2570,7 +2585,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>45462</v>
       </c>
@@ -2581,7 +2596,7 @@
         <v>382</v>
       </c>
       <c r="D44">
-        <v>3.046</v>
+        <v>3.0459999999999998</v>
       </c>
       <c r="E44">
         <v>41</v>
@@ -2593,7 +2608,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>45462</v>
       </c>
@@ -2616,7 +2631,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45548</v>
       </c>
@@ -2627,7 +2642,7 @@
         <v>381</v>
       </c>
       <c r="D46">
-        <v>3.023</v>
+        <v>3.0230000000000001</v>
       </c>
       <c r="E46">
         <v>30</v>
@@ -2639,7 +2654,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>45548</v>
       </c>
@@ -2650,7 +2665,7 @@
         <v>381</v>
       </c>
       <c r="D47">
-        <v>3.038</v>
+        <v>3.0379999999999998</v>
       </c>
       <c r="E47">
         <v>30</v>
@@ -2662,7 +2677,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>45548</v>
       </c>
@@ -2673,7 +2688,7 @@
         <v>381</v>
       </c>
       <c r="D48">
-        <v>3.038</v>
+        <v>3.0379999999999998</v>
       </c>
       <c r="E48">
         <v>30</v>
@@ -2685,7 +2700,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>45548</v>
       </c>
@@ -2696,7 +2711,7 @@
         <v>381</v>
       </c>
       <c r="D49">
-        <v>3.039</v>
+        <v>3.0390000000000001</v>
       </c>
       <c r="E49">
         <v>30</v>
@@ -2708,7 +2723,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>45548</v>
       </c>
@@ -2731,7 +2746,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>45548</v>
       </c>
@@ -2742,7 +2757,7 @@
         <v>381</v>
       </c>
       <c r="D51">
-        <v>2.346</v>
+        <v>2.3460000000000001</v>
       </c>
       <c r="E51">
         <v>27</v>
@@ -2754,7 +2769,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>45548</v>
       </c>
@@ -2765,7 +2780,7 @@
         <v>381</v>
       </c>
       <c r="D52">
-        <v>3.066</v>
+        <v>3.0659999999999998</v>
       </c>
       <c r="E52">
         <v>32</v>
@@ -2777,7 +2792,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>45548</v>
       </c>
@@ -2788,7 +2803,7 @@
         <v>381</v>
       </c>
       <c r="D53">
-        <v>3.078</v>
+        <v>3.0779999999999998</v>
       </c>
       <c r="E53">
         <v>33</v>
@@ -2800,7 +2815,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>45548</v>
       </c>
@@ -2811,7 +2826,7 @@
         <v>381</v>
       </c>
       <c r="D54">
-        <v>3.074</v>
+        <v>3.0739999999999998</v>
       </c>
       <c r="E54">
         <v>31</v>
@@ -2823,7 +2838,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>45548</v>
       </c>
@@ -2834,7 +2849,7 @@
         <v>381</v>
       </c>
       <c r="D55">
-        <v>3.094</v>
+        <v>3.0939999999999999</v>
       </c>
       <c r="E55">
         <v>39</v>
@@ -2846,7 +2861,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>45548</v>
       </c>
@@ -2869,7 +2884,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>45533</v>
       </c>
@@ -2880,19 +2895,19 @@
         <v>382</v>
       </c>
       <c r="D57">
-        <v>1.003</v>
+        <v>1.0029999999999999</v>
       </c>
       <c r="E57">
         <v>13</v>
       </c>
       <c r="F57">
-        <v>64.04000000000001</v>
+        <v>64.040000000000006</v>
       </c>
       <c r="H57" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>45533</v>
       </c>
@@ -2903,7 +2918,7 @@
         <v>382</v>
       </c>
       <c r="D58">
-        <v>1.039</v>
+        <v>1.0389999999999999</v>
       </c>
       <c r="E58">
         <v>17</v>
@@ -2915,7 +2930,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>45533</v>
       </c>
@@ -2938,7 +2953,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>45540</v>
       </c>
@@ -2949,7 +2964,7 @@
         <v>382</v>
       </c>
       <c r="D60">
-        <v>0.9849999999999999</v>
+        <v>0.98499999999999988</v>
       </c>
       <c r="E60">
         <v>13</v>
@@ -2961,7 +2976,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>45540</v>
       </c>
@@ -2972,7 +2987,7 @@
         <v>382</v>
       </c>
       <c r="D61">
-        <v>1.985</v>
+        <v>1.9850000000000001</v>
       </c>
       <c r="E61">
         <v>13</v>
@@ -2984,7 +2999,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>45504</v>
       </c>
@@ -3007,7 +3022,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>45458</v>
       </c>
@@ -3018,7 +3033,7 @@
         <v>383</v>
       </c>
       <c r="D63">
-        <v>2.166</v>
+        <v>2.1659999999999999</v>
       </c>
       <c r="E63">
         <v>12</v>
@@ -3030,7 +3045,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>45458</v>
       </c>
@@ -3041,19 +3056,19 @@
         <v>383</v>
       </c>
       <c r="D64">
-        <v>2.416</v>
+        <v>2.4159999999999999</v>
       </c>
       <c r="E64">
         <v>17</v>
       </c>
       <c r="F64">
-        <v>86.81999999999999</v>
+        <v>86.82</v>
       </c>
       <c r="H64" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>45458</v>
       </c>
@@ -3070,13 +3085,13 @@
         <v>18</v>
       </c>
       <c r="F65">
-        <v>96.17999999999999</v>
+        <v>96.179999999999993</v>
       </c>
       <c r="H65" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>45467</v>
       </c>
@@ -3087,19 +3102,19 @@
         <v>383</v>
       </c>
       <c r="D66">
-        <v>2.185</v>
+        <v>2.1850000000000001</v>
       </c>
       <c r="E66">
         <v>19</v>
       </c>
       <c r="F66">
-        <v>94.69999999999999</v>
+        <v>94.699999999999989</v>
       </c>
       <c r="H66" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>45467</v>
       </c>
@@ -3110,7 +3125,7 @@
         <v>383</v>
       </c>
       <c r="D67">
-        <v>2.189</v>
+        <v>2.1890000000000001</v>
       </c>
       <c r="E67">
         <v>15</v>
@@ -3122,7 +3137,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>45467</v>
       </c>
@@ -3133,7 +3148,7 @@
         <v>383</v>
       </c>
       <c r="D68">
-        <v>2.184</v>
+        <v>2.1840000000000002</v>
       </c>
       <c r="E68">
         <v>15</v>
@@ -3145,7 +3160,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>45467</v>
       </c>
@@ -3162,13 +3177,13 @@
         <v>22</v>
       </c>
       <c r="F69">
-        <v>130.02</v>
+        <v>130.02000000000001</v>
       </c>
       <c r="H69" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>45467</v>
       </c>
@@ -3179,7 +3194,7 @@
         <v>383</v>
       </c>
       <c r="D70">
-        <v>2.147</v>
+        <v>2.1469999999999998</v>
       </c>
       <c r="E70">
         <v>11</v>
@@ -3191,7 +3206,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>45467</v>
       </c>
@@ -3214,7 +3229,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>45467</v>
       </c>
@@ -3225,19 +3240,19 @@
         <v>383</v>
       </c>
       <c r="D72">
-        <v>2.291</v>
+        <v>2.2909999999999999</v>
       </c>
       <c r="E72">
         <v>10</v>
       </c>
       <c r="F72">
-        <v>39.68000000000001</v>
+        <v>39.680000000000007</v>
       </c>
       <c r="H72" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>45467</v>
       </c>
@@ -3260,7 +3275,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>45467</v>
       </c>
@@ -3271,7 +3286,7 @@
         <v>383</v>
       </c>
       <c r="D74">
-        <v>2.938</v>
+        <v>2.9380000000000002</v>
       </c>
       <c r="E74">
         <v>4</v>
@@ -3283,7 +3298,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>45467</v>
       </c>
@@ -3306,7 +3321,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>45443</v>
       </c>
@@ -3317,7 +3332,7 @@
         <v>382</v>
       </c>
       <c r="D76">
-        <v>2.518</v>
+        <v>2.5179999999999998</v>
       </c>
       <c r="E76">
         <v>26</v>
@@ -3329,7 +3344,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>45443</v>
       </c>
@@ -3340,7 +3355,7 @@
         <v>382</v>
       </c>
       <c r="D77">
-        <v>2.507</v>
+        <v>2.5070000000000001</v>
       </c>
       <c r="E77">
         <v>25</v>
@@ -3352,7 +3367,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>45443</v>
       </c>
@@ -3363,7 +3378,7 @@
         <v>382</v>
       </c>
       <c r="D78">
-        <v>1.259</v>
+        <v>1.2589999999999999</v>
       </c>
       <c r="E78">
         <v>16</v>
@@ -3375,7 +3390,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>45443</v>
       </c>
@@ -3386,7 +3401,7 @@
         <v>382</v>
       </c>
       <c r="D79">
-        <v>2.53</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="E79">
         <v>30</v>
@@ -3398,7 +3413,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>45443</v>
       </c>
@@ -3409,7 +3424,7 @@
         <v>382</v>
       </c>
       <c r="D80">
-        <v>2.515</v>
+        <v>2.5150000000000001</v>
       </c>
       <c r="E80">
         <v>16</v>
@@ -3421,7 +3436,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>45443</v>
       </c>
@@ -3432,7 +3447,7 @@
         <v>382</v>
       </c>
       <c r="D81">
-        <v>2.549</v>
+        <v>2.5489999999999999</v>
       </c>
       <c r="E81">
         <v>27</v>
@@ -3444,7 +3459,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>45443</v>
       </c>
@@ -3455,7 +3470,7 @@
         <v>382</v>
       </c>
       <c r="D82">
-        <v>2.505</v>
+        <v>2.5049999999999999</v>
       </c>
       <c r="E82">
         <v>23</v>
@@ -3467,7 +3482,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>45427</v>
       </c>
@@ -3490,7 +3505,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>45427</v>
       </c>
@@ -3501,7 +3516,7 @@
         <v>383</v>
       </c>
       <c r="D84">
-        <v>2.697</v>
+        <v>2.6970000000000001</v>
       </c>
       <c r="E84">
         <v>36</v>
@@ -3513,7 +3528,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>45427</v>
       </c>
@@ -3524,7 +3539,7 @@
         <v>383</v>
       </c>
       <c r="D85">
-        <v>2.671</v>
+        <v>2.6709999999999998</v>
       </c>
       <c r="E85">
         <v>33</v>
@@ -3536,7 +3551,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>45427</v>
       </c>
@@ -3547,7 +3562,7 @@
         <v>383</v>
       </c>
       <c r="D86">
-        <v>2.668</v>
+        <v>2.6680000000000001</v>
       </c>
       <c r="E86">
         <v>38</v>
@@ -3559,7 +3574,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>45427</v>
       </c>
@@ -3570,7 +3585,7 @@
         <v>383</v>
       </c>
       <c r="D87">
-        <v>2.668</v>
+        <v>2.6680000000000001</v>
       </c>
       <c r="E87">
         <v>29</v>
@@ -3582,7 +3597,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>45503</v>
       </c>
@@ -3599,13 +3614,13 @@
         <v>6</v>
       </c>
       <c r="F88">
-        <v>33.2</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="H88" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>45503</v>
       </c>
@@ -3628,7 +3643,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>45503</v>
       </c>
@@ -3639,19 +3654,19 @@
         <v>383</v>
       </c>
       <c r="D90">
-        <v>1.789</v>
+        <v>1.7889999999999999</v>
       </c>
       <c r="E90">
         <v>8</v>
       </c>
       <c r="F90">
-        <v>33.98</v>
+        <v>33.979999999999997</v>
       </c>
       <c r="H90" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>45503</v>
       </c>
@@ -3662,7 +3677,7 @@
         <v>383</v>
       </c>
       <c r="D91">
-        <v>0.954</v>
+        <v>0.95399999999999996</v>
       </c>
       <c r="E91">
         <v>3</v>
@@ -3674,7 +3689,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>45484</v>
       </c>
@@ -3697,7 +3712,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>45484</v>
       </c>
@@ -3720,7 +3735,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>45484</v>
       </c>
@@ -3743,7 +3758,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>45484</v>
       </c>
@@ -3754,7 +3769,7 @@
         <v>383</v>
       </c>
       <c r="D95">
-        <v>1.664</v>
+        <v>1.6639999999999999</v>
       </c>
       <c r="E95">
         <v>15</v>
@@ -3766,7 +3781,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>45484</v>
       </c>
@@ -3789,7 +3804,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>45484</v>
       </c>
@@ -3800,7 +3815,7 @@
         <v>383</v>
       </c>
       <c r="D97">
-        <v>2.005</v>
+        <v>2.0049999999999999</v>
       </c>
       <c r="E97">
         <v>7</v>
@@ -3812,7 +3827,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>45484</v>
       </c>
@@ -3823,7 +3838,7 @@
         <v>383</v>
       </c>
       <c r="D98">
-        <v>1.031</v>
+        <v>1.0309999999999999</v>
       </c>
       <c r="E98">
         <v>3</v>
@@ -3835,7 +3850,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>45436</v>
       </c>
@@ -3858,7 +3873,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>45436</v>
       </c>
@@ -3881,7 +3896,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>45625</v>
       </c>
@@ -3904,7 +3919,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>45625</v>
       </c>
@@ -3915,7 +3930,7 @@
         <v>382</v>
       </c>
       <c r="D102">
-        <v>3.026</v>
+        <v>3.0259999999999998</v>
       </c>
       <c r="E102">
         <v>38</v>
@@ -3927,7 +3942,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>45625</v>
       </c>
@@ -3938,7 +3953,7 @@
         <v>382</v>
       </c>
       <c r="D103">
-        <v>2.688</v>
+        <v>2.6880000000000002</v>
       </c>
       <c r="E103">
         <v>37</v>
@@ -3950,7 +3965,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>45572</v>
       </c>
@@ -3961,19 +3976,19 @@
         <v>381</v>
       </c>
       <c r="D104">
-        <v>3.025</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="E104">
         <v>49</v>
       </c>
       <c r="F104">
-        <v>312.66</v>
+        <v>312.66000000000003</v>
       </c>
       <c r="H104" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>45572</v>
       </c>
@@ -3984,19 +3999,19 @@
         <v>381</v>
       </c>
       <c r="D105">
-        <v>3.025</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="E105">
         <v>42</v>
       </c>
       <c r="F105">
-        <v>291.84</v>
+        <v>291.83999999999997</v>
       </c>
       <c r="H105" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>45572</v>
       </c>
@@ -4007,19 +4022,19 @@
         <v>381</v>
       </c>
       <c r="D106">
-        <v>1.124</v>
+        <v>1.1240000000000001</v>
       </c>
       <c r="E106">
         <v>17</v>
       </c>
       <c r="F106">
-        <v>97.54000000000001</v>
+        <v>97.54</v>
       </c>
       <c r="H106" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>45443</v>
       </c>
@@ -4030,7 +4045,7 @@
         <v>381</v>
       </c>
       <c r="D107">
-        <v>3.025</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="E107">
         <v>62</v>
@@ -4042,7 +4057,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>45443</v>
       </c>
@@ -4053,19 +4068,19 @@
         <v>381</v>
       </c>
       <c r="D108">
-        <v>3.035</v>
+        <v>3.0350000000000001</v>
       </c>
       <c r="E108">
         <v>40</v>
       </c>
       <c r="F108">
-        <v>326.97</v>
+        <v>326.97000000000003</v>
       </c>
       <c r="H108" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>45443</v>
       </c>
@@ -4088,7 +4103,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>45443</v>
       </c>
@@ -4105,13 +4120,13 @@
         <v>22</v>
       </c>
       <c r="F110">
-        <v>159.17</v>
+        <v>159.16999999999999</v>
       </c>
       <c r="H110" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>45594</v>
       </c>
@@ -4134,7 +4149,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>45594</v>
       </c>
@@ -4145,7 +4160,7 @@
         <v>381</v>
       </c>
       <c r="D112">
-        <v>3.015</v>
+        <v>3.0150000000000001</v>
       </c>
       <c r="E112">
         <v>38</v>
@@ -4157,7 +4172,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>45594</v>
       </c>
@@ -4180,7 +4195,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>45594</v>
       </c>
@@ -4191,7 +4206,7 @@
         <v>381</v>
       </c>
       <c r="D114">
-        <v>2.078</v>
+        <v>2.0779999999999998</v>
       </c>
       <c r="E114">
         <v>32</v>
@@ -4203,7 +4218,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>45553</v>
       </c>
@@ -4226,7 +4241,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>45553</v>
       </c>
@@ -4237,7 +4252,7 @@
         <v>382</v>
       </c>
       <c r="D116">
-        <v>2.978</v>
+        <v>2.9780000000000002</v>
       </c>
       <c r="E116">
         <v>23</v>
@@ -4249,7 +4264,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>45553</v>
       </c>
@@ -4260,7 +4275,7 @@
         <v>382</v>
       </c>
       <c r="D117">
-        <v>2.974</v>
+        <v>2.9740000000000002</v>
       </c>
       <c r="E117">
         <v>7</v>
@@ -4272,7 +4287,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>45553</v>
       </c>
@@ -4283,7 +4298,7 @@
         <v>382</v>
       </c>
       <c r="D118">
-        <v>0.844</v>
+        <v>0.84399999999999997</v>
       </c>
       <c r="E118">
         <v>17</v>
@@ -4295,7 +4310,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>45428</v>
       </c>
@@ -4306,7 +4321,7 @@
         <v>383</v>
       </c>
       <c r="D119">
-        <v>3.003</v>
+        <v>3.0030000000000001</v>
       </c>
       <c r="E119">
         <v>41</v>
@@ -4318,7 +4333,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>45428</v>
       </c>
@@ -4329,7 +4344,7 @@
         <v>383</v>
       </c>
       <c r="D120">
-        <v>3.068</v>
+        <v>3.0680000000000001</v>
       </c>
       <c r="E120">
         <v>41</v>
@@ -4341,7 +4356,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>45428</v>
       </c>
@@ -4352,7 +4367,7 @@
         <v>383</v>
       </c>
       <c r="D121">
-        <v>3.026</v>
+        <v>3.0259999999999998</v>
       </c>
       <c r="E121">
         <v>40</v>
@@ -4364,7 +4379,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>45428</v>
       </c>
@@ -4375,7 +4390,7 @@
         <v>383</v>
       </c>
       <c r="D122">
-        <v>3.058</v>
+        <v>3.0579999999999998</v>
       </c>
       <c r="E122">
         <v>40</v>
@@ -4387,7 +4402,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>45428</v>
       </c>
@@ -4398,7 +4413,7 @@
         <v>383</v>
       </c>
       <c r="D123">
-        <v>0.446</v>
+        <v>0.44600000000000001</v>
       </c>
       <c r="E123">
         <v>8</v>
@@ -4410,7 +4425,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>45501</v>
       </c>
@@ -4421,7 +4436,7 @@
         <v>381</v>
       </c>
       <c r="D124">
-        <v>3.055</v>
+        <v>3.0550000000000002</v>
       </c>
       <c r="E124">
         <v>36</v>
@@ -4433,7 +4448,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>45501</v>
       </c>
@@ -4444,7 +4459,7 @@
         <v>381</v>
       </c>
       <c r="D125">
-        <v>3.127</v>
+        <v>3.1269999999999998</v>
       </c>
       <c r="E125">
         <v>37</v>
@@ -4456,7 +4471,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>45501</v>
       </c>
@@ -4479,7 +4494,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>45501</v>
       </c>
@@ -4490,7 +4505,7 @@
         <v>381</v>
       </c>
       <c r="D127">
-        <v>3.099</v>
+        <v>3.0990000000000002</v>
       </c>
       <c r="E127">
         <v>36</v>
@@ -4502,7 +4517,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>45501</v>
       </c>
@@ -4525,7 +4540,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>45501</v>
       </c>
@@ -4536,7 +4551,7 @@
         <v>381</v>
       </c>
       <c r="D129">
-        <v>3.087</v>
+        <v>3.0870000000000002</v>
       </c>
       <c r="E129">
         <v>36</v>
@@ -4548,7 +4563,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>45501</v>
       </c>
@@ -4565,13 +4580,13 @@
         <v>37</v>
       </c>
       <c r="F130">
-        <v>286.21</v>
+        <v>286.20999999999998</v>
       </c>
       <c r="H130" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>45501</v>
       </c>
@@ -4582,7 +4597,7 @@
         <v>381</v>
       </c>
       <c r="D131">
-        <v>2.904</v>
+        <v>2.9039999999999999</v>
       </c>
       <c r="E131">
         <v>36</v>
@@ -4594,7 +4609,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>45431</v>
       </c>
@@ -4605,7 +4620,7 @@
         <v>383</v>
       </c>
       <c r="D132">
-        <v>3.006</v>
+        <v>3.0059999999999998</v>
       </c>
       <c r="E132">
         <v>42</v>
@@ -4617,7 +4632,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>45431</v>
       </c>
@@ -4628,7 +4643,7 @@
         <v>383</v>
       </c>
       <c r="D133">
-        <v>3.009</v>
+        <v>3.0089999999999999</v>
       </c>
       <c r="E133">
         <v>40</v>
@@ -4640,7 +4655,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>45431</v>
       </c>
@@ -4651,19 +4666,19 @@
         <v>383</v>
       </c>
       <c r="D134">
-        <v>3.019</v>
+        <v>3.0190000000000001</v>
       </c>
       <c r="E134">
         <v>35</v>
       </c>
       <c r="F134">
-        <v>264.54</v>
+        <v>264.54000000000002</v>
       </c>
       <c r="H134" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>45431</v>
       </c>
@@ -4686,7 +4701,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>45431</v>
       </c>
@@ -4709,7 +4724,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>45431</v>
       </c>
@@ -4720,19 +4735,19 @@
         <v>383</v>
       </c>
       <c r="D137">
-        <v>3.047</v>
+        <v>3.0470000000000002</v>
       </c>
       <c r="E137">
         <v>37</v>
       </c>
       <c r="F137">
-        <v>265.15</v>
+        <v>265.14999999999998</v>
       </c>
       <c r="H137" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>45431</v>
       </c>
@@ -4743,19 +4758,19 @@
         <v>383</v>
       </c>
       <c r="D138">
-        <v>3.033</v>
+        <v>3.0329999999999999</v>
       </c>
       <c r="E138">
         <v>37</v>
       </c>
       <c r="F138">
-        <v>271.71</v>
+        <v>271.70999999999998</v>
       </c>
       <c r="H138" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>45425</v>
       </c>
@@ -4766,19 +4781,19 @@
         <v>383</v>
       </c>
       <c r="D139">
-        <v>3.025</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="E139">
         <v>44</v>
       </c>
       <c r="F139">
-        <v>274.3800000000001</v>
+        <v>274.38000000000011</v>
       </c>
       <c r="H139" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>45425</v>
       </c>
@@ -4789,19 +4804,19 @@
         <v>383</v>
       </c>
       <c r="D140">
-        <v>3.026</v>
+        <v>3.0259999999999998</v>
       </c>
       <c r="E140">
         <v>44</v>
       </c>
       <c r="F140">
-        <v>276.6</v>
+        <v>276.60000000000002</v>
       </c>
       <c r="H140" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>45425</v>
       </c>
@@ -4812,19 +4827,19 @@
         <v>383</v>
       </c>
       <c r="D141">
-        <v>3.026</v>
+        <v>3.0259999999999998</v>
       </c>
       <c r="E141">
         <v>44</v>
       </c>
       <c r="F141">
-        <v>286.78</v>
+        <v>286.77999999999997</v>
       </c>
       <c r="H141" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>45425</v>
       </c>
@@ -4835,7 +4850,7 @@
         <v>383</v>
       </c>
       <c r="D142">
-        <v>3.026</v>
+        <v>3.0259999999999998</v>
       </c>
       <c r="E142">
         <v>42</v>
@@ -4847,7 +4862,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>45425</v>
       </c>
@@ -4858,19 +4873,19 @@
         <v>383</v>
       </c>
       <c r="D143">
-        <v>3.025</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="E143">
         <v>38</v>
       </c>
       <c r="F143">
-        <v>289.1900000000001</v>
+        <v>289.19000000000011</v>
       </c>
       <c r="H143" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>45425</v>
       </c>
@@ -4881,19 +4896,19 @@
         <v>383</v>
       </c>
       <c r="D144">
-        <v>3.025</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="E144">
         <v>40</v>
       </c>
       <c r="F144">
-        <v>295.78</v>
+        <v>295.77999999999997</v>
       </c>
       <c r="H144" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>45425</v>
       </c>
@@ -4904,7 +4919,7 @@
         <v>383</v>
       </c>
       <c r="D145">
-        <v>3.026</v>
+        <v>3.0259999999999998</v>
       </c>
       <c r="E145">
         <v>37</v>
@@ -4916,7 +4931,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>45425</v>
       </c>
@@ -4927,7 +4942,7 @@
         <v>383</v>
       </c>
       <c r="D146">
-        <v>3.023</v>
+        <v>3.0230000000000001</v>
       </c>
       <c r="E146">
         <v>40</v>
@@ -4939,7 +4954,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>45425</v>
       </c>
@@ -4950,7 +4965,7 @@
         <v>383</v>
       </c>
       <c r="D147">
-        <v>0.845</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="E147">
         <v>12</v>
@@ -4962,7 +4977,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>45578</v>
       </c>
@@ -4985,7 +5000,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>45578</v>
       </c>
@@ -5008,7 +5023,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>45578</v>
       </c>
@@ -5019,7 +5034,7 @@
         <v>382</v>
       </c>
       <c r="D150">
-        <v>3.015</v>
+        <v>3.0150000000000001</v>
       </c>
       <c r="E150">
         <v>46</v>
@@ -5031,7 +5046,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>45578</v>
       </c>
@@ -5042,7 +5057,7 @@
         <v>382</v>
       </c>
       <c r="D151">
-        <v>3.041</v>
+        <v>3.0409999999999999</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -5054,7 +5069,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>45578</v>
       </c>
@@ -5065,19 +5080,19 @@
         <v>382</v>
       </c>
       <c r="D152">
-        <v>3.039</v>
+        <v>3.0390000000000001</v>
       </c>
       <c r="E152">
         <v>25</v>
       </c>
       <c r="F152">
-        <v>150.02</v>
+        <v>150.02000000000001</v>
       </c>
       <c r="H152" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>45578</v>
       </c>
@@ -5088,7 +5103,7 @@
         <v>382</v>
       </c>
       <c r="D153">
-        <v>3.001</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E153">
         <v>23</v>
@@ -5100,7 +5115,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>45578</v>
       </c>
@@ -5111,19 +5126,19 @@
         <v>382</v>
       </c>
       <c r="D154">
-        <v>3.001</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E154">
         <v>31</v>
       </c>
       <c r="F154">
-        <v>155.14</v>
+        <v>155.13999999999999</v>
       </c>
       <c r="H154" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>45578</v>
       </c>
@@ -5134,7 +5149,7 @@
         <v>382</v>
       </c>
       <c r="D155">
-        <v>0.715</v>
+        <v>0.71499999999999997</v>
       </c>
       <c r="E155">
         <v>6</v>
@@ -5146,7 +5161,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>45563</v>
       </c>
@@ -5157,19 +5172,19 @@
         <v>380</v>
       </c>
       <c r="D156">
-        <v>3.049</v>
+        <v>3.0489999999999999</v>
       </c>
       <c r="E156">
         <v>43</v>
       </c>
       <c r="F156">
-        <v>324.9</v>
+        <v>324.89999999999998</v>
       </c>
       <c r="H156" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>45563</v>
       </c>
@@ -5186,13 +5201,13 @@
         <v>44</v>
       </c>
       <c r="F157">
-        <v>304.9399999999999</v>
+        <v>304.93999999999988</v>
       </c>
       <c r="H157" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>45563</v>
       </c>
@@ -5203,19 +5218,19 @@
         <v>380</v>
       </c>
       <c r="D158">
-        <v>3.001</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E158">
         <v>38</v>
       </c>
       <c r="F158">
-        <v>302.96</v>
+        <v>302.95999999999998</v>
       </c>
       <c r="H158" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>45563</v>
       </c>
@@ -5238,7 +5253,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>45563</v>
       </c>
@@ -5249,7 +5264,7 @@
         <v>380</v>
       </c>
       <c r="D160">
-        <v>3.005</v>
+        <v>3.0049999999999999</v>
       </c>
       <c r="E160">
         <v>46</v>
@@ -5261,7 +5276,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>45563</v>
       </c>
@@ -5278,13 +5293,13 @@
         <v>44</v>
       </c>
       <c r="F161">
-        <v>279.28</v>
+        <v>279.27999999999997</v>
       </c>
       <c r="H161" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>45563</v>
       </c>
@@ -5295,19 +5310,19 @@
         <v>380</v>
       </c>
       <c r="D162">
-        <v>3.398</v>
+        <v>3.3980000000000001</v>
       </c>
       <c r="E162">
         <v>57</v>
       </c>
       <c r="F162">
-        <v>289.66</v>
+        <v>289.66000000000003</v>
       </c>
       <c r="H162" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>45419</v>
       </c>
@@ -5330,7 +5345,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>45419</v>
       </c>
@@ -5341,7 +5356,7 @@
         <v>385</v>
       </c>
       <c r="D164">
-        <v>3.074</v>
+        <v>3.0739999999999998</v>
       </c>
       <c r="E164">
         <v>43</v>
@@ -5353,7 +5368,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>45419</v>
       </c>
@@ -5364,7 +5379,7 @@
         <v>385</v>
       </c>
       <c r="D165">
-        <v>3.037</v>
+        <v>3.0369999999999999</v>
       </c>
       <c r="E165">
         <v>44</v>
@@ -5376,7 +5391,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>45419</v>
       </c>
@@ -5387,7 +5402,7 @@
         <v>385</v>
       </c>
       <c r="D166">
-        <v>1.479</v>
+        <v>1.4790000000000001</v>
       </c>
       <c r="E166">
         <v>26</v>
@@ -5399,7 +5414,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>45419</v>
       </c>
@@ -5410,7 +5425,7 @@
         <v>385</v>
       </c>
       <c r="D167">
-        <v>3.096</v>
+        <v>3.0960000000000001</v>
       </c>
       <c r="E167">
         <v>43</v>
@@ -5422,7 +5437,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>45419</v>
       </c>
@@ -5433,7 +5448,7 @@
         <v>385</v>
       </c>
       <c r="D168">
-        <v>3.084</v>
+        <v>3.0840000000000001</v>
       </c>
       <c r="E168">
         <v>45</v>
@@ -5445,7 +5460,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>45419</v>
       </c>
@@ -5456,7 +5471,7 @@
         <v>385</v>
       </c>
       <c r="D169">
-        <v>3.103</v>
+        <v>3.1030000000000002</v>
       </c>
       <c r="E169">
         <v>46</v>
@@ -5468,7 +5483,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>45419</v>
       </c>
@@ -5479,7 +5494,7 @@
         <v>385</v>
       </c>
       <c r="D170">
-        <v>3.103</v>
+        <v>3.1030000000000002</v>
       </c>
       <c r="E170">
         <v>45</v>
@@ -5491,7 +5506,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>45419</v>
       </c>
@@ -5502,7 +5517,7 @@
         <v>385</v>
       </c>
       <c r="D171">
-        <v>3.103</v>
+        <v>3.1030000000000002</v>
       </c>
       <c r="E171">
         <v>43</v>
@@ -5514,7 +5529,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>45419</v>
       </c>
@@ -5525,7 +5540,7 @@
         <v>385</v>
       </c>
       <c r="D172">
-        <v>3.103</v>
+        <v>3.1030000000000002</v>
       </c>
       <c r="E172">
         <v>43</v>
@@ -5537,7 +5552,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>45419</v>
       </c>
@@ -5548,7 +5563,7 @@
         <v>385</v>
       </c>
       <c r="D173">
-        <v>3.103</v>
+        <v>3.1030000000000002</v>
       </c>
       <c r="E173">
         <v>45</v>
@@ -5560,7 +5575,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>45419</v>
       </c>
@@ -5571,7 +5586,7 @@
         <v>385</v>
       </c>
       <c r="D174">
-        <v>3.103</v>
+        <v>3.1030000000000002</v>
       </c>
       <c r="E174">
         <v>47</v>
@@ -5583,7 +5598,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>45419</v>
       </c>
@@ -5594,7 +5609,7 @@
         <v>385</v>
       </c>
       <c r="D175">
-        <v>3.103</v>
+        <v>3.1030000000000002</v>
       </c>
       <c r="E175">
         <v>50</v>
@@ -5606,7 +5621,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>45419</v>
       </c>
@@ -5629,7 +5644,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>45419</v>
       </c>
@@ -5646,13 +5661,13 @@
         <v>9</v>
       </c>
       <c r="F177">
-        <v>54.58000000000001</v>
+        <v>54.580000000000013</v>
       </c>
       <c r="H177" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>45578</v>
       </c>
@@ -5663,19 +5678,19 @@
         <v>380</v>
       </c>
       <c r="D178">
-        <v>3.123</v>
+        <v>3.1230000000000002</v>
       </c>
       <c r="E178">
         <v>42</v>
       </c>
       <c r="F178">
-        <v>321.1</v>
+        <v>321.10000000000002</v>
       </c>
       <c r="H178" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>45578</v>
       </c>
@@ -5686,19 +5701,19 @@
         <v>380</v>
       </c>
       <c r="D179">
-        <v>3.122</v>
+        <v>3.1219999999999999</v>
       </c>
       <c r="E179">
         <v>42</v>
       </c>
       <c r="F179">
-        <v>318.22</v>
+        <v>318.22000000000003</v>
       </c>
       <c r="H179" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>45578</v>
       </c>
@@ -5721,7 +5736,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>45578</v>
       </c>
@@ -5744,7 +5759,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>45578</v>
       </c>
@@ -5755,7 +5770,7 @@
         <v>380</v>
       </c>
       <c r="D182">
-        <v>3.078</v>
+        <v>3.0779999999999998</v>
       </c>
       <c r="E182">
         <v>47</v>
@@ -5767,7 +5782,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>45578</v>
       </c>
@@ -5790,7 +5805,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>45578</v>
       </c>
@@ -5801,7 +5816,7 @@
         <v>380</v>
       </c>
       <c r="D184">
-        <v>3.158</v>
+        <v>3.1579999999999999</v>
       </c>
       <c r="E184">
         <v>42</v>
@@ -5813,7 +5828,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
         <v>45578</v>
       </c>
@@ -5824,7 +5839,7 @@
         <v>380</v>
       </c>
       <c r="D185">
-        <v>1.815</v>
+        <v>1.8149999999999999</v>
       </c>
       <c r="E185">
         <v>30</v>
@@ -5836,7 +5851,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>45484</v>
       </c>
@@ -5859,7 +5874,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>45484</v>
       </c>
@@ -5882,7 +5897,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>45484</v>
       </c>
@@ -5893,7 +5908,7 @@
         <v>382</v>
       </c>
       <c r="D188">
-        <v>3.014</v>
+        <v>3.0139999999999998</v>
       </c>
       <c r="E188">
         <v>38</v>
@@ -5905,7 +5920,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <v>45484</v>
       </c>
@@ -5916,7 +5931,7 @@
         <v>382</v>
       </c>
       <c r="D189">
-        <v>3.014</v>
+        <v>3.0139999999999998</v>
       </c>
       <c r="E189">
         <v>36</v>
@@ -5928,7 +5943,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>45484</v>
       </c>
@@ -5939,7 +5954,7 @@
         <v>382</v>
       </c>
       <c r="D190">
-        <v>3.015</v>
+        <v>3.0150000000000001</v>
       </c>
       <c r="E190">
         <v>42</v>
@@ -5951,7 +5966,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <v>45484</v>
       </c>
@@ -5962,7 +5977,7 @@
         <v>382</v>
       </c>
       <c r="D191">
-        <v>3.007</v>
+        <v>3.0070000000000001</v>
       </c>
       <c r="E191">
         <v>36</v>
@@ -5974,7 +5989,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <v>45484</v>
       </c>
@@ -5985,7 +6000,7 @@
         <v>382</v>
       </c>
       <c r="D192">
-        <v>3.013</v>
+        <v>3.0129999999999999</v>
       </c>
       <c r="E192">
         <v>38</v>
@@ -5997,7 +6012,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
         <v>45484</v>
       </c>
@@ -6008,7 +6023,7 @@
         <v>382</v>
       </c>
       <c r="D193">
-        <v>3.007</v>
+        <v>3.0070000000000001</v>
       </c>
       <c r="E193">
         <v>41</v>
@@ -6020,7 +6035,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>45484</v>
       </c>
@@ -6031,7 +6046,7 @@
         <v>382</v>
       </c>
       <c r="D194">
-        <v>3.042</v>
+        <v>3.0419999999999998</v>
       </c>
       <c r="E194">
         <v>37</v>
@@ -6043,7 +6058,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
         <v>45484</v>
       </c>
@@ -6054,7 +6069,7 @@
         <v>382</v>
       </c>
       <c r="D195">
-        <v>3.013</v>
+        <v>3.0129999999999999</v>
       </c>
       <c r="E195">
         <v>40</v>
@@ -6066,7 +6081,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
         <v>45484</v>
       </c>
@@ -6077,7 +6092,7 @@
         <v>382</v>
       </c>
       <c r="D196">
-        <v>3.007</v>
+        <v>3.0070000000000001</v>
       </c>
       <c r="E196">
         <v>46</v>
@@ -6089,7 +6104,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>45484</v>
       </c>
@@ -6112,7 +6127,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <v>45565</v>
       </c>
@@ -6135,7 +6150,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
         <v>45565</v>
       </c>
@@ -6146,7 +6161,7 @@
         <v>382</v>
       </c>
       <c r="D199">
-        <v>3.035</v>
+        <v>3.0350000000000001</v>
       </c>
       <c r="E199">
         <v>28</v>
@@ -6158,7 +6173,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <v>45565</v>
       </c>
@@ -6181,7 +6196,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
         <v>45565</v>
       </c>
@@ -6192,7 +6207,7 @@
         <v>382</v>
       </c>
       <c r="D201">
-        <v>3.019</v>
+        <v>3.0190000000000001</v>
       </c>
       <c r="E201">
         <v>20</v>
@@ -6204,7 +6219,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>45565</v>
       </c>
@@ -6215,7 +6230,7 @@
         <v>382</v>
       </c>
       <c r="D202">
-        <v>2.388</v>
+        <v>2.3879999999999999</v>
       </c>
       <c r="E202">
         <v>9</v>
@@ -6227,7 +6242,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
         <v>45597</v>
       </c>
@@ -6238,7 +6253,7 @@
         <v>381</v>
       </c>
       <c r="D203">
-        <v>3.026</v>
+        <v>3.0259999999999998</v>
       </c>
       <c r="E203">
         <v>44</v>
@@ -6250,7 +6265,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <v>45597</v>
       </c>
@@ -6261,7 +6276,7 @@
         <v>381</v>
       </c>
       <c r="D204">
-        <v>3.002</v>
+        <v>3.0019999999999998</v>
       </c>
       <c r="E204">
         <v>25</v>
@@ -6273,7 +6288,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
         <v>45597</v>
       </c>
@@ -6296,7 +6311,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>45435</v>
       </c>
@@ -6307,7 +6322,7 @@
         <v>384</v>
       </c>
       <c r="D206">
-        <v>4.195</v>
+        <v>4.1950000000000003</v>
       </c>
       <c r="E206">
         <v>72</v>
@@ -6319,7 +6334,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
         <v>45607</v>
       </c>
@@ -6342,7 +6357,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
         <v>45607</v>
       </c>
@@ -6365,7 +6380,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
         <v>45607</v>
       </c>
@@ -6376,7 +6391,7 @@
         <v>383</v>
       </c>
       <c r="D209">
-        <v>3.037</v>
+        <v>3.0369999999999999</v>
       </c>
       <c r="E209">
         <v>37</v>
@@ -6388,7 +6403,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>45607</v>
       </c>
@@ -6399,7 +6414,7 @@
         <v>383</v>
       </c>
       <c r="D210">
-        <v>3.039</v>
+        <v>3.0390000000000001</v>
       </c>
       <c r="E210">
         <v>37</v>
@@ -6411,7 +6426,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
         <v>45607</v>
       </c>
@@ -6422,7 +6437,7 @@
         <v>383</v>
       </c>
       <c r="D211">
-        <v>3.051</v>
+        <v>3.0510000000000002</v>
       </c>
       <c r="E211">
         <v>38</v>
@@ -6434,7 +6449,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
         <v>45607</v>
       </c>
@@ -6445,7 +6460,7 @@
         <v>383</v>
       </c>
       <c r="D212">
-        <v>0.795</v>
+        <v>0.79500000000000004</v>
       </c>
       <c r="E212">
         <v>11</v>
@@ -6457,7 +6472,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
         <v>45523</v>
       </c>
@@ -6468,7 +6483,7 @@
         <v>383</v>
       </c>
       <c r="D213">
-        <v>1.747</v>
+        <v>1.7470000000000001</v>
       </c>
       <c r="E213">
         <v>27</v>
@@ -6480,7 +6495,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>45523</v>
       </c>
@@ -6491,7 +6506,7 @@
         <v>383</v>
       </c>
       <c r="D214">
-        <v>3.014</v>
+        <v>3.0139999999999998</v>
       </c>
       <c r="E214">
         <v>43</v>
@@ -6503,7 +6518,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
         <v>45523</v>
       </c>
@@ -6520,13 +6535,13 @@
         <v>42</v>
       </c>
       <c r="F215">
-        <v>341.9800000000001</v>
+        <v>341.98000000000008</v>
       </c>
       <c r="H215" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
         <v>45523</v>
       </c>
@@ -6549,7 +6564,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
         <v>45523</v>
       </c>
@@ -6560,7 +6575,7 @@
         <v>383</v>
       </c>
       <c r="D217">
-        <v>3.094</v>
+        <v>3.0939999999999999</v>
       </c>
       <c r="E217">
         <v>30</v>
@@ -6572,7 +6587,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>45613</v>
       </c>
@@ -6583,7 +6598,7 @@
         <v>382</v>
       </c>
       <c r="D218">
-        <v>3.001</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E218">
         <v>32</v>
@@ -6595,7 +6610,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
         <v>45613</v>
       </c>
@@ -6606,7 +6621,7 @@
         <v>382</v>
       </c>
       <c r="D219">
-        <v>3.006</v>
+        <v>3.0059999999999998</v>
       </c>
       <c r="E219">
         <v>32</v>
@@ -6618,7 +6633,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <v>45613</v>
       </c>
@@ -6629,7 +6644,7 @@
         <v>382</v>
       </c>
       <c r="D220">
-        <v>3.017</v>
+        <v>3.0169999999999999</v>
       </c>
       <c r="E220">
         <v>33</v>
@@ -6641,7 +6656,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
         <v>45613</v>
       </c>
@@ -6652,7 +6667,7 @@
         <v>382</v>
       </c>
       <c r="D221">
-        <v>3.002</v>
+        <v>3.0019999999999998</v>
       </c>
       <c r="E221">
         <v>33</v>
@@ -6664,7 +6679,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>45613</v>
       </c>
@@ -6675,7 +6690,7 @@
         <v>382</v>
       </c>
       <c r="D222">
-        <v>3.029</v>
+        <v>3.0289999999999999</v>
       </c>
       <c r="E222">
         <v>36</v>
@@ -6687,7 +6702,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
         <v>45613</v>
       </c>
@@ -6698,7 +6713,7 @@
         <v>382</v>
       </c>
       <c r="D223">
-        <v>1.834</v>
+        <v>1.8340000000000001</v>
       </c>
       <c r="E223">
         <v>25</v>
@@ -6710,7 +6725,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
         <v>45493</v>
       </c>
@@ -6721,7 +6736,7 @@
         <v>381</v>
       </c>
       <c r="D224">
-        <v>3.001</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E224">
         <v>26</v>
@@ -6733,7 +6748,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
         <v>45493</v>
       </c>
@@ -6744,7 +6759,7 @@
         <v>381</v>
       </c>
       <c r="D225">
-        <v>3.002</v>
+        <v>3.0019999999999998</v>
       </c>
       <c r="E225">
         <v>24</v>
@@ -6756,7 +6771,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <v>45493</v>
       </c>
@@ -6767,7 +6782,7 @@
         <v>381</v>
       </c>
       <c r="D226">
-        <v>3.001</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E226">
         <v>26</v>
@@ -6779,7 +6794,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
         <v>45493</v>
       </c>
@@ -6802,7 +6817,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="228" spans="1:8">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
         <v>45493</v>
       </c>
@@ -6813,7 +6828,7 @@
         <v>381</v>
       </c>
       <c r="D228">
-        <v>3.001</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E228">
         <v>26</v>
@@ -6825,7 +6840,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
         <v>45493</v>
       </c>
@@ -6836,7 +6851,7 @@
         <v>381</v>
       </c>
       <c r="D229">
-        <v>3.001</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E229">
         <v>25</v>
@@ -6848,7 +6863,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <v>45493</v>
       </c>
@@ -6859,19 +6874,19 @@
         <v>381</v>
       </c>
       <c r="D230">
-        <v>3.003</v>
+        <v>3.0030000000000001</v>
       </c>
       <c r="E230">
         <v>25</v>
       </c>
       <c r="F230">
-        <v>152.67</v>
+        <v>152.66999999999999</v>
       </c>
       <c r="H230" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
         <v>45493</v>
       </c>
@@ -6882,7 +6897,7 @@
         <v>381</v>
       </c>
       <c r="D231">
-        <v>2.134</v>
+        <v>2.1339999999999999</v>
       </c>
       <c r="E231">
         <v>26</v>
@@ -6894,7 +6909,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
         <v>45615</v>
       </c>
@@ -6905,7 +6920,7 @@
         <v>382</v>
       </c>
       <c r="D232">
-        <v>3.054</v>
+        <v>3.0539999999999998</v>
       </c>
       <c r="E232">
         <v>29</v>
@@ -6917,7 +6932,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="233" spans="1:8">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
         <v>45615</v>
       </c>
@@ -6928,7 +6943,7 @@
         <v>382</v>
       </c>
       <c r="D233">
-        <v>3.055</v>
+        <v>3.0550000000000002</v>
       </c>
       <c r="E233">
         <v>28</v>
@@ -6940,7 +6955,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="234" spans="1:8">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <v>45615</v>
       </c>
@@ -6963,7 +6978,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="235" spans="1:8">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
         <v>45615</v>
       </c>
@@ -6986,7 +7001,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="236" spans="1:8">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
         <v>45615</v>
       </c>
@@ -6997,7 +7012,7 @@
         <v>382</v>
       </c>
       <c r="D236">
-        <v>3.064</v>
+        <v>3.0640000000000001</v>
       </c>
       <c r="E236">
         <v>23</v>
@@ -7009,7 +7024,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="237" spans="1:8">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <v>45615</v>
       </c>
@@ -7032,7 +7047,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="238" spans="1:8">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>45615</v>
       </c>
@@ -7055,7 +7070,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="239" spans="1:8">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
         <v>45446</v>
       </c>
@@ -7072,13 +7087,13 @@
         <v>44</v>
       </c>
       <c r="F239">
-        <v>296.34</v>
+        <v>296.33999999999997</v>
       </c>
       <c r="H239" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="240" spans="1:8">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
         <v>45446</v>
       </c>
@@ -7089,7 +7104,7 @@
         <v>383</v>
       </c>
       <c r="D240">
-        <v>3.053</v>
+        <v>3.0529999999999999</v>
       </c>
       <c r="E240">
         <v>42</v>
@@ -7101,7 +7116,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="241" spans="1:8">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
         <v>45446</v>
       </c>
@@ -7112,7 +7127,7 @@
         <v>383</v>
       </c>
       <c r="D241">
-        <v>3.046</v>
+        <v>3.0459999999999998</v>
       </c>
       <c r="E241">
         <v>45</v>
@@ -7124,7 +7139,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="242" spans="1:8">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>45446</v>
       </c>
@@ -7135,19 +7150,19 @@
         <v>383</v>
       </c>
       <c r="D242">
-        <v>3.054</v>
+        <v>3.0539999999999998</v>
       </c>
       <c r="E242">
         <v>48</v>
       </c>
       <c r="F242">
-        <v>281.29</v>
+        <v>281.29000000000002</v>
       </c>
       <c r="H242" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="243" spans="1:8">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <v>45446</v>
       </c>
@@ -7158,19 +7173,19 @@
         <v>383</v>
       </c>
       <c r="D243">
-        <v>3.055</v>
+        <v>3.0550000000000002</v>
       </c>
       <c r="E243">
         <v>45</v>
       </c>
       <c r="F243">
-        <v>281.8800000000001</v>
+        <v>281.88000000000011</v>
       </c>
       <c r="H243" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="244" spans="1:8">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <v>45446</v>
       </c>
@@ -7181,19 +7196,19 @@
         <v>383</v>
       </c>
       <c r="D244">
-        <v>3.064</v>
+        <v>3.0640000000000001</v>
       </c>
       <c r="E244">
         <v>46</v>
       </c>
       <c r="F244">
-        <v>269.3200000000001</v>
+        <v>269.32000000000011</v>
       </c>
       <c r="H244" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="245" spans="1:8">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
         <v>45446</v>
       </c>
@@ -7204,7 +7219,7 @@
         <v>383</v>
       </c>
       <c r="D245">
-        <v>3.071</v>
+        <v>3.0710000000000002</v>
       </c>
       <c r="E245">
         <v>46</v>
@@ -7216,7 +7231,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="246" spans="1:8">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <v>45446</v>
       </c>
@@ -7227,7 +7242,7 @@
         <v>383</v>
       </c>
       <c r="D246">
-        <v>3.049</v>
+        <v>3.0489999999999999</v>
       </c>
       <c r="E246">
         <v>45</v>
@@ -7239,7 +7254,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="247" spans="1:8">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <v>45446</v>
       </c>
@@ -7250,7 +7265,7 @@
         <v>383</v>
       </c>
       <c r="D247">
-        <v>0.362</v>
+        <v>0.36199999999999999</v>
       </c>
       <c r="E247">
         <v>7</v>
@@ -7262,7 +7277,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="248" spans="1:8">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
         <v>45622</v>
       </c>
@@ -7273,19 +7288,19 @@
         <v>382</v>
       </c>
       <c r="D248">
-        <v>3.038</v>
+        <v>3.0379999999999998</v>
       </c>
       <c r="E248">
         <v>22</v>
       </c>
       <c r="F248">
-        <v>98.54000000000001</v>
+        <v>98.54</v>
       </c>
       <c r="H248" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="249" spans="1:8">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
         <v>45622</v>
       </c>
@@ -7296,7 +7311,7 @@
         <v>382</v>
       </c>
       <c r="D249">
-        <v>3.025</v>
+        <v>3.0249999999999999</v>
       </c>
       <c r="E249">
         <v>25</v>
@@ -7308,7 +7323,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="250" spans="1:8">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <v>45622</v>
       </c>
@@ -7331,7 +7346,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="251" spans="1:8">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
         <v>45622</v>
       </c>
@@ -7354,7 +7369,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="252" spans="1:8">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
         <v>45622</v>
       </c>
@@ -7365,19 +7380,19 @@
         <v>382</v>
       </c>
       <c r="D252">
-        <v>3.005</v>
+        <v>3.0049999999999999</v>
       </c>
       <c r="E252">
         <v>30</v>
       </c>
       <c r="F252">
-        <v>129.52</v>
+        <v>129.52000000000001</v>
       </c>
       <c r="H252" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="253" spans="1:8">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
         <v>45622</v>
       </c>
@@ -7388,7 +7403,7 @@
         <v>382</v>
       </c>
       <c r="D253">
-        <v>3.011</v>
+        <v>3.0110000000000001</v>
       </c>
       <c r="E253">
         <v>29</v>
@@ -7400,7 +7415,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="254" spans="1:8">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <v>45622</v>
       </c>
@@ -7411,19 +7426,19 @@
         <v>382</v>
       </c>
       <c r="D254">
-        <v>1.011</v>
+        <v>1.0109999999999999</v>
       </c>
       <c r="E254">
         <v>9</v>
       </c>
       <c r="F254">
-        <v>36.48</v>
+        <v>36.479999999999997</v>
       </c>
       <c r="H254" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="255" spans="1:8">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
         <v>45552</v>
       </c>
@@ -7434,7 +7449,7 @@
         <v>383</v>
       </c>
       <c r="D255">
-        <v>4.051</v>
+        <v>4.0510000000000002</v>
       </c>
       <c r="E255">
         <v>37</v>
@@ -7446,7 +7461,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="256" spans="1:8">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
         <v>45552</v>
       </c>
@@ -7463,13 +7478,13 @@
         <v>37</v>
       </c>
       <c r="F256">
-        <v>287.72</v>
+        <v>287.72000000000003</v>
       </c>
       <c r="H256" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="257" spans="1:8">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
         <v>45552</v>
       </c>
@@ -7492,7 +7507,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="258" spans="1:8">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
         <v>45552</v>
       </c>
@@ -7515,7 +7530,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="259" spans="1:8">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
         <v>45552</v>
       </c>
@@ -7526,7 +7541,7 @@
         <v>383</v>
       </c>
       <c r="D259">
-        <v>3.021</v>
+        <v>3.0209999999999999</v>
       </c>
       <c r="E259">
         <v>39</v>
@@ -7538,7 +7553,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="260" spans="1:8">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
         <v>45552</v>
       </c>
@@ -7549,7 +7564,7 @@
         <v>383</v>
       </c>
       <c r="D260">
-        <v>3.021</v>
+        <v>3.0209999999999999</v>
       </c>
       <c r="E260">
         <v>38</v>
@@ -7561,7 +7576,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="261" spans="1:8">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
         <v>45552</v>
       </c>
@@ -7584,7 +7599,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="262" spans="1:8">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
         <v>45552</v>
       </c>
@@ -7607,7 +7622,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="263" spans="1:8">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="2">
         <v>45510</v>
       </c>
@@ -7630,7 +7645,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="264" spans="1:8">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="2">
         <v>45510</v>
       </c>
@@ -7641,7 +7656,7 @@
         <v>382</v>
       </c>
       <c r="D264">
-        <v>3.118</v>
+        <v>3.1179999999999999</v>
       </c>
       <c r="E264">
         <v>36</v>
@@ -7653,7 +7668,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="265" spans="1:8">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" s="2">
         <v>45510</v>
       </c>
@@ -7664,7 +7679,7 @@
         <v>382</v>
       </c>
       <c r="D265">
-        <v>3.136</v>
+        <v>3.1360000000000001</v>
       </c>
       <c r="E265">
         <v>42</v>
@@ -7676,7 +7691,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="266" spans="1:8">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <v>45510</v>
       </c>
@@ -7687,7 +7702,7 @@
         <v>382</v>
       </c>
       <c r="D266">
-        <v>3.136</v>
+        <v>3.1360000000000001</v>
       </c>
       <c r="E266">
         <v>34</v>
@@ -7699,7 +7714,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="267" spans="1:8">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
         <v>45510</v>
       </c>
@@ -7722,7 +7737,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="268" spans="1:8">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
         <v>45510</v>
       </c>
@@ -7733,7 +7748,7 @@
         <v>382</v>
       </c>
       <c r="D268">
-        <v>2.697</v>
+        <v>2.6970000000000001</v>
       </c>
       <c r="E268">
         <v>36</v>
@@ -7745,7 +7760,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="269" spans="1:8">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
         <v>45594</v>
       </c>
@@ -7756,7 +7771,7 @@
         <v>381</v>
       </c>
       <c r="D269">
-        <v>2.994</v>
+        <v>2.9940000000000002</v>
       </c>
       <c r="E269">
         <v>36</v>
@@ -7768,7 +7783,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="270" spans="1:8">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
         <v>45594</v>
       </c>
@@ -7791,7 +7806,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="271" spans="1:8">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
         <v>45594</v>
       </c>
@@ -7814,7 +7829,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="272" spans="1:8">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
         <v>45594</v>
       </c>
@@ -7825,7 +7840,7 @@
         <v>381</v>
       </c>
       <c r="D272">
-        <v>2.997</v>
+        <v>2.9969999999999999</v>
       </c>
       <c r="E272">
         <v>34</v>
@@ -7837,7 +7852,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="273" spans="1:8">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
         <v>45594</v>
       </c>
@@ -7860,7 +7875,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="274" spans="1:8">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
         <v>45594</v>
       </c>
@@ -7883,7 +7898,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="275" spans="1:8">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" s="2">
         <v>45594</v>
       </c>
@@ -7906,7 +7921,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="276" spans="1:8">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" s="2">
         <v>45594</v>
       </c>
@@ -7917,7 +7932,7 @@
         <v>381</v>
       </c>
       <c r="D276">
-        <v>2.997</v>
+        <v>2.9969999999999999</v>
       </c>
       <c r="E276">
         <v>37</v>
@@ -7929,7 +7944,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="277" spans="1:8">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" s="2">
         <v>45594</v>
       </c>
@@ -7940,19 +7955,19 @@
         <v>381</v>
       </c>
       <c r="D277">
-        <v>0.143</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="E277">
         <v>5</v>
       </c>
       <c r="F277">
-        <v>17.58</v>
+        <v>17.579999999999998</v>
       </c>
       <c r="H277" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="278" spans="1:8">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
         <v>45413</v>
       </c>
@@ -7963,7 +7978,7 @@
         <v>383</v>
       </c>
       <c r="D278">
-        <v>3.108</v>
+        <v>3.1080000000000001</v>
       </c>
       <c r="E278">
         <v>37</v>
@@ -7975,7 +7990,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="279" spans="1:8">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" s="2">
         <v>45413</v>
       </c>
@@ -7986,19 +8001,19 @@
         <v>383</v>
       </c>
       <c r="D279">
-        <v>3.126</v>
+        <v>3.1259999999999999</v>
       </c>
       <c r="E279">
         <v>37</v>
       </c>
       <c r="F279">
-        <v>284.97</v>
+        <v>284.97000000000003</v>
       </c>
       <c r="H279" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="280" spans="1:8">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
         <v>45413</v>
       </c>
@@ -8015,13 +8030,13 @@
         <v>38</v>
       </c>
       <c r="F280">
-        <v>295.16</v>
+        <v>295.16000000000003</v>
       </c>
       <c r="H280" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="281" spans="1:8">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="2">
         <v>45413</v>
       </c>
@@ -8032,7 +8047,7 @@
         <v>383</v>
       </c>
       <c r="D281">
-        <v>4.634</v>
+        <v>4.6340000000000003</v>
       </c>
       <c r="E281">
         <v>63</v>
@@ -8044,7 +8059,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="282" spans="1:8">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
         <v>45473</v>
       </c>
@@ -8055,19 +8070,19 @@
         <v>382</v>
       </c>
       <c r="D282">
-        <v>3.001</v>
+        <v>3.0009999999999999</v>
       </c>
       <c r="E282">
         <v>41</v>
       </c>
       <c r="F282">
-        <v>289.96</v>
+        <v>289.95999999999998</v>
       </c>
       <c r="H282" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="283" spans="1:8">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="2">
         <v>45473</v>
       </c>
@@ -8078,19 +8093,19 @@
         <v>382</v>
       </c>
       <c r="D283">
-        <v>2.897</v>
+        <v>2.8969999999999998</v>
       </c>
       <c r="E283">
         <v>43</v>
       </c>
       <c r="F283">
-        <v>292.72</v>
+        <v>292.72000000000003</v>
       </c>
       <c r="H283" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="284" spans="1:8">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="2">
         <v>45473</v>
       </c>
@@ -8101,19 +8116,19 @@
         <v>382</v>
       </c>
       <c r="D284">
-        <v>3.006</v>
+        <v>3.0059999999999998</v>
       </c>
       <c r="E284">
         <v>47</v>
       </c>
       <c r="F284">
-        <v>309.9</v>
+        <v>309.89999999999998</v>
       </c>
       <c r="H284" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="285" spans="1:8">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="2">
         <v>45521</v>
       </c>
@@ -8136,7 +8151,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="286" spans="1:8">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
         <v>45521</v>
       </c>
@@ -8147,19 +8162,19 @@
         <v>382</v>
       </c>
       <c r="D286">
-        <v>3.027</v>
+        <v>3.0270000000000001</v>
       </c>
       <c r="E286">
         <v>37</v>
       </c>
       <c r="F286">
-        <v>135.42</v>
+        <v>135.41999999999999</v>
       </c>
       <c r="H286" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="287" spans="1:8">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="2">
         <v>45521</v>
       </c>
@@ -8182,7 +8197,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="288" spans="1:8">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="2">
         <v>45521</v>
       </c>
@@ -8193,7 +8208,7 @@
         <v>382</v>
       </c>
       <c r="D288">
-        <v>3.027</v>
+        <v>3.0270000000000001</v>
       </c>
       <c r="E288">
         <v>25</v>
@@ -8205,7 +8220,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="289" spans="1:19">
+    <row r="289" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A289" s="2">
         <v>45521</v>
       </c>
@@ -8216,7 +8231,7 @@
         <v>382</v>
       </c>
       <c r="D289">
-        <v>3.027</v>
+        <v>3.0270000000000001</v>
       </c>
       <c r="E289">
         <v>24</v>
@@ -8228,7 +8243,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="290" spans="1:19">
+    <row r="290" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
         <v>45521</v>
       </c>
@@ -8239,7 +8254,7 @@
         <v>382</v>
       </c>
       <c r="D290">
-        <v>3.013</v>
+        <v>3.0129999999999999</v>
       </c>
       <c r="E290">
         <v>24</v>
@@ -8251,7 +8266,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="291" spans="1:19">
+    <row r="291" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A291" s="2">
         <v>45521</v>
       </c>
@@ -8262,7 +8277,7 @@
         <v>382</v>
       </c>
       <c r="D291">
-        <v>3.003</v>
+        <v>3.0030000000000001</v>
       </c>
       <c r="E291">
         <v>29</v>
@@ -8274,7 +8289,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="292" spans="1:19">
+    <row r="292" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A292" s="2">
         <v>45521</v>
       </c>
@@ -8285,7 +8300,7 @@
         <v>382</v>
       </c>
       <c r="D292">
-        <v>2.025</v>
+        <v>2.0249999999999999</v>
       </c>
       <c r="E292">
         <v>20</v>
@@ -8297,7 +8312,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="293" spans="1:19">
+    <row r="293" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A293" s="2">
         <v>45784</v>
       </c>
@@ -8356,7 +8371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:19">
+    <row r="294" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
         <v>45784</v>
       </c>
@@ -8415,7 +8430,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="295" spans="1:19">
+    <row r="295" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A295" s="2">
         <v>45784</v>
       </c>
@@ -8474,7 +8489,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="296" spans="1:19">
+    <row r="296" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A296" s="2">
         <v>45784</v>
       </c>
@@ -8533,7 +8548,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="297" spans="1:19">
+    <row r="297" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A297" s="2">
         <v>45787</v>
       </c>
@@ -8592,7 +8607,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="298" spans="1:19">
+    <row r="298" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
         <v>45787</v>
       </c>
@@ -8651,7 +8666,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="299" spans="1:19">
+    <row r="299" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A299" s="2">
         <v>45789</v>
       </c>
@@ -8710,7 +8725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:19">
+    <row r="300" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A300" s="2">
         <v>45789</v>
       </c>
@@ -8769,7 +8784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:19">
+    <row r="301" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A301" s="2">
         <v>45789</v>
       </c>
@@ -8828,7 +8843,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="302" spans="1:19">
+    <row r="302" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A302" s="2">
         <v>45789</v>
       </c>
@@ -8887,7 +8902,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="303" spans="1:19">
+    <row r="303" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A303" s="2">
         <v>45789</v>
       </c>
@@ -8946,7 +8961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="304" spans="1:19">
+    <row r="304" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A304" s="2">
         <v>45789</v>
       </c>
@@ -9005,7 +9020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:19">
+    <row r="305" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A305" s="2">
         <v>45790</v>
       </c>
@@ -9016,7 +9031,7 @@
         <v>384</v>
       </c>
       <c r="D305">
-        <v>4.19</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="E305">
         <v>61</v>
@@ -9064,7 +9079,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="306" spans="1:19">
+    <row r="306" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A306" s="2">
         <v>45795</v>
       </c>
@@ -9123,7 +9138,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="307" spans="1:19">
+    <row r="307" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A307" s="2">
         <v>45795</v>
       </c>
@@ -9182,7 +9197,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="308" spans="1:19">
+    <row r="308" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A308" s="2">
         <v>45795</v>
       </c>
@@ -9241,7 +9256,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="309" spans="1:19">
+    <row r="309" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A309" s="2">
         <v>45795</v>
       </c>
@@ -9300,7 +9315,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="310" spans="1:19">
+    <row r="310" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A310" s="2">
         <v>45795</v>
       </c>
@@ -9359,7 +9374,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="311" spans="1:19">
+    <row r="311" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A311" s="2">
         <v>45796</v>
       </c>
@@ -9418,7 +9433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="312" spans="1:19">
+    <row r="312" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A312" s="2">
         <v>45796</v>
       </c>
@@ -9477,7 +9492,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="313" spans="1:19">
+    <row r="313" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A313" s="2">
         <v>45796</v>
       </c>
@@ -9536,7 +9551,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="314" spans="1:19">
+    <row r="314" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A314" s="2">
         <v>45796</v>
       </c>
@@ -9595,7 +9610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:19">
+    <row r="315" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A315" s="2">
         <v>45796</v>
       </c>
@@ -9654,7 +9669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="316" spans="1:19">
+    <row r="316" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A316" s="2">
         <v>45798</v>
       </c>
@@ -9713,7 +9728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:19">
+    <row r="317" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A317" s="2">
         <v>45798</v>
       </c>
@@ -9772,7 +9787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:19">
+    <row r="318" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A318" s="2">
         <v>45798</v>
       </c>
@@ -9831,7 +9846,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="319" spans="1:19">
+    <row r="319" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A319" s="2">
         <v>45798</v>
       </c>
@@ -9890,7 +9905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="320" spans="1:19">
+    <row r="320" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A320" s="2">
         <v>45798</v>
       </c>
@@ -9949,7 +9964,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="1:19">
+    <row r="321" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A321" s="2">
         <v>45807</v>
       </c>
@@ -10008,7 +10023,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="322" spans="1:19">
+    <row r="322" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A322" s="2">
         <v>45807</v>
       </c>
@@ -10067,7 +10082,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:19">
+    <row r="323" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A323" s="2">
         <v>45807</v>
       </c>
@@ -10126,7 +10141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="324" spans="1:19">
+    <row r="324" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A324" s="2">
         <v>45807</v>
       </c>
@@ -10185,7 +10200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="325" spans="1:19">
+    <row r="325" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A325" s="2">
         <v>45807</v>
       </c>
@@ -10244,7 +10259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:19">
+    <row r="326" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A326" s="2">
         <v>45808</v>
       </c>
@@ -10303,7 +10318,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="1:19">
+    <row r="327" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A327" s="2">
         <v>45809</v>
       </c>
@@ -10362,7 +10377,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="328" spans="1:19">
+    <row r="328" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A328" s="2">
         <v>45809</v>
       </c>
@@ -10421,7 +10436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="329" spans="1:19">
+    <row r="329" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A329" s="2">
         <v>45809</v>
       </c>
@@ -10480,7 +10495,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="330" spans="1:19">
+    <row r="330" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A330" s="2">
         <v>45809</v>
       </c>
@@ -10539,7 +10554,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="331" spans="1:19">
+    <row r="331" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A331" s="2">
         <v>45809</v>
       </c>
@@ -10598,7 +10613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="1:19">
+    <row r="332" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A332" s="2">
         <v>45814</v>
       </c>
@@ -10657,7 +10672,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="333" spans="1:19">
+    <row r="333" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A333" s="2">
         <v>45814</v>
       </c>
@@ -10716,7 +10731,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="334" spans="1:19">
+    <row r="334" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A334" s="2">
         <v>45814</v>
       </c>
@@ -10775,7 +10790,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="335" spans="1:19">
+    <row r="335" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A335" s="2">
         <v>45814</v>
       </c>
@@ -10834,7 +10849,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="336" spans="1:19">
+    <row r="336" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A336" s="2">
         <v>45815</v>
       </c>
@@ -10893,7 +10908,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="337" spans="1:19">
+    <row r="337" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A337" s="2">
         <v>45815</v>
       </c>
@@ -10952,7 +10967,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="338" spans="1:19">
+    <row r="338" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A338" s="2">
         <v>45815</v>
       </c>
@@ -11011,7 +11026,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="339" spans="1:19">
+    <row r="339" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A339" s="2">
         <v>45825</v>
       </c>
@@ -11070,7 +11085,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="340" spans="1:19">
+    <row r="340" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A340" s="2">
         <v>45825</v>
       </c>
@@ -11129,7 +11144,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="341" spans="1:19">
+    <row r="341" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A341" s="2">
         <v>45825</v>
       </c>
@@ -11188,7 +11203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="342" spans="1:19">
+    <row r="342" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A342" s="2">
         <v>45825</v>
       </c>
@@ -11247,7 +11262,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="343" spans="1:19">
+    <row r="343" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A343" s="2">
         <v>45826</v>
       </c>
@@ -11306,7 +11321,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="1:19">
+    <row r="344" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A344" s="2">
         <v>45826</v>
       </c>
@@ -11365,7 +11380,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="345" spans="1:19">
+    <row r="345" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A345" s="2">
         <v>45826</v>
       </c>
@@ -11424,7 +11439,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="346" spans="1:19">
+    <row r="346" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A346" s="2">
         <v>45826</v>
       </c>
@@ -11483,7 +11498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="347" spans="1:19">
+    <row r="347" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A347" s="2">
         <v>45833</v>
       </c>
@@ -11542,7 +11557,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="348" spans="1:19">
+    <row r="348" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A348" s="2">
         <v>45833</v>
       </c>
@@ -11601,7 +11616,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="349" spans="1:19">
+    <row r="349" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A349" s="2">
         <v>45833</v>
       </c>
@@ -11660,7 +11675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="350" spans="1:19">
+    <row r="350" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A350" s="2">
         <v>45833</v>
       </c>
@@ -11719,7 +11734,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="351" spans="1:19">
+    <row r="351" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A351" s="2">
         <v>45842</v>
       </c>
@@ -11778,7 +11793,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="352" spans="1:19">
+    <row r="352" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A352" s="2">
         <v>45842</v>
       </c>
@@ -11837,7 +11852,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="353" spans="1:19">
+    <row r="353" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A353" s="2">
         <v>45842</v>
       </c>
@@ -11896,7 +11911,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="354" spans="1:19">
+    <row r="354" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A354" s="2">
         <v>45842</v>
       </c>
@@ -11955,7 +11970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="355" spans="1:19">
+    <row r="355" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A355" s="2">
         <v>45842</v>
       </c>
@@ -12014,7 +12029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="356" spans="1:19">
+    <row r="356" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A356" s="2">
         <v>45848</v>
       </c>
@@ -12073,7 +12088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="357" spans="1:19">
+    <row r="357" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A357" s="2">
         <v>45848</v>
       </c>
@@ -12132,7 +12147,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="358" spans="1:19">
+    <row r="358" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A358" s="2">
         <v>45848</v>
       </c>
@@ -12191,7 +12206,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="359" spans="1:19">
+    <row r="359" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A359" s="2">
         <v>45848</v>
       </c>
@@ -12250,7 +12265,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="360" spans="1:19">
+    <row r="360" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A360" s="2">
         <v>45848</v>
       </c>
@@ -12309,7 +12324,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="361" spans="1:19">
+    <row r="361" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A361" s="2">
         <v>45849</v>
       </c>
@@ -12368,7 +12383,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="362" spans="1:19">
+    <row r="362" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A362" s="2">
         <v>45849</v>
       </c>
@@ -12427,7 +12442,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:19">
+    <row r="363" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A363" s="2">
         <v>45849</v>
       </c>
@@ -12486,7 +12501,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="364" spans="1:19">
+    <row r="364" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A364" s="2">
         <v>45849</v>
       </c>
@@ -12545,7 +12560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="365" spans="1:19">
+    <row r="365" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A365" s="2">
         <v>45849</v>
       </c>
@@ -12604,7 +12619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="366" spans="1:19">
+    <row r="366" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A366" s="2">
         <v>45849</v>
       </c>
@@ -12663,7 +12678,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="367" spans="1:19">
+    <row r="367" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A367" s="2">
         <v>45849</v>
       </c>
@@ -12722,7 +12737,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="368" spans="1:19">
+    <row r="368" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A368" s="2">
         <v>45849</v>
       </c>
@@ -12733,7 +12748,7 @@
         <v>382</v>
       </c>
       <c r="D368">
-        <v>2.55</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="E368">
         <v>36</v>
@@ -12781,7 +12796,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="369" spans="1:19">
+    <row r="369" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A369" s="2">
         <v>45850</v>
       </c>
@@ -12840,7 +12855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="370" spans="1:19">
+    <row r="370" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A370" s="2">
         <v>45850</v>
       </c>
@@ -12899,7 +12914,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="371" spans="1:19">
+    <row r="371" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A371" s="2">
         <v>45850</v>
       </c>
@@ -12958,7 +12973,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="372" spans="1:19">
+    <row r="372" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A372" s="2">
         <v>45850</v>
       </c>
@@ -13017,7 +13032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:19">
+    <row r="373" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A373" s="2">
         <v>45850</v>
       </c>
@@ -13076,7 +13091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:19">
+    <row r="374" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A374" s="2">
         <v>45850</v>
       </c>
@@ -13135,7 +13150,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="375" spans="1:19">
+    <row r="375" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A375" s="2">
         <v>45851</v>
       </c>
@@ -13194,7 +13209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:19">
+    <row r="376" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A376" s="2">
         <v>45851</v>
       </c>
@@ -13253,7 +13268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="377" spans="1:19">
+    <row r="377" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A377" s="2">
         <v>45851</v>
       </c>
@@ -13312,7 +13327,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="378" spans="1:19">
+    <row r="378" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A378" s="2">
         <v>45851</v>
       </c>
@@ -13371,7 +13386,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="379" spans="1:19">
+    <row r="379" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A379" s="2">
         <v>45851</v>
       </c>
@@ -13430,7 +13445,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="380" spans="1:19">
+    <row r="380" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A380" s="2">
         <v>45851</v>
       </c>
@@ -13489,7 +13504,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="381" spans="1:19">
+    <row r="381" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A381" s="2">
         <v>45852</v>
       </c>
@@ -13548,7 +13563,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="382" spans="1:19">
+    <row r="382" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A382" s="2">
         <v>45852</v>
       </c>
@@ -13607,7 +13622,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="383" spans="1:19">
+    <row r="383" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A383" s="2">
         <v>45864</v>
       </c>
@@ -13666,7 +13681,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="384" spans="1:19">
+    <row r="384" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A384" s="2">
         <v>45865</v>
       </c>
@@ -13725,7 +13740,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="385" spans="1:19">
+    <row r="385" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A385" s="2">
         <v>45865</v>
       </c>
@@ -13784,7 +13799,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="386" spans="1:19">
+    <row r="386" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A386" s="2">
         <v>45865</v>
       </c>
@@ -13843,7 +13858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="387" spans="1:19">
+    <row r="387" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A387" s="2">
         <v>45865</v>
       </c>
@@ -13902,7 +13917,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="388" spans="1:19">
+    <row r="388" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A388" s="2">
         <v>45865</v>
       </c>
@@ -13961,7 +13976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:19">
+    <row r="389" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A389" s="2">
         <v>45866</v>
       </c>
@@ -14020,7 +14035,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="390" spans="1:19">
+    <row r="390" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A390" s="2">
         <v>45866</v>
       </c>
@@ -14079,7 +14094,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="391" spans="1:19">
+    <row r="391" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A391" s="2">
         <v>45872</v>
       </c>
@@ -14090,7 +14105,7 @@
         <v>381</v>
       </c>
       <c r="D391">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E391">
         <v>3</v>
@@ -14138,7 +14153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:19">
+    <row r="392" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A392" s="2">
         <v>45872</v>
       </c>
@@ -14197,7 +14212,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="393" spans="1:19">
+    <row r="393" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A393" s="2">
         <v>45872</v>
       </c>
@@ -14256,7 +14271,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="394" spans="1:19">
+    <row r="394" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A394" s="2">
         <v>45872</v>
       </c>
@@ -14315,7 +14330,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="395" spans="1:19">
+    <row r="395" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A395" s="2">
         <v>45872</v>
       </c>
@@ -14374,7 +14389,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="396" spans="1:19">
+    <row r="396" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A396" s="2">
         <v>45872</v>
       </c>
@@ -14385,7 +14400,7 @@
         <v>383</v>
       </c>
       <c r="D396">
-        <v>2.45</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="E396">
         <v>19</v>
@@ -14433,7 +14448,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="397" spans="1:19">
+    <row r="397" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A397" s="2">
         <v>45873</v>
       </c>
@@ -14492,7 +14507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="398" spans="1:19">
+    <row r="398" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A398" s="2">
         <v>45873</v>
       </c>
@@ -14551,7 +14566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="399" spans="1:19">
+    <row r="399" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A399" s="2">
         <v>45873</v>
       </c>
@@ -14610,7 +14625,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="400" spans="1:19">
+    <row r="400" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A400" s="2">
         <v>45873</v>
       </c>
@@ -14669,7 +14684,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="401" spans="1:19">
+    <row r="401" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A401" s="2">
         <v>45875</v>
       </c>
@@ -14728,7 +14743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="402" spans="1:19">
+    <row r="402" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A402" s="2">
         <v>45880</v>
       </c>
@@ -14787,7 +14802,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="403" spans="1:19">
+    <row r="403" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A403" s="2">
         <v>45880</v>
       </c>
@@ -14846,7 +14861,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="404" spans="1:19">
+    <row r="404" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A404" s="2">
         <v>45880</v>
       </c>
@@ -14905,7 +14920,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="405" spans="1:19">
+    <row r="405" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A405" s="2">
         <v>45882</v>
       </c>
@@ -14964,7 +14979,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="406" spans="1:19">
+    <row r="406" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A406" s="2">
         <v>45886</v>
       </c>
@@ -15023,7 +15038,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="407" spans="1:19">
+    <row r="407" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A407" s="2">
         <v>45889</v>
       </c>
@@ -15082,7 +15097,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="408" spans="1:19">
+    <row r="408" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A408" s="2">
         <v>45889</v>
       </c>
@@ -15141,7 +15156,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="409" spans="1:19">
+    <row r="409" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A409" s="2">
         <v>45889</v>
       </c>
@@ -15200,7 +15215,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="410" spans="1:19">
+    <row r="410" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A410" s="2">
         <v>45889</v>
       </c>
@@ -15211,7 +15226,7 @@
         <v>383</v>
       </c>
       <c r="D410">
-        <v>2.18</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="E410">
         <v>18</v>
@@ -15259,7 +15274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:19">
+    <row r="411" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A411" s="2">
         <v>45890</v>
       </c>
@@ -15318,7 +15333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="412" spans="1:19">
+    <row r="412" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A412" s="2">
         <v>45890</v>
       </c>
@@ -15377,7 +15392,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="413" spans="1:19">
+    <row r="413" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A413" s="2">
         <v>45890</v>
       </c>
@@ -15436,7 +15451,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="414" spans="1:19">
+    <row r="414" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A414" s="2">
         <v>45890</v>
       </c>
@@ -15495,7 +15510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:19">
+    <row r="415" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A415" s="2">
         <v>45896</v>
       </c>
@@ -15554,7 +15569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:19">
+    <row r="416" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A416" s="2">
         <v>45903</v>
       </c>
@@ -15613,7 +15628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="417" spans="1:19">
+    <row r="417" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A417" s="2">
         <v>45903</v>
       </c>
@@ -15672,7 +15687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:19">
+    <row r="418" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A418" s="2">
         <v>45903</v>
       </c>
@@ -15731,7 +15746,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="419" spans="1:19">
+    <row r="419" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A419" s="2">
         <v>45903</v>
       </c>
@@ -15790,7 +15805,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="420" spans="1:19">
+    <row r="420" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A420" s="2">
         <v>45903</v>
       </c>
@@ -15849,7 +15864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:19">
+    <row r="421" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A421" s="2">
         <v>45904</v>
       </c>
@@ -15908,7 +15923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:19">
+    <row r="422" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A422" s="2">
         <v>45904</v>
       </c>
@@ -15967,7 +15982,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="423" spans="1:19">
+    <row r="423" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A423" s="2">
         <v>45904</v>
       </c>
@@ -16026,7 +16041,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="424" spans="1:19">
+    <row r="424" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A424" s="2">
         <v>45904</v>
       </c>
@@ -16085,7 +16100,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="425" spans="1:19">
+    <row r="425" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A425" s="2">
         <v>45904</v>
       </c>
@@ -16144,7 +16159,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="426" spans="1:19">
+    <row r="426" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A426" s="2">
         <v>45905</v>
       </c>
@@ -16155,7 +16170,7 @@
         <v>383</v>
       </c>
       <c r="D426">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="E426">
         <v>19</v>
@@ -16203,7 +16218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="427" spans="1:19">
+    <row r="427" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A427" s="2">
         <v>45905</v>
       </c>
@@ -16262,7 +16277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="428" spans="1:19">
+    <row r="428" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A428" s="2">
         <v>45905</v>
       </c>
@@ -16321,7 +16336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="429" spans="1:19">
+    <row r="429" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A429" s="2">
         <v>45905</v>
       </c>
@@ -16380,7 +16395,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:19">
+    <row r="430" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A430" s="2">
         <v>45905</v>
       </c>
@@ -16439,7 +16454,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="431" spans="1:19">
+    <row r="431" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A431" s="2">
         <v>45906</v>
       </c>
@@ -16498,7 +16513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:19">
+    <row r="432" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A432" s="2">
         <v>45906</v>
       </c>
@@ -16557,7 +16572,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="433" spans="1:19">
+    <row r="433" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A433" s="2">
         <v>45910</v>
       </c>
@@ -16568,7 +16583,7 @@
         <v>383</v>
       </c>
       <c r="D433">
-        <v>2.03</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="E433">
         <v>16</v>
@@ -16616,7 +16631,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="434" spans="1:19">
+    <row r="434" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A434" s="2">
         <v>45911</v>
       </c>
@@ -16675,7 +16690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="435" spans="1:19">
+    <row r="435" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A435" s="2">
         <v>45911</v>
       </c>
@@ -16734,7 +16749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="436" spans="1:19">
+    <row r="436" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A436" s="2">
         <v>45911</v>
       </c>
@@ -16793,7 +16808,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="437" spans="1:19">
+    <row r="437" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A437" s="2">
         <v>45911</v>
       </c>
@@ -16852,7 +16867,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="438" spans="1:19">
+    <row r="438" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A438" s="2">
         <v>45911</v>
       </c>
@@ -16911,7 +16926,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="439" spans="1:19">
+    <row r="439" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A439" s="2">
         <v>45911</v>
       </c>
@@ -16970,7 +16985,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="440" spans="1:19">
+    <row r="440" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A440" s="2">
         <v>45912</v>
       </c>
@@ -17029,7 +17044,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="441" spans="1:19">
+    <row r="441" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A441" s="2">
         <v>45912</v>
       </c>
@@ -17088,7 +17103,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="442" spans="1:19">
+    <row r="442" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A442" s="2">
         <v>45912</v>
       </c>
@@ -17147,7 +17162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="443" spans="1:19">
+    <row r="443" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A443" s="2">
         <v>45912</v>
       </c>
@@ -17206,7 +17221,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="444" spans="1:19">
+    <row r="444" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A444" s="2">
         <v>45916</v>
       </c>
@@ -17265,7 +17280,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="445" spans="1:19">
+    <row r="445" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A445" s="2">
         <v>45916</v>
       </c>
@@ -17324,7 +17339,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="446" spans="1:19">
+    <row r="446" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>19</v>
       </c>
@@ -17383,7 +17398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="447" spans="1:19">
+    <row r="447" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>19</v>
       </c>
@@ -17442,7 +17457,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="448" spans="1:19">
+    <row r="448" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>19</v>
       </c>
@@ -17501,7 +17516,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="449" spans="1:19">
+    <row r="449" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>19</v>
       </c>
@@ -17560,7 +17575,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="450" spans="1:19">
+    <row r="450" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>19</v>
       </c>
@@ -17619,7 +17634,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="451" spans="1:19">
+    <row r="451" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>20</v>
       </c>
@@ -17678,7 +17693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:19">
+    <row r="452" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>20</v>
       </c>
@@ -17737,7 +17752,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="453" spans="1:19">
+    <row r="453" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>20</v>
       </c>
@@ -17796,7 +17811,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="454" spans="1:19">
+    <row r="454" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>20</v>
       </c>
@@ -17855,7 +17870,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="455" spans="1:19">
+    <row r="455" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>21</v>
       </c>
@@ -17914,7 +17929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="456" spans="1:19">
+    <row r="456" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>22</v>
       </c>
@@ -17973,7 +17988,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="457" spans="1:19">
+    <row r="457" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>22</v>
       </c>
@@ -18032,7 +18047,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="458" spans="1:19">
+    <row r="458" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>22</v>
       </c>
@@ -18091,7 +18106,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="459" spans="1:19">
+    <row r="459" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>22</v>
       </c>
@@ -18150,7 +18165,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="460" spans="1:19">
+    <row r="460" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>23</v>
       </c>
@@ -18209,7 +18224,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="461" spans="1:19">
+    <row r="461" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>24</v>
       </c>
@@ -18268,7 +18283,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="462" spans="1:19">
+    <row r="462" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>24</v>
       </c>
@@ -18327,7 +18342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="463" spans="1:19">
+    <row r="463" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>24</v>
       </c>
@@ -18386,7 +18401,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="464" spans="1:19">
+    <row r="464" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>24</v>
       </c>
@@ -18445,7 +18460,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="465" spans="1:19">
+    <row r="465" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>25</v>
       </c>
@@ -18504,7 +18519,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="466" spans="1:19">
+    <row r="466" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>26</v>
       </c>
@@ -18563,7 +18578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:19">
+    <row r="467" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>27</v>
       </c>
@@ -18622,7 +18637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:19">
+    <row r="468" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>28</v>
       </c>
@@ -18681,7 +18696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="469" spans="1:19">
+    <row r="469" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>28</v>
       </c>
@@ -18740,7 +18755,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="470" spans="1:19">
+    <row r="470" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>28</v>
       </c>
@@ -18799,7 +18814,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="471" spans="1:19">
+    <row r="471" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>28</v>
       </c>
@@ -18858,7 +18873,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="472" spans="1:19">
+    <row r="472" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>28</v>
       </c>
@@ -18917,7 +18932,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="473" spans="1:19">
+    <row r="473" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>29</v>
       </c>
@@ -18976,7 +18991,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="474" spans="1:19">
+    <row r="474" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>29</v>
       </c>
@@ -19035,7 +19050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="475" spans="1:19">
+    <row r="475" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>29</v>
       </c>
@@ -19094,7 +19109,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="476" spans="1:19">
+    <row r="476" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>29</v>
       </c>
@@ -19153,7 +19168,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="477" spans="1:19">
+    <row r="477" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>30</v>
       </c>
@@ -19212,7 +19227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="478" spans="1:19">
+    <row r="478" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>31</v>
       </c>
@@ -19223,7 +19238,7 @@
         <v>382</v>
       </c>
       <c r="D478">
-        <v>2.51</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="E478">
         <v>32</v>
@@ -19271,7 +19286,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="479" spans="1:19">
+    <row r="479" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>32</v>
       </c>
@@ -19330,7 +19345,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="480" spans="1:19">
+    <row r="480" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>32</v>
       </c>
@@ -19389,7 +19404,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="481" spans="1:19">
+    <row r="481" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>32</v>
       </c>
@@ -19448,7 +19463,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="482" spans="1:19">
+    <row r="482" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>32</v>
       </c>
@@ -19507,7 +19522,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="483" spans="1:19">
+    <row r="483" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>32</v>
       </c>
@@ -19566,7 +19581,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="484" spans="1:19">
+    <row r="484" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>32</v>
       </c>
@@ -19625,7 +19640,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="485" spans="1:19">
+    <row r="485" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>33</v>
       </c>
@@ -19684,7 +19699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:19">
+    <row r="486" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>34</v>
       </c>
@@ -19743,7 +19758,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="487" spans="1:19">
+    <row r="487" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>33</v>
       </c>
@@ -19802,7 +19817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="488" spans="1:19">
+    <row r="488" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>33</v>
       </c>
@@ -19861,7 +19876,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="489" spans="1:19">
+    <row r="489" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>33</v>
       </c>
@@ -19920,7 +19935,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="490" spans="1:19">
+    <row r="490" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>33</v>
       </c>
@@ -19979,7 +19994,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="491" spans="1:19">
+    <row r="491" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>35</v>
       </c>
@@ -20038,7 +20053,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="492" spans="1:19">
+    <row r="492" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>36</v>
       </c>
@@ -20097,7 +20112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:19">
+    <row r="493" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>35</v>
       </c>
@@ -20156,7 +20171,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="494" spans="1:19">
+    <row r="494" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>35</v>
       </c>
@@ -20215,7 +20230,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="495" spans="1:19">
+    <row r="495" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>35</v>
       </c>
@@ -20226,7 +20241,7 @@
         <v>382</v>
       </c>
       <c r="D495">
-        <v>2.55</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="E495">
         <v>35</v>
@@ -20274,7 +20289,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="496" spans="1:19">
+    <row r="496" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>36</v>
       </c>
@@ -20333,7 +20348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:19">
+    <row r="497" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>36</v>
       </c>
@@ -20392,7 +20407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:19">
+    <row r="498" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>36</v>
       </c>
@@ -20451,7 +20466,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="499" spans="1:19">
+    <row r="499" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>36</v>
       </c>
@@ -20510,7 +20525,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="500" spans="1:19">
+    <row r="500" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>36</v>
       </c>
@@ -20569,7 +20584,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="501" spans="1:19">
+    <row r="501" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>37</v>
       </c>
@@ -20628,7 +20643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="502" spans="1:19">
+    <row r="502" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>37</v>
       </c>
@@ -20687,7 +20702,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="503" spans="1:19">
+    <row r="503" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>37</v>
       </c>
@@ -20746,7 +20761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:19">
+    <row r="504" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>38</v>
       </c>
@@ -20805,7 +20820,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="505" spans="1:19">
+    <row r="505" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>38</v>
       </c>
@@ -20864,7 +20879,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="506" spans="1:19">
+    <row r="506" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>38</v>
       </c>
@@ -20923,7 +20938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:19">
+    <row r="507" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>38</v>
       </c>
@@ -20982,7 +20997,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="508" spans="1:19">
+    <row r="508" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>38</v>
       </c>
@@ -21041,7 +21056,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="509" spans="1:19">
+    <row r="509" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>38</v>
       </c>
@@ -21100,7 +21115,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="510" spans="1:19">
+    <row r="510" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>38</v>
       </c>
@@ -21159,7 +21174,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="511" spans="1:19">
+    <row r="511" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>39</v>
       </c>
@@ -21218,7 +21233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:19">
+    <row r="512" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>39</v>
       </c>
@@ -21277,7 +21292,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="513" spans="1:19">
+    <row r="513" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>39</v>
       </c>
@@ -21336,7 +21351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:19">
+    <row r="514" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>40</v>
       </c>
@@ -21395,7 +21410,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="515" spans="1:19">
+    <row r="515" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>40</v>
       </c>
@@ -21454,7 +21469,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="516" spans="1:19">
+    <row r="516" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>40</v>
       </c>
@@ -21465,7 +21480,7 @@
         <v>383</v>
       </c>
       <c r="D516">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="E516">
         <v>26</v>
@@ -21513,7 +21528,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="517" spans="1:19">
+    <row r="517" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>41</v>
       </c>
@@ -21572,7 +21587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="518" spans="1:19">
+    <row r="518" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>42</v>
       </c>
@@ -21631,7 +21646,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="519" spans="1:19">
+    <row r="519" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>42</v>
       </c>
@@ -21690,7 +21705,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="520" spans="1:19">
+    <row r="520" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>42</v>
       </c>
@@ -21749,7 +21764,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="521" spans="1:19">
+    <row r="521" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>42</v>
       </c>
@@ -21808,7 +21823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="522" spans="1:19">
+    <row r="522" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>43</v>
       </c>
@@ -21867,7 +21882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:19">
+    <row r="523" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>43</v>
       </c>
@@ -21926,7 +21941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:19">
+    <row r="524" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>43</v>
       </c>
@@ -21985,7 +22000,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="525" spans="1:19">
+    <row r="525" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>44</v>
       </c>
@@ -22044,7 +22059,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="526" spans="1:19">
+    <row r="526" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>44</v>
       </c>
@@ -22103,7 +22118,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="527" spans="1:19">
+    <row r="527" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>44</v>
       </c>
@@ -22162,7 +22177,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="528" spans="1:19">
+    <row r="528" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>44</v>
       </c>
@@ -22221,7 +22236,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="529" spans="1:19">
+    <row r="529" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>44</v>
       </c>
@@ -22280,7 +22295,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="530" spans="1:19">
+    <row r="530" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>45</v>
       </c>
@@ -22339,7 +22354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="531" spans="1:19">
+    <row r="531" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>45</v>
       </c>
@@ -22398,7 +22413,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="532" spans="1:19">
+    <row r="532" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>45</v>
       </c>
@@ -22457,7 +22472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:19">
+    <row r="533" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>46</v>
       </c>
@@ -22516,7 +22531,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="534" spans="1:19">
+    <row r="534" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>47</v>
       </c>
@@ -22575,7 +22590,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="535" spans="1:19">
+    <row r="535" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>48</v>
       </c>
@@ -22634,7 +22649,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="536" spans="1:19">
+    <row r="536" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>48</v>
       </c>
@@ -22693,7 +22708,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="537" spans="1:19">
+    <row r="537" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>48</v>
       </c>
@@ -22704,7 +22719,7 @@
         <v>381</v>
       </c>
       <c r="D537">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="E537">
         <v>22</v>
@@ -22752,7 +22767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="538" spans="1:19">
+    <row r="538" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>49</v>
       </c>
@@ -22811,7 +22826,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="539" spans="1:19">
+    <row r="539" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>49</v>
       </c>
@@ -22870,7 +22885,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="540" spans="1:19">
+    <row r="540" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>50</v>
       </c>
@@ -22929,7 +22944,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="541" spans="1:19">
+    <row r="541" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>50</v>
       </c>
@@ -22988,7 +23003,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="542" spans="1:19">
+    <row r="542" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>50</v>
       </c>
@@ -23047,7 +23062,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="543" spans="1:19">
+    <row r="543" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>50</v>
       </c>
@@ -23106,7 +23121,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="544" spans="1:19">
+    <row r="544" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>51</v>
       </c>
@@ -23165,7 +23180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:19">
+    <row r="545" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>51</v>
       </c>
@@ -23224,7 +23239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:19">
+    <row r="546" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>51</v>
       </c>
@@ -23283,7 +23298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:19">
+    <row r="547" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>51</v>
       </c>
@@ -23342,7 +23357,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="548" spans="1:19">
+    <row r="548" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>51</v>
       </c>
@@ -23401,7 +23416,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="549" spans="1:19">
+    <row r="549" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>51</v>
       </c>
@@ -23460,7 +23475,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="550" spans="1:19">
+    <row r="550" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>51</v>
       </c>
@@ -23471,7 +23486,7 @@
         <v>382</v>
       </c>
       <c r="D550">
-        <v>2.03</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="E550">
         <v>15</v>
@@ -23519,7 +23534,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="551" spans="1:19">
+    <row r="551" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>52</v>
       </c>
@@ -23578,7 +23593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:19">
+    <row r="552" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>52</v>
       </c>
@@ -23637,7 +23652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:19">
+    <row r="553" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>52</v>
       </c>
@@ -23696,7 +23711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:19">
+    <row r="554" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>52</v>
       </c>
@@ -23755,7 +23770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="555" spans="1:19">
+    <row r="555" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>52</v>
       </c>
@@ -23814,7 +23829,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="556" spans="1:19">
+    <row r="556" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>53</v>
       </c>
@@ -23873,7 +23888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:19">
+    <row r="557" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>53</v>
       </c>
@@ -23932,7 +23947,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="558" spans="1:19">
+    <row r="558" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>53</v>
       </c>
@@ -23991,7 +24006,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="559" spans="1:19">
+    <row r="559" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>54</v>
       </c>
@@ -24002,7 +24017,7 @@
         <v>382</v>
       </c>
       <c r="D559">
-        <v>2.53</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="E559">
         <v>11</v>
@@ -24050,7 +24065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560" spans="1:19">
+    <row r="560" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>55</v>
       </c>
@@ -24109,7 +24124,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="561" spans="1:19">
+    <row r="561" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>55</v>
       </c>
@@ -24168,7 +24183,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="562" spans="1:19">
+    <row r="562" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>55</v>
       </c>
@@ -24227,7 +24242,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="563" spans="1:19">
+    <row r="563" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>55</v>
       </c>
@@ -24286,7 +24301,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="564" spans="1:19">
+    <row r="564" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>56</v>
       </c>
@@ -24345,7 +24360,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="565" spans="1:19">
+    <row r="565" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>56</v>
       </c>
@@ -24404,7 +24419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="566" spans="1:19">
+    <row r="566" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>56</v>
       </c>
@@ -24463,7 +24478,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="567" spans="1:19">
+    <row r="567" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>38</v>
       </c>
@@ -24522,7 +24537,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="568" spans="1:19">
+    <row r="568" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>56</v>
       </c>
@@ -24581,7 +24596,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="569" spans="1:19">
+    <row r="569" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>57</v>
       </c>
@@ -24640,7 +24655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:19">
+    <row r="570" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>58</v>
       </c>
@@ -24699,7 +24714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:19">
+    <row r="571" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>59</v>
       </c>
@@ -24758,7 +24773,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="572" spans="1:19">
+    <row r="572" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>59</v>
       </c>
@@ -24817,7 +24832,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="573" spans="1:19">
+    <row r="573" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>59</v>
       </c>
@@ -24876,7 +24891,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="574" spans="1:19">
+    <row r="574" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>60</v>
       </c>
@@ -24935,7 +24950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:19">
+    <row r="575" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>60</v>
       </c>
@@ -24994,7 +25009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="576" spans="1:19">
+    <row r="576" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>60</v>
       </c>
@@ -25053,7 +25068,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="577" spans="1:19">
+    <row r="577" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>60</v>
       </c>
@@ -25112,7 +25127,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="578" spans="1:19">
+    <row r="578" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>60</v>
       </c>
@@ -25171,7 +25186,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="579" spans="1:19">
+    <row r="579" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>60</v>
       </c>
@@ -25230,7 +25245,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="580" spans="1:19">
+    <row r="580" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>60</v>
       </c>
@@ -25241,7 +25256,7 @@
         <v>382</v>
       </c>
       <c r="D580">
-        <v>2.03</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="E580">
         <v>18</v>
@@ -25289,7 +25304,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="581" spans="1:19">
+    <row r="581" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>61</v>
       </c>
@@ -25348,7 +25363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:19">
+    <row r="582" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>61</v>
       </c>
@@ -25407,7 +25422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583" spans="1:19">
+    <row r="583" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>61</v>
       </c>
@@ -25466,7 +25481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:19">
+    <row r="584" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>61</v>
       </c>
@@ -25525,7 +25540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:19">
+    <row r="585" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>61</v>
       </c>
@@ -25584,7 +25599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="586" spans="1:19">
+    <row r="586" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>61</v>
       </c>
@@ -25643,7 +25658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="587" spans="1:19">
+    <row r="587" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>62</v>
       </c>
@@ -25702,7 +25717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="588" spans="1:19">
+    <row r="588" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>62</v>
       </c>
@@ -25761,7 +25776,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="589" spans="1:19">
+    <row r="589" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>62</v>
       </c>
@@ -25820,7 +25835,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="590" spans="1:19">
+    <row r="590" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>62</v>
       </c>
@@ -25879,7 +25894,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="591" spans="1:19">
+    <row r="591" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>62</v>
       </c>
@@ -25938,7 +25953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:19">
+    <row r="592" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>63</v>
       </c>
@@ -25997,7 +26012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:19">
+    <row r="593" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>63</v>
       </c>
@@ -26056,7 +26071,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="594" spans="1:19">
+    <row r="594" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>63</v>
       </c>
@@ -26115,7 +26130,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="595" spans="1:19">
+    <row r="595" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>63</v>
       </c>
@@ -26174,7 +26189,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="596" spans="1:19">
+    <row r="596" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>63</v>
       </c>
@@ -26233,7 +26248,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="597" spans="1:19">
+    <row r="597" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>63</v>
       </c>
@@ -26292,7 +26307,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="598" spans="1:19">
+    <row r="598" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>64</v>
       </c>
@@ -26351,7 +26366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="599" spans="1:19">
+    <row r="599" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>64</v>
       </c>
@@ -26410,7 +26425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:19">
+    <row r="600" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>64</v>
       </c>
@@ -26469,7 +26484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:19">
+    <row r="601" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>65</v>
       </c>
@@ -26528,7 +26543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:19">
+    <row r="602" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>66</v>
       </c>
@@ -26587,7 +26602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="603" spans="1:19">
+    <row r="603" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>66</v>
       </c>
@@ -26646,7 +26661,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="604" spans="1:19">
+    <row r="604" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>66</v>
       </c>
@@ -26705,7 +26720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="605" spans="1:19">
+    <row r="605" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>66</v>
       </c>
@@ -26764,7 +26779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="606" spans="1:19">
+    <row r="606" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>66</v>
       </c>
@@ -26775,7 +26790,7 @@
         <v>380</v>
       </c>
       <c r="D606">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E606">
         <v>11</v>
@@ -26823,7 +26838,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="607" spans="1:19">
+    <row r="607" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>67</v>
       </c>
@@ -26882,7 +26897,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="608" spans="1:19">
+    <row r="608" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>67</v>
       </c>
@@ -26941,7 +26956,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="609" spans="1:19">
+    <row r="609" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>67</v>
       </c>
@@ -27000,7 +27015,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="610" spans="1:19">
+    <row r="610" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>68</v>
       </c>
@@ -27059,7 +27074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="611" spans="1:19">
+    <row r="611" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>68</v>
       </c>
@@ -27118,7 +27133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:19">
+    <row r="612" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>68</v>
       </c>
@@ -27177,7 +27192,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="613" spans="1:19">
+    <row r="613" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>66</v>
       </c>
@@ -27236,7 +27251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="614" spans="1:19">
+    <row r="614" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>69</v>
       </c>
@@ -27295,7 +27310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="615" spans="1:19">
+    <row r="615" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>69</v>
       </c>
@@ -27354,7 +27369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:19">
+    <row r="616" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>70</v>
       </c>
@@ -27413,7 +27428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="617" spans="1:19">
+    <row r="617" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>70</v>
       </c>
@@ -27472,7 +27487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:19">
+    <row r="618" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>71</v>
       </c>
@@ -27531,7 +27546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:19">
+    <row r="619" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>72</v>
       </c>
@@ -27590,7 +27605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="620" spans="1:19">
+    <row r="620" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>73</v>
       </c>
@@ -27649,7 +27664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:19">
+    <row r="621" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>74</v>
       </c>
@@ -27708,7 +27723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="622" spans="1:19">
+    <row r="622" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>75</v>
       </c>
@@ -27767,7 +27782,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="623" spans="1:19">
+    <row r="623" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>76</v>
       </c>

--- a/data/harvesting_records.xlsx
+++ b/data/harvesting_records.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5563" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6705" uniqueCount="647">
   <si>
     <t>Date</t>
   </si>
@@ -1772,6 +1772,195 @@
   <si>
     <t>2023/24</t>
   </si>
+  <si>
+    <t>2023-06-30</t>
+  </si>
+  <si>
+    <t>2023-07-8</t>
+  </si>
+  <si>
+    <t>2023-07-14</t>
+  </si>
+  <si>
+    <t>2023-07-18</t>
+  </si>
+  <si>
+    <t>2023-09-24</t>
+  </si>
+  <si>
+    <t>2023-11-7</t>
+  </si>
+  <si>
+    <t>2023-10-5</t>
+  </si>
+  <si>
+    <t>2023-09-23</t>
+  </si>
+  <si>
+    <t>2023-06-11</t>
+  </si>
+  <si>
+    <t>2023-09-19</t>
+  </si>
+  <si>
+    <t>2023-09-17</t>
+  </si>
+  <si>
+    <t>2023-09-21</t>
+  </si>
+  <si>
+    <t>2023-09-25</t>
+  </si>
+  <si>
+    <t>2023-09-22</t>
+  </si>
+  <si>
+    <t>2023-10-17</t>
+  </si>
+  <si>
+    <t>2023-08-10</t>
+  </si>
+  <si>
+    <t>2023-05-15</t>
+  </si>
+  <si>
+    <t>2023-08-19</t>
+  </si>
+  <si>
+    <t>2023-05-21</t>
+  </si>
+  <si>
+    <t>2023-08-26</t>
+  </si>
+  <si>
+    <t>2023-10-1</t>
+  </si>
+  <si>
+    <t>2023-11-9</t>
+  </si>
+  <si>
+    <t>2023-10-23</t>
+  </si>
+  <si>
+    <t>2023-10-8</t>
+  </si>
+  <si>
+    <t>2023-06-17</t>
+  </si>
+  <si>
+    <t>2023-11-10</t>
+  </si>
+  <si>
+    <t>2023-09-12</t>
+  </si>
+  <si>
+    <t>2023-07-26</t>
+  </si>
+  <si>
+    <t>2023-09-7</t>
+  </si>
+  <si>
+    <t>2023-05-5</t>
+  </si>
+  <si>
+    <t>2023-10-13</t>
+  </si>
+  <si>
+    <t>2023-05-10</t>
+  </si>
+  <si>
+    <t>2023-06-22</t>
+  </si>
+  <si>
+    <t>2023-07-19</t>
+  </si>
+  <si>
+    <t>2023-06-7</t>
+  </si>
+  <si>
+    <t>2023-10-29</t>
+  </si>
+  <si>
+    <t>2023-08-7</t>
+  </si>
+  <si>
+    <t>2023-06-26</t>
+  </si>
+  <si>
+    <t>2023-11-15</t>
+  </si>
+  <si>
+    <t>2023-11-4</t>
+  </si>
+  <si>
+    <t>2023-08-29</t>
+  </si>
+  <si>
+    <t>2023-08-5</t>
+  </si>
+  <si>
+    <t>2023-08-8</t>
+  </si>
+  <si>
+    <t>2023-10-4</t>
+  </si>
+  <si>
+    <t>2023-10-6</t>
+  </si>
+  <si>
+    <t>2023-08-12</t>
+  </si>
+  <si>
+    <t>2023-09-29</t>
+  </si>
+  <si>
+    <t>2023-09-28</t>
+  </si>
+  <si>
+    <t>2023-10-3</t>
+  </si>
+  <si>
+    <t>2023-09-1</t>
+  </si>
+  <si>
+    <t>2023-08-22</t>
+  </si>
+  <si>
+    <t>2023-09-5</t>
+  </si>
+  <si>
+    <t>2023-09-3</t>
+  </si>
+  <si>
+    <t>2023-09-9</t>
+  </si>
+  <si>
+    <t>2023-09-13</t>
+  </si>
+  <si>
+    <t>2023-09-15</t>
+  </si>
+  <si>
+    <t>2023-07-12</t>
+  </si>
+  <si>
+    <t>2023-08-1</t>
+  </si>
+  <si>
+    <t>2023-07-22</t>
+  </si>
+  <si>
+    <t>2023-07-10</t>
+  </si>
+  <si>
+    <t>2023-08-6</t>
+  </si>
+  <si>
+    <t>2023-06-18</t>
+  </si>
+  <si>
+    <t>2023-07-29</t>
+  </si>
 </sst>
 </file>
 
@@ -2144,7 +2333,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S1503"/>
+  <dimension ref="A1:S1784"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -59660,32 +59849,6603 @@
       </c>
     </row>
     <row r="1498" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1498" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1498" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1498" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1498">
+        <v>3.008</v>
+      </c>
+      <c r="E1498">
+        <v>51</v>
+      </c>
+      <c r="F1498">
+        <v>306</v>
+      </c>
       <c r="H1498" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="1499" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1499" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1499" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1499" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1499">
+        <v>3.0870000000000002</v>
+      </c>
+      <c r="E1499">
+        <v>41</v>
+      </c>
+      <c r="F1499">
+        <v>246</v>
+      </c>
       <c r="H1499" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="1500" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1500" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1500" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1500" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1500">
+        <v>3.0419999999999998</v>
+      </c>
+      <c r="E1500">
+        <v>39</v>
+      </c>
+      <c r="F1500">
+        <v>234</v>
+      </c>
       <c r="H1500" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="1501" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1501" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1501" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1501" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1501">
+        <v>3.0219999999999998</v>
+      </c>
+      <c r="E1501">
+        <v>54</v>
+      </c>
+      <c r="F1501">
+        <v>324</v>
+      </c>
       <c r="H1501" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="1502" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1502" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1502" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1502" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1502">
+        <v>3.0419999999999998</v>
+      </c>
+      <c r="E1502">
+        <v>47</v>
+      </c>
+      <c r="F1502">
+        <v>282</v>
+      </c>
       <c r="H1502" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="1503" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1503" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1503" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1503" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1503">
+        <v>3.04</v>
+      </c>
+      <c r="E1503">
+        <v>42</v>
+      </c>
+      <c r="F1503">
+        <v>252</v>
+      </c>
       <c r="H1503" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1504" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1504" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1504" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1504">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="E1504">
+        <v>21</v>
+      </c>
+      <c r="F1504">
+        <v>126</v>
+      </c>
+      <c r="H1504" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1505" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1505" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1505" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1505">
+        <v>3.0539999999999998</v>
+      </c>
+      <c r="E1505">
+        <v>42</v>
+      </c>
+      <c r="F1505">
+        <v>252</v>
+      </c>
+      <c r="H1505" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1506" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1506" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1506" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1506">
+        <v>3.0310000000000001</v>
+      </c>
+      <c r="E1506">
+        <v>35</v>
+      </c>
+      <c r="F1506">
+        <v>210</v>
+      </c>
+      <c r="H1506" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1507" t="s">
+        <v>588</v>
+      </c>
+      <c r="B1507" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1507" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1507">
+        <v>3.05</v>
+      </c>
+      <c r="E1507">
+        <v>29</v>
+      </c>
+      <c r="F1507">
+        <v>174</v>
+      </c>
+      <c r="H1507" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1508" t="s">
+        <v>589</v>
+      </c>
+      <c r="B1508" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1508" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1508">
+        <v>3.02</v>
+      </c>
+      <c r="E1508">
+        <v>23</v>
+      </c>
+      <c r="F1508">
+        <v>138</v>
+      </c>
+      <c r="H1508" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1509" t="s">
+        <v>589</v>
+      </c>
+      <c r="B1509" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1509" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1509">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="E1509">
+        <v>49</v>
+      </c>
+      <c r="F1509">
+        <v>294</v>
+      </c>
+      <c r="H1509" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1510" t="s">
+        <v>590</v>
+      </c>
+      <c r="B1510" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1510" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1510">
+        <v>1.3049999999999999</v>
+      </c>
+      <c r="E1510">
+        <v>6</v>
+      </c>
+      <c r="F1510">
+        <v>36</v>
+      </c>
+      <c r="H1510" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1511" t="s">
+        <v>591</v>
+      </c>
+      <c r="B1511" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1511" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1511">
+        <v>3.093</v>
+      </c>
+      <c r="E1511">
+        <v>19</v>
+      </c>
+      <c r="F1511">
+        <v>114</v>
+      </c>
+      <c r="H1511" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1512" t="s">
+        <v>591</v>
+      </c>
+      <c r="B1512" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1512" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1512">
+        <v>3.0640000000000001</v>
+      </c>
+      <c r="E1512">
+        <v>33</v>
+      </c>
+      <c r="F1512">
+        <v>198</v>
+      </c>
+      <c r="H1512" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1513" t="s">
+        <v>591</v>
+      </c>
+      <c r="B1513" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1513" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1513">
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="E1513">
+        <v>10</v>
+      </c>
+      <c r="F1513">
+        <v>60</v>
+      </c>
+      <c r="H1513" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1514" t="s">
+        <v>590</v>
+      </c>
+      <c r="B1514" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1514" t="s">
+        <v>445</v>
+      </c>
+      <c r="D1514">
+        <v>3.0230000000000001</v>
+      </c>
+      <c r="E1514">
+        <v>35</v>
+      </c>
+      <c r="F1514">
+        <v>210</v>
+      </c>
+      <c r="H1514" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1515" t="s">
+        <v>590</v>
+      </c>
+      <c r="B1515" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1515" t="s">
+        <v>445</v>
+      </c>
+      <c r="D1515">
+        <v>3.0390000000000001</v>
+      </c>
+      <c r="E1515">
+        <v>33</v>
+      </c>
+      <c r="F1515">
+        <v>198</v>
+      </c>
+      <c r="H1515" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1516" t="s">
+        <v>590</v>
+      </c>
+      <c r="B1516" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1516" t="s">
+        <v>445</v>
+      </c>
+      <c r="D1516">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="E1516">
+        <v>31</v>
+      </c>
+      <c r="F1516">
+        <v>186</v>
+      </c>
+      <c r="H1516" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1517" t="s">
+        <v>590</v>
+      </c>
+      <c r="B1517" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1517" t="s">
+        <v>445</v>
+      </c>
+      <c r="D1517">
+        <v>3.0369999999999999</v>
+      </c>
+      <c r="E1517">
+        <v>31</v>
+      </c>
+      <c r="F1517">
+        <v>186</v>
+      </c>
+      <c r="H1517" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1518" t="s">
+        <v>590</v>
+      </c>
+      <c r="B1518" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1518" t="s">
+        <v>445</v>
+      </c>
+      <c r="D1518">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="E1518">
+        <v>32</v>
+      </c>
+      <c r="F1518">
+        <v>192</v>
+      </c>
+      <c r="H1518" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1519" t="s">
+        <v>590</v>
+      </c>
+      <c r="B1519" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1519" t="s">
+        <v>445</v>
+      </c>
+      <c r="D1519">
+        <v>1.7269999999999999</v>
+      </c>
+      <c r="E1519">
+        <v>22</v>
+      </c>
+      <c r="F1519">
+        <v>132</v>
+      </c>
+      <c r="H1519" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1520" t="s">
+        <v>592</v>
+      </c>
+      <c r="B1520" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1520" t="s">
+        <v>446</v>
+      </c>
+      <c r="D1520">
+        <v>3.0310000000000001</v>
+      </c>
+      <c r="E1520">
+        <v>25</v>
+      </c>
+      <c r="F1520">
+        <v>150</v>
+      </c>
+      <c r="H1520" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1521" t="s">
+        <v>592</v>
+      </c>
+      <c r="B1521" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1521" t="s">
+        <v>446</v>
+      </c>
+      <c r="D1521">
+        <v>3.04</v>
+      </c>
+      <c r="E1521">
+        <v>26</v>
+      </c>
+      <c r="F1521">
+        <v>156</v>
+      </c>
+      <c r="H1521" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1522" t="s">
+        <v>592</v>
+      </c>
+      <c r="B1522" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1522" t="s">
+        <v>446</v>
+      </c>
+      <c r="D1522">
+        <v>3.0310000000000001</v>
+      </c>
+      <c r="E1522">
+        <v>27</v>
+      </c>
+      <c r="F1522">
+        <v>162</v>
+      </c>
+      <c r="H1522" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1523" t="s">
+        <v>592</v>
+      </c>
+      <c r="B1523" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1523" t="s">
+        <v>446</v>
+      </c>
+      <c r="D1523">
+        <v>3.0190000000000001</v>
+      </c>
+      <c r="E1523">
+        <v>26</v>
+      </c>
+      <c r="F1523">
+        <v>156</v>
+      </c>
+      <c r="H1523" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1524" t="s">
+        <v>592</v>
+      </c>
+      <c r="B1524" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1524" t="s">
+        <v>446</v>
+      </c>
+      <c r="D1524">
+        <v>3.0139999999999998</v>
+      </c>
+      <c r="E1524">
+        <v>26</v>
+      </c>
+      <c r="F1524">
+        <v>156</v>
+      </c>
+      <c r="H1524" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1525" t="s">
+        <v>592</v>
+      </c>
+      <c r="B1525" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1525" t="s">
+        <v>446</v>
+      </c>
+      <c r="D1525">
+        <v>0.56200000000000006</v>
+      </c>
+      <c r="E1525">
+        <v>8</v>
+      </c>
+      <c r="F1525">
+        <v>48</v>
+      </c>
+      <c r="H1525" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1526" t="s">
+        <v>585</v>
+      </c>
+      <c r="B1526" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1526" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1526">
+        <v>3.024</v>
+      </c>
+      <c r="E1526">
+        <v>31</v>
+      </c>
+      <c r="F1526">
+        <v>186</v>
+      </c>
+      <c r="H1526" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1527" t="s">
+        <v>585</v>
+      </c>
+      <c r="B1527" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1527" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1527">
+        <v>3.0230000000000001</v>
+      </c>
+      <c r="E1527">
+        <v>32</v>
+      </c>
+      <c r="F1527">
+        <v>192</v>
+      </c>
+      <c r="H1527" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1528" t="s">
+        <v>585</v>
+      </c>
+      <c r="B1528" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1528" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1528">
+        <v>3.008</v>
+      </c>
+      <c r="E1528">
+        <v>31</v>
+      </c>
+      <c r="F1528">
+        <v>186</v>
+      </c>
+      <c r="H1528" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1529" t="s">
+        <v>585</v>
+      </c>
+      <c r="B1529" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1529" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1529">
+        <v>3.0329999999999999</v>
+      </c>
+      <c r="E1529">
+        <v>31</v>
+      </c>
+      <c r="F1529">
+        <v>186</v>
+      </c>
+      <c r="H1529" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1530" t="s">
+        <v>585</v>
+      </c>
+      <c r="B1530" t="s">
+        <v>157</v>
+      </c>
+      <c r="C1530" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1530">
+        <v>3.0139999999999998</v>
+      </c>
+      <c r="E1530">
+        <v>33</v>
+      </c>
+      <c r="F1530">
+        <v>198</v>
+      </c>
+      <c r="H1530" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1531" t="s">
+        <v>585</v>
+      </c>
+      <c r="B1531" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1531" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1531">
+        <v>3.0070000000000001</v>
+      </c>
+      <c r="E1531">
+        <v>40</v>
+      </c>
+      <c r="F1531">
+        <v>240</v>
+      </c>
+      <c r="H1531" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1532" t="s">
+        <v>585</v>
+      </c>
+      <c r="B1532" t="s">
+        <v>417</v>
+      </c>
+      <c r="C1532" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1532">
+        <v>0.78600000000000003</v>
+      </c>
+      <c r="E1532">
+        <v>14</v>
+      </c>
+      <c r="F1532">
+        <v>84</v>
+      </c>
+      <c r="H1532" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1533" t="s">
+        <v>586</v>
+      </c>
+      <c r="B1533" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1533" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1533">
+        <v>3.081</v>
+      </c>
+      <c r="E1533">
+        <v>34</v>
+      </c>
+      <c r="F1533">
+        <v>204</v>
+      </c>
+      <c r="H1533" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1534" t="s">
+        <v>586</v>
+      </c>
+      <c r="B1534" t="s">
+        <v>160</v>
+      </c>
+      <c r="C1534" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1534">
+        <v>3.0470000000000002</v>
+      </c>
+      <c r="E1534">
+        <v>35</v>
+      </c>
+      <c r="F1534">
+        <v>210</v>
+      </c>
+      <c r="H1534" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1535" t="s">
+        <v>586</v>
+      </c>
+      <c r="B1535" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1535" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1535">
+        <v>3.048</v>
+      </c>
+      <c r="E1535">
+        <v>35</v>
+      </c>
+      <c r="F1535">
+        <v>210</v>
+      </c>
+      <c r="H1535" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1536" t="s">
+        <v>586</v>
+      </c>
+      <c r="B1536" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1536" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1536">
+        <v>3.0470000000000002</v>
+      </c>
+      <c r="E1536">
+        <v>34</v>
+      </c>
+      <c r="F1536">
+        <v>204</v>
+      </c>
+      <c r="H1536" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1537" t="s">
+        <v>586</v>
+      </c>
+      <c r="B1537" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1537" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1537">
+        <v>3.0459999999999998</v>
+      </c>
+      <c r="E1537">
+        <v>35</v>
+      </c>
+      <c r="F1537">
+        <v>210</v>
+      </c>
+      <c r="H1537" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1538" t="s">
+        <v>586</v>
+      </c>
+      <c r="B1538" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1538" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1538">
+        <v>2.3359999999999999</v>
+      </c>
+      <c r="E1538">
+        <v>26</v>
+      </c>
+      <c r="F1538">
+        <v>156</v>
+      </c>
+      <c r="H1538" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1539" t="s">
+        <v>598</v>
+      </c>
+      <c r="B1539" t="s">
+        <v>165</v>
+      </c>
+      <c r="C1539" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1539">
+        <v>3.0230000000000001</v>
+      </c>
+      <c r="E1539">
+        <v>28</v>
+      </c>
+      <c r="F1539">
+        <v>168</v>
+      </c>
+      <c r="H1539" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1540" t="s">
+        <v>598</v>
+      </c>
+      <c r="B1540" t="s">
+        <v>166</v>
+      </c>
+      <c r="C1540" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1540">
+        <v>3.0379999999999998</v>
+      </c>
+      <c r="E1540">
+        <v>28</v>
+      </c>
+      <c r="F1540">
+        <v>168</v>
+      </c>
+      <c r="H1540" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1541" t="s">
+        <v>598</v>
+      </c>
+      <c r="B1541" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1541" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1541">
+        <v>3.0379999999999998</v>
+      </c>
+      <c r="E1541">
+        <v>27</v>
+      </c>
+      <c r="F1541">
+        <v>162</v>
+      </c>
+      <c r="H1541" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1542" t="s">
+        <v>598</v>
+      </c>
+      <c r="B1542" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1542" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1542">
+        <v>3.0390000000000001</v>
+      </c>
+      <c r="E1542">
+        <v>28</v>
+      </c>
+      <c r="F1542">
+        <v>168</v>
+      </c>
+      <c r="H1542" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1543" t="s">
+        <v>598</v>
+      </c>
+      <c r="B1543" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1543" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1543">
+        <v>3.02</v>
+      </c>
+      <c r="E1543">
+        <v>27</v>
+      </c>
+      <c r="F1543">
+        <v>162</v>
+      </c>
+      <c r="H1543" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1544" t="s">
+        <v>598</v>
+      </c>
+      <c r="B1544" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1544" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1544">
+        <v>2.3460000000000001</v>
+      </c>
+      <c r="E1544">
+        <v>26</v>
+      </c>
+      <c r="F1544">
+        <v>156</v>
+      </c>
+      <c r="H1544" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1545" t="s">
+        <v>598</v>
+      </c>
+      <c r="B1545" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1545" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1545">
+        <v>3.0659999999999998</v>
+      </c>
+      <c r="E1545">
+        <v>31</v>
+      </c>
+      <c r="F1545">
+        <v>186</v>
+      </c>
+      <c r="H1545" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1546" t="s">
+        <v>598</v>
+      </c>
+      <c r="B1546" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1546" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1546">
+        <v>3.0779999999999998</v>
+      </c>
+      <c r="E1546">
+        <v>36</v>
+      </c>
+      <c r="F1546">
+        <v>216</v>
+      </c>
+      <c r="H1546" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1547" t="s">
+        <v>598</v>
+      </c>
+      <c r="B1547" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1547" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1547">
+        <v>3.0739999999999998</v>
+      </c>
+      <c r="E1547">
+        <v>33</v>
+      </c>
+      <c r="F1547">
+        <v>198</v>
+      </c>
+      <c r="H1547" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1548" t="s">
+        <v>598</v>
+      </c>
+      <c r="B1548" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1548" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1548">
+        <v>3.0939999999999999</v>
+      </c>
+      <c r="E1548">
+        <v>29</v>
+      </c>
+      <c r="F1548">
+        <v>174</v>
+      </c>
+      <c r="H1548" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1549" t="s">
+        <v>598</v>
+      </c>
+      <c r="B1549" t="s">
+        <v>175</v>
+      </c>
+      <c r="C1549" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1549">
+        <v>1.89</v>
+      </c>
+      <c r="E1549">
+        <v>22</v>
+      </c>
+      <c r="F1549">
+        <v>132</v>
+      </c>
+      <c r="H1549" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1550" t="s">
+        <v>599</v>
+      </c>
+      <c r="B1550" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1550" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1550">
+        <v>3.077</v>
+      </c>
+      <c r="E1550">
+        <v>33</v>
+      </c>
+      <c r="F1550">
+        <v>198</v>
+      </c>
+      <c r="H1550" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1551" t="s">
+        <v>599</v>
+      </c>
+      <c r="B1551" t="s">
+        <v>276</v>
+      </c>
+      <c r="C1551" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1551">
+        <v>3.024</v>
+      </c>
+      <c r="E1551">
+        <v>27</v>
+      </c>
+      <c r="F1551">
+        <v>162</v>
+      </c>
+      <c r="H1551" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1552" t="s">
+        <v>599</v>
+      </c>
+      <c r="B1552" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1552" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1552">
+        <v>3.0779999999999998</v>
+      </c>
+      <c r="E1552">
+        <v>29</v>
+      </c>
+      <c r="F1552">
+        <v>174</v>
+      </c>
+      <c r="H1552" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1553" t="s">
+        <v>587</v>
+      </c>
+      <c r="B1553" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1553" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1553">
+        <v>3.1019999999999999</v>
+      </c>
+      <c r="E1553">
+        <v>34</v>
+      </c>
+      <c r="F1553">
+        <v>204</v>
+      </c>
+      <c r="H1553" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1554" t="s">
+        <v>587</v>
+      </c>
+      <c r="B1554" t="s">
+        <v>279</v>
+      </c>
+      <c r="C1554" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1554">
+        <v>3.0939999999999999</v>
+      </c>
+      <c r="E1554">
+        <v>35</v>
+      </c>
+      <c r="F1554">
+        <v>210</v>
+      </c>
+      <c r="H1554" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1555" t="s">
+        <v>587</v>
+      </c>
+      <c r="B1555" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1555" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1555">
+        <v>3.1070000000000002</v>
+      </c>
+      <c r="E1555">
+        <v>34</v>
+      </c>
+      <c r="F1555">
+        <v>204</v>
+      </c>
+      <c r="H1555" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1556" t="s">
+        <v>587</v>
+      </c>
+      <c r="B1556" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1556" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1556">
+        <v>3.3980000000000001</v>
+      </c>
+      <c r="E1556">
+        <v>40</v>
+      </c>
+      <c r="F1556">
+        <v>240</v>
+      </c>
+      <c r="H1556" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1557" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1557" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1557" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1557">
+        <v>3.056</v>
+      </c>
+      <c r="E1557">
+        <v>35</v>
+      </c>
+      <c r="F1557">
+        <v>210</v>
+      </c>
+      <c r="H1557" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1558" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1558" t="s">
+        <v>283</v>
+      </c>
+      <c r="C1558" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1558">
+        <v>3.0739999999999998</v>
+      </c>
+      <c r="E1558">
+        <v>34</v>
+      </c>
+      <c r="F1558">
+        <v>204</v>
+      </c>
+      <c r="H1558" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1559" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1559" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1559" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1559">
+        <v>3.0369999999999999</v>
+      </c>
+      <c r="E1559">
+        <v>33</v>
+      </c>
+      <c r="F1559">
+        <v>198</v>
+      </c>
+      <c r="H1559" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1560" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1560" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1560" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1560">
+        <v>1.4790000000000001</v>
+      </c>
+      <c r="E1560">
+        <v>17</v>
+      </c>
+      <c r="F1560">
+        <v>102</v>
+      </c>
+      <c r="H1560" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1561" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1561" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1561" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1561">
+        <v>3.0960000000000001</v>
+      </c>
+      <c r="E1561">
+        <v>27</v>
+      </c>
+      <c r="F1561">
+        <v>162</v>
+      </c>
+      <c r="H1561" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1562" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1562" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1562" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1562">
+        <v>3.0840000000000001</v>
+      </c>
+      <c r="E1562">
+        <v>26</v>
+      </c>
+      <c r="F1562">
+        <v>156</v>
+      </c>
+      <c r="H1562" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1563" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1563" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1563" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1563">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="E1563">
+        <v>25</v>
+      </c>
+      <c r="F1563">
+        <v>150</v>
+      </c>
+      <c r="H1563" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1564" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1564" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1564" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1564">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="E1564">
+        <v>24</v>
+      </c>
+      <c r="F1564">
+        <v>144</v>
+      </c>
+      <c r="H1564" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1565" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1565" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1565" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1565">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="E1565">
+        <v>28</v>
+      </c>
+      <c r="F1565">
+        <v>168</v>
+      </c>
+      <c r="H1565" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1566" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1566" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1566" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1566">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="E1566">
+        <v>25</v>
+      </c>
+      <c r="F1566">
+        <v>150</v>
+      </c>
+      <c r="H1566" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1567" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1567" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1567" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1567">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="E1567">
+        <v>25</v>
+      </c>
+      <c r="F1567">
+        <v>150</v>
+      </c>
+      <c r="H1567" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1568" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1568" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1568" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1568">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="E1568">
+        <v>28</v>
+      </c>
+      <c r="F1568">
+        <v>168</v>
+      </c>
+      <c r="H1568" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1569" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1569" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1569" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1569">
+        <v>3.1030000000000002</v>
+      </c>
+      <c r="E1569">
+        <v>27</v>
+      </c>
+      <c r="F1569">
+        <v>162</v>
+      </c>
+      <c r="H1569" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1570" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1570" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1570" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1570">
+        <v>3.036</v>
+      </c>
+      <c r="E1570">
+        <v>41</v>
+      </c>
+      <c r="F1570">
+        <v>246</v>
+      </c>
+      <c r="H1570" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1571" t="s">
+        <v>600</v>
+      </c>
+      <c r="B1571" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1571" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1571">
+        <v>0.45</v>
+      </c>
+      <c r="E1571">
+        <v>6</v>
+      </c>
+      <c r="F1571">
+        <v>36</v>
+      </c>
+      <c r="H1571" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1572" t="s">
+        <v>601</v>
+      </c>
+      <c r="B1572" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1572" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1572">
+        <v>3.1230000000000002</v>
+      </c>
+      <c r="E1572">
+        <v>36</v>
+      </c>
+      <c r="F1572">
+        <v>216</v>
+      </c>
+      <c r="H1572" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1573" t="s">
+        <v>601</v>
+      </c>
+      <c r="B1573" t="s">
+        <v>298</v>
+      </c>
+      <c r="C1573" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1573">
+        <v>3.1219999999999999</v>
+      </c>
+      <c r="E1573">
+        <v>40</v>
+      </c>
+      <c r="F1573">
+        <v>240</v>
+      </c>
+      <c r="H1573" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1574" t="s">
+        <v>601</v>
+      </c>
+      <c r="B1574" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1574" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1574">
+        <v>3.145</v>
+      </c>
+      <c r="E1574">
+        <v>38</v>
+      </c>
+      <c r="F1574">
+        <v>228</v>
+      </c>
+      <c r="H1574" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1575" t="s">
+        <v>601</v>
+      </c>
+      <c r="B1575" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1575" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1575">
+        <v>3.14</v>
+      </c>
+      <c r="E1575">
+        <v>38</v>
+      </c>
+      <c r="F1575">
+        <v>228</v>
+      </c>
+      <c r="H1575" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1576" t="s">
+        <v>601</v>
+      </c>
+      <c r="B1576" t="s">
+        <v>301</v>
+      </c>
+      <c r="C1576" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1576">
+        <v>3.0779999999999998</v>
+      </c>
+      <c r="E1576">
+        <v>38</v>
+      </c>
+      <c r="F1576">
+        <v>228</v>
+      </c>
+      <c r="H1576" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1577" t="s">
+        <v>601</v>
+      </c>
+      <c r="B1577" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1577" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1577">
+        <v>3.077</v>
+      </c>
+      <c r="E1577">
+        <v>41</v>
+      </c>
+      <c r="F1577">
+        <v>246</v>
+      </c>
+      <c r="H1577" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1578" t="s">
+        <v>601</v>
+      </c>
+      <c r="B1578" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1578" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1578">
+        <v>3.1579999999999999</v>
+      </c>
+      <c r="E1578">
+        <v>39</v>
+      </c>
+      <c r="F1578">
+        <v>234</v>
+      </c>
+      <c r="H1578" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1579" t="s">
+        <v>601</v>
+      </c>
+      <c r="B1579" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1579" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1579">
+        <v>1.8149999999999999</v>
+      </c>
+      <c r="E1579">
+        <v>28</v>
+      </c>
+      <c r="F1579">
+        <v>168</v>
+      </c>
+      <c r="H1579" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1580" t="s">
+        <v>602</v>
+      </c>
+      <c r="B1580" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1580" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1580">
+        <v>3.024</v>
+      </c>
+      <c r="E1580">
+        <v>30</v>
+      </c>
+      <c r="F1580">
+        <v>180</v>
+      </c>
+      <c r="H1580" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1581" t="s">
+        <v>602</v>
+      </c>
+      <c r="B1581" t="s">
+        <v>306</v>
+      </c>
+      <c r="C1581" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1581">
+        <v>3.016</v>
+      </c>
+      <c r="E1581">
+        <v>30</v>
+      </c>
+      <c r="F1581">
+        <v>180</v>
+      </c>
+      <c r="H1581" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1582" t="s">
+        <v>602</v>
+      </c>
+      <c r="B1582" t="s">
+        <v>307</v>
+      </c>
+      <c r="C1582" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1582">
+        <v>3.0139999999999998</v>
+      </c>
+      <c r="E1582">
+        <v>28</v>
+      </c>
+      <c r="F1582">
+        <v>168</v>
+      </c>
+      <c r="H1582" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1583" t="s">
+        <v>602</v>
+      </c>
+      <c r="B1583" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1583" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1583">
+        <v>3.0139999999999998</v>
+      </c>
+      <c r="E1583">
+        <v>29</v>
+      </c>
+      <c r="F1583">
+        <v>174</v>
+      </c>
+      <c r="H1583" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1584" t="s">
+        <v>602</v>
+      </c>
+      <c r="B1584" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1584" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1584">
+        <v>3.0150000000000001</v>
+      </c>
+      <c r="E1584">
+        <v>28</v>
+      </c>
+      <c r="F1584">
+        <v>168</v>
+      </c>
+      <c r="H1584" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1585" t="s">
+        <v>602</v>
+      </c>
+      <c r="B1585" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1585" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1585">
+        <v>3.0070000000000001</v>
+      </c>
+      <c r="E1585">
+        <v>30</v>
+      </c>
+      <c r="F1585">
+        <v>180</v>
+      </c>
+      <c r="H1585" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1586" t="s">
+        <v>602</v>
+      </c>
+      <c r="B1586" t="s">
+        <v>311</v>
+      </c>
+      <c r="C1586" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1586">
+        <v>3.0129999999999999</v>
+      </c>
+      <c r="E1586">
+        <v>32</v>
+      </c>
+      <c r="F1586">
+        <v>192</v>
+      </c>
+      <c r="H1586" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1587" t="s">
+        <v>602</v>
+      </c>
+      <c r="B1587" t="s">
+        <v>312</v>
+      </c>
+      <c r="C1587" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1587">
+        <v>3.0070000000000001</v>
+      </c>
+      <c r="E1587">
+        <v>29</v>
+      </c>
+      <c r="F1587">
+        <v>174</v>
+      </c>
+      <c r="H1587" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1588" t="s">
+        <v>602</v>
+      </c>
+      <c r="B1588" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1588" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1588">
+        <v>3.0419999999999998</v>
+      </c>
+      <c r="E1588">
+        <v>31</v>
+      </c>
+      <c r="F1588">
+        <v>186</v>
+      </c>
+      <c r="H1588" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1589" t="s">
+        <v>602</v>
+      </c>
+      <c r="B1589" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1589" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1589">
+        <v>3.0129999999999999</v>
+      </c>
+      <c r="E1589">
+        <v>30</v>
+      </c>
+      <c r="F1589">
+        <v>180</v>
+      </c>
+      <c r="H1589" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1590" t="s">
+        <v>602</v>
+      </c>
+      <c r="B1590" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1590" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1590">
+        <v>3.0070000000000001</v>
+      </c>
+      <c r="E1590">
+        <v>32</v>
+      </c>
+      <c r="F1590">
+        <v>192</v>
+      </c>
+      <c r="H1590" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1591" t="s">
+        <v>602</v>
+      </c>
+      <c r="B1591" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1591" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1591">
+        <v>1.48</v>
+      </c>
+      <c r="E1591">
+        <v>23</v>
+      </c>
+      <c r="F1591">
+        <v>138</v>
+      </c>
+      <c r="H1591" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1592" t="s">
+        <v>589</v>
+      </c>
+      <c r="B1592" t="s">
+        <v>317</v>
+      </c>
+      <c r="C1592" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1592" s="3">
+        <v>3.012</v>
+      </c>
+      <c r="E1592">
+        <v>29</v>
+      </c>
+      <c r="F1592">
+        <v>174</v>
+      </c>
+      <c r="H1592" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1593" t="s">
+        <v>589</v>
+      </c>
+      <c r="B1593" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1593" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1593" s="3">
+        <v>3.0350000000000001</v>
+      </c>
+      <c r="E1593">
+        <v>26</v>
+      </c>
+      <c r="F1593">
+        <v>156</v>
+      </c>
+      <c r="H1593" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1594" t="s">
+        <v>589</v>
+      </c>
+      <c r="B1594" t="s">
+        <v>319</v>
+      </c>
+      <c r="C1594" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1594" s="3">
+        <v>3.05</v>
+      </c>
+      <c r="E1594">
+        <v>23</v>
+      </c>
+      <c r="F1594">
+        <v>138</v>
+      </c>
+      <c r="H1594" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1595" t="s">
+        <v>589</v>
+      </c>
+      <c r="B1595" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1595" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1595" s="3">
+        <v>3.0190000000000001</v>
+      </c>
+      <c r="E1595">
+        <v>24</v>
+      </c>
+      <c r="F1595">
+        <v>144</v>
+      </c>
+      <c r="H1595" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1596" t="s">
+        <v>589</v>
+      </c>
+      <c r="B1596" t="s">
+        <v>321</v>
+      </c>
+      <c r="C1596" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1596" s="3">
+        <v>2.3879999999999999</v>
+      </c>
+      <c r="E1596">
+        <v>15</v>
+      </c>
+      <c r="F1596">
+        <v>90</v>
+      </c>
+      <c r="H1596" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1597" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1597" t="s">
+        <v>418</v>
+      </c>
+      <c r="C1597" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1597">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="E1597">
+        <v>25</v>
+      </c>
+      <c r="F1597">
+        <v>150</v>
+      </c>
+      <c r="H1597" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1598" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1598" t="s">
+        <v>419</v>
+      </c>
+      <c r="C1598" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1598">
+        <v>3.024</v>
+      </c>
+      <c r="E1598">
+        <v>22</v>
+      </c>
+      <c r="F1598">
+        <v>132</v>
+      </c>
+      <c r="H1598" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1599" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1599" t="s">
+        <v>420</v>
+      </c>
+      <c r="C1599" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1599">
+        <v>3.004</v>
+      </c>
+      <c r="E1599">
+        <v>28</v>
+      </c>
+      <c r="F1599">
+        <v>168</v>
+      </c>
+      <c r="H1599" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1600" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1600" t="s">
+        <v>421</v>
+      </c>
+      <c r="C1600" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1600">
+        <v>3.032</v>
+      </c>
+      <c r="E1600">
+        <v>25</v>
+      </c>
+      <c r="F1600">
+        <v>150</v>
+      </c>
+      <c r="H1600" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1601" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1601" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1601" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1601">
+        <v>3.032</v>
+      </c>
+      <c r="E1601">
+        <v>28</v>
+      </c>
+      <c r="F1601">
+        <v>168</v>
+      </c>
+      <c r="H1601" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1602" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1602" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1602" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1602">
+        <v>3.0270000000000001</v>
+      </c>
+      <c r="E1602">
+        <v>27</v>
+      </c>
+      <c r="F1602">
+        <v>162</v>
+      </c>
+      <c r="H1602" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1603" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1603" t="s">
+        <v>322</v>
+      </c>
+      <c r="C1603" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1603">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="E1603">
+        <v>25</v>
+      </c>
+      <c r="F1603">
+        <v>150</v>
+      </c>
+      <c r="H1603" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1604" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1604" t="s">
+        <v>323</v>
+      </c>
+      <c r="C1604" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1604">
+        <v>3.0019999999999998</v>
+      </c>
+      <c r="E1604">
+        <v>22</v>
+      </c>
+      <c r="F1604">
+        <v>132</v>
+      </c>
+      <c r="H1604" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1605" t="s">
+        <v>603</v>
+      </c>
+      <c r="B1605" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1605" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1605">
+        <v>0.95</v>
+      </c>
+      <c r="E1605">
+        <v>10</v>
+      </c>
+      <c r="F1605">
+        <v>60</v>
+      </c>
+      <c r="H1605" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1606" t="s">
+        <v>585</v>
+      </c>
+      <c r="B1606" t="s">
+        <v>325</v>
+      </c>
+      <c r="C1606" t="s">
+        <v>446</v>
+      </c>
+      <c r="D1606">
+        <v>4.1950000000000003</v>
+      </c>
+      <c r="E1606">
+        <v>51</v>
+      </c>
+      <c r="F1606">
+        <v>306</v>
+      </c>
+      <c r="H1606" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1607" t="s">
+        <v>604</v>
+      </c>
+      <c r="B1607" t="s">
+        <v>326</v>
+      </c>
+      <c r="C1607" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1607">
+        <v>3.077</v>
+      </c>
+      <c r="E1607">
+        <v>28</v>
+      </c>
+      <c r="F1607">
+        <v>168</v>
+      </c>
+      <c r="H1607" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1608" t="s">
+        <v>604</v>
+      </c>
+      <c r="B1608" t="s">
+        <v>327</v>
+      </c>
+      <c r="C1608" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1608">
+        <v>3.08</v>
+      </c>
+      <c r="E1608">
+        <v>24</v>
+      </c>
+      <c r="F1608">
+        <v>144</v>
+      </c>
+      <c r="H1608" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1609" t="s">
+        <v>604</v>
+      </c>
+      <c r="B1609" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1609" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1609">
+        <v>3.0369999999999999</v>
+      </c>
+      <c r="E1609">
+        <v>25</v>
+      </c>
+      <c r="F1609">
+        <v>150</v>
+      </c>
+      <c r="H1609" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1610" t="s">
+        <v>604</v>
+      </c>
+      <c r="B1610" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1610" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1610">
+        <v>3.0390000000000001</v>
+      </c>
+      <c r="E1610">
+        <v>25</v>
+      </c>
+      <c r="F1610">
+        <v>150</v>
+      </c>
+      <c r="H1610" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1611" t="s">
+        <v>604</v>
+      </c>
+      <c r="B1611" t="s">
+        <v>330</v>
+      </c>
+      <c r="C1611" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1611">
+        <v>3.0510000000000002</v>
+      </c>
+      <c r="E1611">
+        <v>26</v>
+      </c>
+      <c r="F1611">
+        <v>156</v>
+      </c>
+      <c r="H1611" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1612" t="s">
+        <v>604</v>
+      </c>
+      <c r="B1612" t="s">
+        <v>331</v>
+      </c>
+      <c r="C1612" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1612">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="E1612">
+        <v>7</v>
+      </c>
+      <c r="F1612">
+        <v>42</v>
+      </c>
+      <c r="H1612" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1613" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1613" t="s">
+        <v>337</v>
+      </c>
+      <c r="C1613" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1613">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="E1613">
+        <v>39</v>
+      </c>
+      <c r="F1613">
+        <v>234</v>
+      </c>
+      <c r="H1613" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1614" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1614" t="s">
+        <v>338</v>
+      </c>
+      <c r="C1614" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1614">
+        <v>3.0059999999999998</v>
+      </c>
+      <c r="E1614">
+        <v>38</v>
+      </c>
+      <c r="F1614">
+        <v>228</v>
+      </c>
+      <c r="H1614" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1615" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1615" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1615" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1615">
+        <v>3.0169999999999999</v>
+      </c>
+      <c r="E1615">
+        <v>37</v>
+      </c>
+      <c r="F1615">
+        <v>222</v>
+      </c>
+      <c r="H1615" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1616" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1616" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1616" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1616">
+        <v>3.0019999999999998</v>
+      </c>
+      <c r="E1616">
+        <v>38</v>
+      </c>
+      <c r="F1616">
+        <v>228</v>
+      </c>
+      <c r="H1616" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1617" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1617" t="s">
+        <v>341</v>
+      </c>
+      <c r="C1617" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1617">
+        <v>3.0289999999999999</v>
+      </c>
+      <c r="E1617">
+        <v>40</v>
+      </c>
+      <c r="F1617">
+        <v>240</v>
+      </c>
+      <c r="H1617" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1618" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1618" t="s">
+        <v>342</v>
+      </c>
+      <c r="C1618" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1618">
+        <v>1.8340000000000001</v>
+      </c>
+      <c r="E1618">
+        <v>30</v>
+      </c>
+      <c r="F1618">
+        <v>180</v>
+      </c>
+      <c r="H1618" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1619" t="s">
+        <v>606</v>
+      </c>
+      <c r="B1619" t="s">
+        <v>343</v>
+      </c>
+      <c r="C1619" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1619">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="E1619">
+        <v>30</v>
+      </c>
+      <c r="F1619">
+        <v>180</v>
+      </c>
+      <c r="H1619" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1620" t="s">
+        <v>606</v>
+      </c>
+      <c r="B1620" t="s">
+        <v>344</v>
+      </c>
+      <c r="C1620" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1620">
+        <v>3.0019999999999998</v>
+      </c>
+      <c r="E1620">
+        <v>29</v>
+      </c>
+      <c r="F1620">
+        <v>174</v>
+      </c>
+      <c r="H1620" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1621" t="s">
+        <v>606</v>
+      </c>
+      <c r="B1621" t="s">
+        <v>345</v>
+      </c>
+      <c r="C1621" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1621">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="E1621">
+        <v>27</v>
+      </c>
+      <c r="F1621">
+        <v>162</v>
+      </c>
+      <c r="H1621" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1622" t="s">
+        <v>606</v>
+      </c>
+      <c r="B1622" t="s">
+        <v>346</v>
+      </c>
+      <c r="C1622" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1622">
+        <v>3.004</v>
+      </c>
+      <c r="E1622">
+        <v>30</v>
+      </c>
+      <c r="F1622">
+        <v>180</v>
+      </c>
+      <c r="H1622" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1623" t="s">
+        <v>606</v>
+      </c>
+      <c r="B1623" t="s">
+        <v>347</v>
+      </c>
+      <c r="C1623" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1623">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="E1623">
+        <v>29</v>
+      </c>
+      <c r="F1623">
+        <v>174</v>
+      </c>
+      <c r="H1623" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1624" t="s">
+        <v>606</v>
+      </c>
+      <c r="B1624" t="s">
+        <v>348</v>
+      </c>
+      <c r="C1624" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1624">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="E1624">
+        <v>25</v>
+      </c>
+      <c r="F1624">
+        <v>150</v>
+      </c>
+      <c r="H1624" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1625" t="s">
+        <v>606</v>
+      </c>
+      <c r="B1625" t="s">
+        <v>349</v>
+      </c>
+      <c r="C1625" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1625">
+        <v>3.0030000000000001</v>
+      </c>
+      <c r="E1625">
+        <v>26</v>
+      </c>
+      <c r="F1625">
+        <v>156</v>
+      </c>
+      <c r="H1625" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1626" t="s">
+        <v>606</v>
+      </c>
+      <c r="B1626" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1626" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1626">
+        <v>2.1339999999999999</v>
+      </c>
+      <c r="E1626">
+        <v>25</v>
+      </c>
+      <c r="F1626">
+        <v>150</v>
+      </c>
+      <c r="H1626" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1627" t="s">
+        <v>607</v>
+      </c>
+      <c r="B1627" t="s">
+        <v>351</v>
+      </c>
+      <c r="C1627" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1627">
+        <v>3.0539999999999998</v>
+      </c>
+      <c r="E1627">
+        <v>16</v>
+      </c>
+      <c r="F1627">
+        <v>96</v>
+      </c>
+      <c r="H1627" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1628" t="s">
+        <v>607</v>
+      </c>
+      <c r="B1628" t="s">
+        <v>352</v>
+      </c>
+      <c r="C1628" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1628">
+        <v>3.0550000000000002</v>
+      </c>
+      <c r="E1628">
+        <v>8</v>
+      </c>
+      <c r="F1628">
+        <v>48</v>
+      </c>
+      <c r="H1628" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1629" t="s">
+        <v>607</v>
+      </c>
+      <c r="B1629" t="s">
+        <v>353</v>
+      </c>
+      <c r="C1629" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1629">
+        <v>3.141</v>
+      </c>
+      <c r="E1629">
+        <v>16</v>
+      </c>
+      <c r="F1629">
+        <v>96</v>
+      </c>
+      <c r="H1629" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1630" t="s">
+        <v>607</v>
+      </c>
+      <c r="B1630" t="s">
+        <v>354</v>
+      </c>
+      <c r="C1630" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1630">
+        <v>3.12</v>
+      </c>
+      <c r="E1630">
+        <v>18</v>
+      </c>
+      <c r="F1630">
+        <v>108</v>
+      </c>
+      <c r="H1630" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1631" t="s">
+        <v>607</v>
+      </c>
+      <c r="B1631" t="s">
+        <v>355</v>
+      </c>
+      <c r="C1631" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1631">
+        <v>3.0640000000000001</v>
+      </c>
+      <c r="E1631">
+        <v>22</v>
+      </c>
+      <c r="F1631">
+        <v>132</v>
+      </c>
+      <c r="H1631" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1632" t="s">
+        <v>607</v>
+      </c>
+      <c r="B1632" t="s">
+        <v>356</v>
+      </c>
+      <c r="C1632" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1632">
+        <v>3.004</v>
+      </c>
+      <c r="E1632">
+        <v>14</v>
+      </c>
+      <c r="F1632">
+        <v>84</v>
+      </c>
+      <c r="H1632" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1633" t="s">
+        <v>607</v>
+      </c>
+      <c r="B1633" t="s">
+        <v>357</v>
+      </c>
+      <c r="C1633" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1633">
+        <v>0.114</v>
+      </c>
+      <c r="E1633">
+        <v>3</v>
+      </c>
+      <c r="F1633">
+        <v>18</v>
+      </c>
+      <c r="H1633" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1634" t="s">
+        <v>608</v>
+      </c>
+      <c r="B1634" t="s">
+        <v>358</v>
+      </c>
+      <c r="C1634" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1634">
+        <v>3.05</v>
+      </c>
+      <c r="E1634">
+        <v>33</v>
+      </c>
+      <c r="F1634">
+        <v>198</v>
+      </c>
+      <c r="H1634" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1635" t="s">
+        <v>608</v>
+      </c>
+      <c r="B1635" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1635" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1635">
+        <v>3.0529999999999999</v>
+      </c>
+      <c r="E1635">
+        <v>35</v>
+      </c>
+      <c r="F1635">
+        <v>210</v>
+      </c>
+      <c r="H1635" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1636" t="s">
+        <v>608</v>
+      </c>
+      <c r="B1636" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1636" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1636">
+        <v>3.0459999999999998</v>
+      </c>
+      <c r="E1636">
+        <v>31</v>
+      </c>
+      <c r="F1636">
+        <v>186</v>
+      </c>
+      <c r="H1636" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1637" t="s">
+        <v>608</v>
+      </c>
+      <c r="B1637" t="s">
+        <v>361</v>
+      </c>
+      <c r="C1637" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1637">
+        <v>3.0539999999999998</v>
+      </c>
+      <c r="E1637">
+        <v>34</v>
+      </c>
+      <c r="F1637">
+        <v>204</v>
+      </c>
+      <c r="H1637" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1638" t="s">
+        <v>608</v>
+      </c>
+      <c r="B1638" t="s">
+        <v>362</v>
+      </c>
+      <c r="C1638" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1638">
+        <v>3.0550000000000002</v>
+      </c>
+      <c r="E1638">
+        <v>36</v>
+      </c>
+      <c r="F1638">
+        <v>216</v>
+      </c>
+      <c r="H1638" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1639" t="s">
+        <v>608</v>
+      </c>
+      <c r="B1639" t="s">
+        <v>363</v>
+      </c>
+      <c r="C1639" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1639">
+        <v>3.0640000000000001</v>
+      </c>
+      <c r="E1639">
+        <v>31</v>
+      </c>
+      <c r="F1639">
+        <v>186</v>
+      </c>
+      <c r="H1639" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1640" t="s">
+        <v>608</v>
+      </c>
+      <c r="B1640" t="s">
+        <v>364</v>
+      </c>
+      <c r="C1640" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1640">
+        <v>3.0710000000000002</v>
+      </c>
+      <c r="E1640">
+        <v>31</v>
+      </c>
+      <c r="F1640">
+        <v>186</v>
+      </c>
+      <c r="H1640" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1641" t="s">
+        <v>608</v>
+      </c>
+      <c r="B1641" t="s">
+        <v>365</v>
+      </c>
+      <c r="C1641" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1641">
+        <v>3.0489999999999999</v>
+      </c>
+      <c r="E1641">
+        <v>28</v>
+      </c>
+      <c r="F1641">
+        <v>168</v>
+      </c>
+      <c r="H1641" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1642" t="s">
+        <v>608</v>
+      </c>
+      <c r="B1642" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1642" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1642">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="E1642">
+        <v>4</v>
+      </c>
+      <c r="F1642">
+        <v>24</v>
+      </c>
+      <c r="H1642" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1643" t="s">
+        <v>609</v>
+      </c>
+      <c r="B1643" t="s">
+        <v>367</v>
+      </c>
+      <c r="C1643" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1643">
+        <v>3.0379999999999998</v>
+      </c>
+      <c r="E1643">
+        <v>24</v>
+      </c>
+      <c r="F1643">
+        <v>144</v>
+      </c>
+      <c r="H1643" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1644" t="s">
+        <v>609</v>
+      </c>
+      <c r="B1644" t="s">
+        <v>368</v>
+      </c>
+      <c r="C1644" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1644">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="E1644">
+        <v>26</v>
+      </c>
+      <c r="F1644">
+        <v>156</v>
+      </c>
+      <c r="H1644" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1645" t="s">
+        <v>609</v>
+      </c>
+      <c r="B1645" t="s">
+        <v>369</v>
+      </c>
+      <c r="C1645" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1645">
+        <v>3.03</v>
+      </c>
+      <c r="E1645">
+        <v>24</v>
+      </c>
+      <c r="F1645">
+        <v>144</v>
+      </c>
+      <c r="H1645" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1646" t="s">
+        <v>609</v>
+      </c>
+      <c r="B1646" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1646" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1646">
+        <v>3.03</v>
+      </c>
+      <c r="E1646">
+        <v>27</v>
+      </c>
+      <c r="F1646">
+        <v>162</v>
+      </c>
+      <c r="H1646" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1647" t="s">
+        <v>609</v>
+      </c>
+      <c r="B1647" t="s">
+        <v>371</v>
+      </c>
+      <c r="C1647" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1647">
+        <v>3.0049999999999999</v>
+      </c>
+      <c r="E1647">
+        <v>25</v>
+      </c>
+      <c r="F1647">
+        <v>150</v>
+      </c>
+      <c r="H1647" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1648" t="s">
+        <v>609</v>
+      </c>
+      <c r="B1648" t="s">
+        <v>372</v>
+      </c>
+      <c r="C1648" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1648">
+        <v>3.0110000000000001</v>
+      </c>
+      <c r="E1648">
+        <v>25</v>
+      </c>
+      <c r="F1648">
+        <v>150</v>
+      </c>
+      <c r="H1648" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1649" t="s">
+        <v>609</v>
+      </c>
+      <c r="B1649" t="s">
+        <v>373</v>
+      </c>
+      <c r="C1649" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1649">
+        <v>1.0109999999999999</v>
+      </c>
+      <c r="E1649">
+        <v>9</v>
+      </c>
+      <c r="F1649">
+        <v>54</v>
+      </c>
+      <c r="H1649" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1650" t="s">
+        <v>610</v>
+      </c>
+      <c r="B1650" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1650" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1650">
+        <v>3.5539999999999998</v>
+      </c>
+      <c r="E1650">
+        <v>36</v>
+      </c>
+      <c r="F1650">
+        <v>216</v>
+      </c>
+      <c r="H1650" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1651" t="s">
+        <v>610</v>
+      </c>
+      <c r="B1651" t="s">
+        <v>375</v>
+      </c>
+      <c r="C1651" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1651">
+        <v>0.5169999999999999</v>
+      </c>
+      <c r="E1651">
+        <v>5</v>
+      </c>
+      <c r="F1651">
+        <v>30</v>
+      </c>
+      <c r="H1651" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1652" t="s">
+        <v>610</v>
+      </c>
+      <c r="B1652" t="s">
+        <v>376</v>
+      </c>
+      <c r="C1652" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1652">
+        <v>3.02</v>
+      </c>
+      <c r="E1652">
+        <v>35</v>
+      </c>
+      <c r="F1652">
+        <v>210</v>
+      </c>
+      <c r="H1652" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1653" t="s">
+        <v>610</v>
+      </c>
+      <c r="B1653" t="s">
+        <v>377</v>
+      </c>
+      <c r="C1653" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1653">
+        <v>3.028</v>
+      </c>
+      <c r="E1653">
+        <v>35</v>
+      </c>
+      <c r="F1653">
+        <v>210</v>
+      </c>
+      <c r="H1653" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1654" t="s">
+        <v>610</v>
+      </c>
+      <c r="B1654" t="s">
+        <v>378</v>
+      </c>
+      <c r="C1654" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1654">
+        <v>3.0209999999999999</v>
+      </c>
+      <c r="E1654">
+        <v>36</v>
+      </c>
+      <c r="F1654">
+        <v>216</v>
+      </c>
+      <c r="H1654" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1655" t="s">
+        <v>610</v>
+      </c>
+      <c r="B1655" t="s">
+        <v>379</v>
+      </c>
+      <c r="C1655" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1655">
+        <v>3.0209999999999999</v>
+      </c>
+      <c r="E1655">
+        <v>36</v>
+      </c>
+      <c r="F1655">
+        <v>216</v>
+      </c>
+      <c r="H1655" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1656" t="s">
+        <v>610</v>
+      </c>
+      <c r="B1656" t="s">
+        <v>380</v>
+      </c>
+      <c r="C1656" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1656">
+        <v>3.028</v>
+      </c>
+      <c r="E1656">
+        <v>35</v>
+      </c>
+      <c r="F1656">
+        <v>210</v>
+      </c>
+      <c r="H1656" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1657" t="s">
+        <v>610</v>
+      </c>
+      <c r="B1657" t="s">
+        <v>381</v>
+      </c>
+      <c r="C1657" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1657">
+        <v>3.004</v>
+      </c>
+      <c r="E1657">
+        <v>34</v>
+      </c>
+      <c r="F1657">
+        <v>204</v>
+      </c>
+      <c r="H1657" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1658" t="s">
+        <v>611</v>
+      </c>
+      <c r="B1658" t="s">
+        <v>382</v>
+      </c>
+      <c r="C1658" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1658">
+        <v>3.097</v>
+      </c>
+      <c r="E1658">
+        <v>37</v>
+      </c>
+      <c r="F1658">
+        <v>222</v>
+      </c>
+      <c r="H1658" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1659" t="s">
+        <v>611</v>
+      </c>
+      <c r="B1659" t="s">
+        <v>383</v>
+      </c>
+      <c r="C1659" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1659">
+        <v>3.1179999999999999</v>
+      </c>
+      <c r="E1659">
+        <v>37</v>
+      </c>
+      <c r="F1659">
+        <v>222</v>
+      </c>
+      <c r="H1659" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1660" t="s">
+        <v>611</v>
+      </c>
+      <c r="B1660" t="s">
+        <v>384</v>
+      </c>
+      <c r="C1660" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1660">
+        <v>3.1360000000000001</v>
+      </c>
+      <c r="E1660">
+        <v>39</v>
+      </c>
+      <c r="F1660">
+        <v>234</v>
+      </c>
+      <c r="H1660" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1661" t="s">
+        <v>611</v>
+      </c>
+      <c r="B1661" t="s">
+        <v>385</v>
+      </c>
+      <c r="C1661" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1661">
+        <v>3.1360000000000001</v>
+      </c>
+      <c r="E1661">
+        <v>36</v>
+      </c>
+      <c r="F1661">
+        <v>216</v>
+      </c>
+      <c r="H1661" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1662" t="s">
+        <v>611</v>
+      </c>
+      <c r="B1662" t="s">
+        <v>386</v>
+      </c>
+      <c r="C1662" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1662">
+        <v>3.141</v>
+      </c>
+      <c r="E1662">
+        <v>37</v>
+      </c>
+      <c r="F1662">
+        <v>222</v>
+      </c>
+      <c r="H1662" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1663" t="s">
+        <v>611</v>
+      </c>
+      <c r="B1663" t="s">
+        <v>387</v>
+      </c>
+      <c r="C1663" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1663">
+        <v>2.6970000000000001</v>
+      </c>
+      <c r="E1663">
+        <v>34</v>
+      </c>
+      <c r="F1663">
+        <v>204</v>
+      </c>
+      <c r="H1663" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1664" t="s">
+        <v>612</v>
+      </c>
+      <c r="B1664" t="s">
+        <v>388</v>
+      </c>
+      <c r="C1664" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1664">
+        <v>2.9940000000000002</v>
+      </c>
+      <c r="E1664">
+        <v>34</v>
+      </c>
+      <c r="F1664">
+        <v>204</v>
+      </c>
+      <c r="H1664" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1665" t="s">
+        <v>612</v>
+      </c>
+      <c r="B1665" t="s">
+        <v>389</v>
+      </c>
+      <c r="C1665" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1665">
+        <v>2.992</v>
+      </c>
+      <c r="E1665">
+        <v>35</v>
+      </c>
+      <c r="F1665">
+        <v>210</v>
+      </c>
+      <c r="H1665" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1666" t="s">
+        <v>612</v>
+      </c>
+      <c r="B1666" t="s">
+        <v>390</v>
+      </c>
+      <c r="C1666" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1666">
+        <v>2.996</v>
+      </c>
+      <c r="E1666">
+        <v>31</v>
+      </c>
+      <c r="F1666">
+        <v>186</v>
+      </c>
+      <c r="H1666" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1667" t="s">
+        <v>612</v>
+      </c>
+      <c r="B1667" t="s">
+        <v>391</v>
+      </c>
+      <c r="C1667" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1667">
+        <v>2.9969999999999999</v>
+      </c>
+      <c r="E1667">
+        <v>32</v>
+      </c>
+      <c r="F1667">
+        <v>192</v>
+      </c>
+      <c r="H1667" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1668" t="s">
+        <v>612</v>
+      </c>
+      <c r="B1668" t="s">
+        <v>392</v>
+      </c>
+      <c r="C1668" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1668">
+        <v>2.996</v>
+      </c>
+      <c r="E1668">
+        <v>32</v>
+      </c>
+      <c r="F1668">
+        <v>192</v>
+      </c>
+      <c r="H1668" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1669" t="s">
+        <v>612</v>
+      </c>
+      <c r="B1669" t="s">
+        <v>393</v>
+      </c>
+      <c r="C1669" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1669">
+        <v>2.996</v>
+      </c>
+      <c r="E1669">
+        <v>30</v>
+      </c>
+      <c r="F1669">
+        <v>180</v>
+      </c>
+      <c r="H1669" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1670" t="s">
+        <v>612</v>
+      </c>
+      <c r="B1670" t="s">
+        <v>394</v>
+      </c>
+      <c r="C1670" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1670">
+        <v>2.996</v>
+      </c>
+      <c r="E1670">
+        <v>32</v>
+      </c>
+      <c r="F1670">
+        <v>192</v>
+      </c>
+      <c r="H1670" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1671" t="s">
+        <v>612</v>
+      </c>
+      <c r="B1671" t="s">
+        <v>395</v>
+      </c>
+      <c r="C1671" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1671">
+        <v>2.9969999999999999</v>
+      </c>
+      <c r="E1671">
+        <v>29</v>
+      </c>
+      <c r="F1671">
+        <v>174</v>
+      </c>
+      <c r="H1671" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1672" t="s">
+        <v>612</v>
+      </c>
+      <c r="B1672" t="s">
+        <v>396</v>
+      </c>
+      <c r="C1672" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1672">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="E1672">
+        <v>3</v>
+      </c>
+      <c r="F1672">
+        <v>18</v>
+      </c>
+      <c r="H1672" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1673" t="s">
+        <v>613</v>
+      </c>
+      <c r="B1673" t="s">
+        <v>397</v>
+      </c>
+      <c r="C1673" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1673">
+        <v>3.1080000000000001</v>
+      </c>
+      <c r="E1673">
+        <v>39</v>
+      </c>
+      <c r="F1673">
+        <v>234</v>
+      </c>
+      <c r="H1673" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1674" t="s">
+        <v>613</v>
+      </c>
+      <c r="B1674" t="s">
+        <v>398</v>
+      </c>
+      <c r="C1674" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1674">
+        <v>3.1259999999999999</v>
+      </c>
+      <c r="E1674">
+        <v>36</v>
+      </c>
+      <c r="F1674">
+        <v>216</v>
+      </c>
+      <c r="H1674" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1675" t="s">
+        <v>613</v>
+      </c>
+      <c r="B1675" t="s">
+        <v>399</v>
+      </c>
+      <c r="C1675" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1675">
+        <v>3.125</v>
+      </c>
+      <c r="E1675">
+        <v>37</v>
+      </c>
+      <c r="F1675">
+        <v>222</v>
+      </c>
+      <c r="H1675" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1676" t="s">
+        <v>613</v>
+      </c>
+      <c r="B1676" t="s">
+        <v>400</v>
+      </c>
+      <c r="C1676" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1676">
+        <v>4.6340000000000003</v>
+      </c>
+      <c r="E1676">
+        <v>68</v>
+      </c>
+      <c r="F1676">
+        <v>408</v>
+      </c>
+      <c r="H1676" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1677" t="s">
+        <v>614</v>
+      </c>
+      <c r="B1677" t="s">
+        <v>404</v>
+      </c>
+      <c r="C1677" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1677">
+        <v>3.016</v>
+      </c>
+      <c r="E1677">
+        <v>22</v>
+      </c>
+      <c r="F1677">
+        <v>132</v>
+      </c>
+      <c r="H1677" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1678" t="s">
+        <v>614</v>
+      </c>
+      <c r="B1678" t="s">
+        <v>405</v>
+      </c>
+      <c r="C1678" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1678">
+        <v>3.0270000000000001</v>
+      </c>
+      <c r="E1678">
+        <v>22</v>
+      </c>
+      <c r="F1678">
+        <v>132</v>
+      </c>
+      <c r="H1678" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1679" t="s">
+        <v>614</v>
+      </c>
+      <c r="B1679" t="s">
+        <v>406</v>
+      </c>
+      <c r="C1679" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1679">
+        <v>3.024</v>
+      </c>
+      <c r="E1679">
+        <v>20</v>
+      </c>
+      <c r="F1679">
+        <v>120</v>
+      </c>
+      <c r="H1679" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1680" t="s">
+        <v>614</v>
+      </c>
+      <c r="B1680" t="s">
+        <v>407</v>
+      </c>
+      <c r="C1680" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1680">
+        <v>3.0270000000000001</v>
+      </c>
+      <c r="E1680">
+        <v>21</v>
+      </c>
+      <c r="F1680">
+        <v>126</v>
+      </c>
+      <c r="H1680" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1681" t="s">
+        <v>614</v>
+      </c>
+      <c r="B1681" t="s">
+        <v>408</v>
+      </c>
+      <c r="C1681" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1681">
+        <v>3.0270000000000001</v>
+      </c>
+      <c r="E1681">
+        <v>21</v>
+      </c>
+      <c r="F1681">
+        <v>126</v>
+      </c>
+      <c r="H1681" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1682" t="s">
+        <v>614</v>
+      </c>
+      <c r="B1682" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1682" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1682">
+        <v>3.0129999999999999</v>
+      </c>
+      <c r="E1682">
+        <v>25</v>
+      </c>
+      <c r="F1682">
+        <v>150</v>
+      </c>
+      <c r="H1682" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1683" t="s">
+        <v>614</v>
+      </c>
+      <c r="B1683" t="s">
+        <v>410</v>
+      </c>
+      <c r="C1683" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1683">
+        <v>3.0030000000000001</v>
+      </c>
+      <c r="E1683">
+        <v>22</v>
+      </c>
+      <c r="F1683">
+        <v>132</v>
+      </c>
+      <c r="H1683" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1684" t="s">
+        <v>614</v>
+      </c>
+      <c r="B1684" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1684" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1684">
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="E1684">
+        <v>20</v>
+      </c>
+      <c r="F1684">
+        <v>120</v>
+      </c>
+      <c r="H1684" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1685" t="s">
+        <v>615</v>
+      </c>
+      <c r="B1685" t="s">
+        <v>401</v>
+      </c>
+      <c r="C1685" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1685">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="E1685">
+        <v>38</v>
+      </c>
+      <c r="F1685">
+        <v>228</v>
+      </c>
+      <c r="H1685" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1686" t="s">
+        <v>615</v>
+      </c>
+      <c r="B1686" t="s">
+        <v>402</v>
+      </c>
+      <c r="C1686" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1686">
+        <v>2.8969999999999998</v>
+      </c>
+      <c r="E1686">
+        <v>33</v>
+      </c>
+      <c r="F1686">
+        <v>198</v>
+      </c>
+      <c r="H1686" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1687" t="s">
+        <v>615</v>
+      </c>
+      <c r="B1687" t="s">
+        <v>403</v>
+      </c>
+      <c r="C1687" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1687">
+        <v>3.0059999999999998</v>
+      </c>
+      <c r="E1687">
+        <v>41</v>
+      </c>
+      <c r="F1687">
+        <v>246</v>
+      </c>
+      <c r="H1687" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1688" t="s">
+        <v>594</v>
+      </c>
+      <c r="B1688" t="s">
+        <v>267</v>
+      </c>
+      <c r="C1688" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1688">
+        <v>3.036</v>
+      </c>
+      <c r="E1688">
+        <v>21</v>
+      </c>
+      <c r="F1688">
+        <v>126</v>
+      </c>
+      <c r="H1688" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1689" t="s">
+        <v>594</v>
+      </c>
+      <c r="B1689" t="s">
+        <v>268</v>
+      </c>
+      <c r="C1689" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1689">
+        <v>3.01</v>
+      </c>
+      <c r="E1689">
+        <v>18</v>
+      </c>
+      <c r="F1689">
+        <v>108</v>
+      </c>
+      <c r="H1689" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1690" t="s">
+        <v>594</v>
+      </c>
+      <c r="B1690" t="s">
+        <v>269</v>
+      </c>
+      <c r="C1690" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1690">
+        <v>3.0150000000000001</v>
+      </c>
+      <c r="E1690">
+        <v>18</v>
+      </c>
+      <c r="F1690">
+        <v>108</v>
+      </c>
+      <c r="H1690" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1691" t="s">
+        <v>594</v>
+      </c>
+      <c r="B1691" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1691" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1691">
+        <v>3.0409999999999999</v>
+      </c>
+      <c r="E1691">
+        <v>20</v>
+      </c>
+      <c r="F1691">
+        <v>120</v>
+      </c>
+      <c r="H1691" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1692" t="s">
+        <v>594</v>
+      </c>
+      <c r="B1692" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1692" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1692">
+        <v>3.0390000000000001</v>
+      </c>
+      <c r="E1692">
+        <v>21</v>
+      </c>
+      <c r="F1692">
+        <v>126</v>
+      </c>
+      <c r="H1692" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1693" t="s">
+        <v>594</v>
+      </c>
+      <c r="B1693" t="s">
+        <v>272</v>
+      </c>
+      <c r="C1693" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1693">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="E1693">
+        <v>18</v>
+      </c>
+      <c r="F1693">
+        <v>108</v>
+      </c>
+      <c r="H1693" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1694" t="s">
+        <v>594</v>
+      </c>
+      <c r="B1694" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1694" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1694">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="E1694">
+        <v>19</v>
+      </c>
+      <c r="F1694">
+        <v>114</v>
+      </c>
+      <c r="H1694" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1695" t="s">
+        <v>594</v>
+      </c>
+      <c r="B1695" t="s">
+        <v>274</v>
+      </c>
+      <c r="C1695" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1695">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="E1695">
+        <v>6</v>
+      </c>
+      <c r="F1695">
+        <v>36</v>
+      </c>
+      <c r="H1695" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1696" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1696" t="s">
+        <v>258</v>
+      </c>
+      <c r="C1696" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1696">
+        <v>42</v>
+      </c>
+      <c r="E1696">
+        <v>42</v>
+      </c>
+      <c r="F1696">
+        <v>252</v>
+      </c>
+      <c r="H1696" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1697" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1697" t="s">
+        <v>259</v>
+      </c>
+      <c r="C1697" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1697">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="E1697">
+        <v>36</v>
+      </c>
+      <c r="F1697">
+        <v>216</v>
+      </c>
+      <c r="H1697" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1698" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1698" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1698" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1698">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="E1698">
+        <v>38</v>
+      </c>
+      <c r="F1698">
+        <v>228</v>
+      </c>
+      <c r="H1698" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1699" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1699" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1699" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1699">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="E1699">
+        <v>39</v>
+      </c>
+      <c r="F1699">
+        <v>234</v>
+      </c>
+      <c r="H1699" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1700" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1700" t="s">
+        <v>262</v>
+      </c>
+      <c r="C1700" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1700">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="E1700">
+        <v>37</v>
+      </c>
+      <c r="F1700">
+        <v>222</v>
+      </c>
+      <c r="H1700" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1701" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1701" t="s">
+        <v>263</v>
+      </c>
+      <c r="C1701" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1701">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="E1701">
+        <v>38</v>
+      </c>
+      <c r="F1701">
+        <v>228</v>
+      </c>
+      <c r="H1701" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1702" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1702" t="s">
+        <v>264</v>
+      </c>
+      <c r="C1702" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1702">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="E1702">
+        <v>37</v>
+      </c>
+      <c r="F1702">
+        <v>222</v>
+      </c>
+      <c r="H1702" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1703" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1703" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1703" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1703">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="E1703">
+        <v>42</v>
+      </c>
+      <c r="F1703">
+        <v>252</v>
+      </c>
+      <c r="H1703" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1704" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1704" t="s">
+        <v>266</v>
+      </c>
+      <c r="C1704" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1704">
+        <v>3.0230000000000001</v>
+      </c>
+      <c r="E1704">
+        <v>14</v>
+      </c>
+      <c r="F1704">
+        <v>84</v>
+      </c>
+      <c r="H1704" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1705" t="s">
+        <v>616</v>
+      </c>
+      <c r="B1705" t="s">
+        <v>251</v>
+      </c>
+      <c r="C1705" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1705">
+        <v>0.84499999999999997</v>
+      </c>
+      <c r="E1705">
+        <v>35</v>
+      </c>
+      <c r="F1705">
+        <v>210</v>
+      </c>
+      <c r="H1705" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1706" t="s">
+        <v>616</v>
+      </c>
+      <c r="B1706" t="s">
+        <v>252</v>
+      </c>
+      <c r="C1706" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1706">
+        <v>3.0089999999999999</v>
+      </c>
+      <c r="E1706">
+        <v>35</v>
+      </c>
+      <c r="F1706">
+        <v>210</v>
+      </c>
+      <c r="H1706" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1707" t="s">
+        <v>616</v>
+      </c>
+      <c r="B1707" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1707" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1707">
+        <v>3.0190000000000001</v>
+      </c>
+      <c r="E1707">
+        <v>33</v>
+      </c>
+      <c r="F1707">
+        <v>198</v>
+      </c>
+      <c r="H1707" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1708" t="s">
+        <v>616</v>
+      </c>
+      <c r="B1708" t="s">
+        <v>254</v>
+      </c>
+      <c r="C1708" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1708">
+        <v>3.012</v>
+      </c>
+      <c r="E1708">
+        <v>33</v>
+      </c>
+      <c r="F1708">
+        <v>198</v>
+      </c>
+      <c r="H1708" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1709" t="s">
+        <v>616</v>
+      </c>
+      <c r="B1709" t="s">
+        <v>255</v>
+      </c>
+      <c r="C1709" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1709">
+        <v>3.012</v>
+      </c>
+      <c r="E1709">
+        <v>35</v>
+      </c>
+      <c r="F1709">
+        <v>210</v>
+      </c>
+      <c r="H1709" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1710" t="s">
+        <v>616</v>
+      </c>
+      <c r="B1710" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1710" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1710">
+        <v>3.0470000000000002</v>
+      </c>
+      <c r="E1710">
+        <v>31</v>
+      </c>
+      <c r="F1710">
+        <v>186</v>
+      </c>
+      <c r="H1710" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1711" t="s">
+        <v>616</v>
+      </c>
+      <c r="B1711" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1711" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1711">
+        <v>3.0329999999999999</v>
+      </c>
+      <c r="E1711">
+        <v>32</v>
+      </c>
+      <c r="F1711">
+        <v>192</v>
+      </c>
+      <c r="H1711" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1712" t="s">
+        <v>617</v>
+      </c>
+      <c r="B1712" t="s">
+        <v>243</v>
+      </c>
+      <c r="C1712" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1712">
+        <v>3.0550000000000002</v>
+      </c>
+      <c r="E1712">
+        <v>35</v>
+      </c>
+      <c r="F1712">
+        <v>210</v>
+      </c>
+      <c r="H1712" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1713" t="s">
+        <v>617</v>
+      </c>
+      <c r="B1713" t="s">
+        <v>244</v>
+      </c>
+      <c r="C1713" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1713">
+        <v>3.1269999999999998</v>
+      </c>
+      <c r="E1713">
+        <v>35</v>
+      </c>
+      <c r="F1713">
+        <v>210</v>
+      </c>
+      <c r="H1713" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1714" t="s">
+        <v>617</v>
+      </c>
+      <c r="B1714" t="s">
+        <v>245</v>
+      </c>
+      <c r="C1714" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1714">
+        <v>3.089</v>
+      </c>
+      <c r="E1714">
+        <v>41</v>
+      </c>
+      <c r="F1714">
+        <v>246</v>
+      </c>
+      <c r="H1714" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1715" t="s">
+        <v>617</v>
+      </c>
+      <c r="B1715" t="s">
+        <v>246</v>
+      </c>
+      <c r="C1715" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1715">
+        <v>3.0990000000000002</v>
+      </c>
+      <c r="E1715">
+        <v>42</v>
+      </c>
+      <c r="F1715">
+        <v>252</v>
+      </c>
+      <c r="H1715" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1716" t="s">
+        <v>617</v>
+      </c>
+      <c r="B1716" t="s">
+        <v>247</v>
+      </c>
+      <c r="C1716" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1716">
+        <v>3.093</v>
+      </c>
+      <c r="E1716">
+        <v>39</v>
+      </c>
+      <c r="F1716">
+        <v>234</v>
+      </c>
+      <c r="H1716" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1717" t="s">
+        <v>617</v>
+      </c>
+      <c r="B1717" t="s">
+        <v>248</v>
+      </c>
+      <c r="C1717" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1717">
+        <v>3.0870000000000002</v>
+      </c>
+      <c r="E1717">
+        <v>36</v>
+      </c>
+      <c r="F1717">
+        <v>216</v>
+      </c>
+      <c r="H1717" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1718" t="s">
+        <v>617</v>
+      </c>
+      <c r="B1718" t="s">
+        <v>249</v>
+      </c>
+      <c r="C1718" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1718">
+        <v>3.089</v>
+      </c>
+      <c r="E1718">
+        <v>39</v>
+      </c>
+      <c r="F1718">
+        <v>234</v>
+      </c>
+      <c r="H1718" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1719" t="s">
+        <v>617</v>
+      </c>
+      <c r="B1719" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1719" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1719">
+        <v>2.9039999999999999</v>
+      </c>
+      <c r="E1719">
+        <v>36</v>
+      </c>
+      <c r="F1719">
+        <v>216</v>
+      </c>
+      <c r="H1719" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1720" t="s">
+        <v>618</v>
+      </c>
+      <c r="B1720" t="s">
+        <v>238</v>
+      </c>
+      <c r="C1720" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1720">
+        <v>3.0030000000000001</v>
+      </c>
+      <c r="E1720">
+        <v>40</v>
+      </c>
+      <c r="F1720">
+        <v>240</v>
+      </c>
+      <c r="H1720" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1721" t="s">
+        <v>618</v>
+      </c>
+      <c r="B1721" t="s">
+        <v>239</v>
+      </c>
+      <c r="C1721" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1721">
+        <v>3.0680000000000001</v>
+      </c>
+      <c r="E1721">
+        <v>34</v>
+      </c>
+      <c r="F1721">
+        <v>204</v>
+      </c>
+      <c r="H1721" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1722" t="s">
+        <v>618</v>
+      </c>
+      <c r="B1722" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1722" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1722">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="E1722">
+        <v>36</v>
+      </c>
+      <c r="F1722">
+        <v>216</v>
+      </c>
+      <c r="H1722" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1723" t="s">
+        <v>618</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>241</v>
+      </c>
+      <c r="C1723" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1723">
+        <v>3.0579999999999998</v>
+      </c>
+      <c r="E1723">
+        <v>37</v>
+      </c>
+      <c r="F1723">
+        <v>222</v>
+      </c>
+      <c r="H1723" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1724" t="s">
+        <v>618</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>242</v>
+      </c>
+      <c r="C1724" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1724">
+        <v>0.64100000000000001</v>
+      </c>
+      <c r="E1724">
+        <v>7</v>
+      </c>
+      <c r="F1724">
+        <v>42</v>
+      </c>
+      <c r="H1724" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1725" t="s">
+        <v>619</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>234</v>
+      </c>
+      <c r="C1725" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1725">
+        <v>2.984</v>
+      </c>
+      <c r="E1725">
+        <v>15</v>
+      </c>
+      <c r="F1725">
+        <v>90</v>
+      </c>
+      <c r="H1725" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1726" t="s">
+        <v>619</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>235</v>
+      </c>
+      <c r="C1726" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1726">
+        <v>2.9780000000000002</v>
+      </c>
+      <c r="E1726">
+        <v>19</v>
+      </c>
+      <c r="F1726">
+        <v>114</v>
+      </c>
+      <c r="H1726" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1727" t="s">
+        <v>619</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1727" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1727">
+        <v>2.9740000000000002</v>
+      </c>
+      <c r="E1727">
+        <v>11</v>
+      </c>
+      <c r="F1727">
+        <v>66</v>
+      </c>
+      <c r="H1727" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1728" t="s">
+        <v>619</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1728" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1728">
+        <v>0.84399999999999997</v>
+      </c>
+      <c r="E1728">
+        <v>4</v>
+      </c>
+      <c r="F1728">
+        <v>24</v>
+      </c>
+      <c r="H1728" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1729" t="s">
+        <v>620</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1729" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1729">
+        <v>3.016</v>
+      </c>
+      <c r="E1729">
+        <v>28</v>
+      </c>
+      <c r="F1729">
+        <v>168</v>
+      </c>
+      <c r="H1729" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1730" t="s">
+        <v>620</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1730" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1730">
+        <v>3.0150000000000001</v>
+      </c>
+      <c r="E1730">
+        <v>28</v>
+      </c>
+      <c r="F1730">
+        <v>168</v>
+      </c>
+      <c r="H1730" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1731" t="s">
+        <v>620</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>232</v>
+      </c>
+      <c r="C1731" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1731">
+        <v>3.016</v>
+      </c>
+      <c r="E1731">
+        <v>28</v>
+      </c>
+      <c r="F1731">
+        <v>168</v>
+      </c>
+      <c r="H1731" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1732" t="s">
+        <v>620</v>
+      </c>
+      <c r="B1732" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1732" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1732">
+        <v>2.0779999999999998</v>
+      </c>
+      <c r="E1732">
+        <v>20</v>
+      </c>
+      <c r="F1732">
+        <v>120</v>
+      </c>
+      <c r="H1732" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1733" t="s">
+        <v>621</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1733" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1733">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="E1733">
+        <v>51</v>
+      </c>
+      <c r="F1733">
+        <v>306</v>
+      </c>
+      <c r="H1733" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1734" t="s">
+        <v>621</v>
+      </c>
+      <c r="B1734" t="s">
+        <v>227</v>
+      </c>
+      <c r="C1734" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1734">
+        <v>3.0350000000000001</v>
+      </c>
+      <c r="E1734">
+        <v>39</v>
+      </c>
+      <c r="F1734">
+        <v>234</v>
+      </c>
+      <c r="H1734" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1735" t="s">
+        <v>621</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>228</v>
+      </c>
+      <c r="C1735" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1735">
+        <v>3.03</v>
+      </c>
+      <c r="E1735">
+        <v>27</v>
+      </c>
+      <c r="F1735">
+        <v>162</v>
+      </c>
+      <c r="H1735" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1736" t="s">
+        <v>621</v>
+      </c>
+      <c r="B1736" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1736" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1736">
+        <v>1.349</v>
+      </c>
+      <c r="E1736">
+        <v>20</v>
+      </c>
+      <c r="F1736">
+        <v>120</v>
+      </c>
+      <c r="H1736" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1737" t="s">
+        <v>619</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1737" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1737">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="E1737">
+        <v>46</v>
+      </c>
+      <c r="F1737">
+        <v>276</v>
+      </c>
+      <c r="H1737" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1738" t="s">
+        <v>619</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1738" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1738">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="E1738">
+        <v>38</v>
+      </c>
+      <c r="F1738">
+        <v>228</v>
+      </c>
+      <c r="H1738" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1739" t="s">
+        <v>622</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1739" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1739">
+        <v>1.1240000000000001</v>
+      </c>
+      <c r="E1739">
+        <v>4</v>
+      </c>
+      <c r="F1739">
+        <v>24</v>
+      </c>
+      <c r="H1739" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1740" t="s">
+        <v>623</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1740" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1740">
+        <v>3.024</v>
+      </c>
+      <c r="E1740">
+        <v>37</v>
+      </c>
+      <c r="F1740">
+        <v>222</v>
+      </c>
+      <c r="H1740" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1741" t="s">
+        <v>623</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1741" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1741">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="E1741">
+        <v>35</v>
+      </c>
+      <c r="F1741">
+        <v>210</v>
+      </c>
+      <c r="H1741" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1742" t="s">
+        <v>623</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1742" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1742">
+        <v>2.6880000000000002</v>
+      </c>
+      <c r="E1742">
+        <v>37</v>
+      </c>
+      <c r="F1742">
+        <v>222</v>
+      </c>
+      <c r="H1742" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1743" t="s">
+        <v>633</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1743" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1743" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E1743">
+        <v>21</v>
+      </c>
+      <c r="F1743">
+        <v>126</v>
+      </c>
+      <c r="H1743" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1744" t="s">
+        <v>634</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1744" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1744">
+        <v>2.6970000000000001</v>
+      </c>
+      <c r="E1744">
+        <v>22</v>
+      </c>
+      <c r="F1744">
+        <v>132</v>
+      </c>
+      <c r="H1744" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1745" t="s">
+        <v>629</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1745" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1745">
+        <v>2.6709999999999998</v>
+      </c>
+      <c r="E1745">
+        <v>22</v>
+      </c>
+      <c r="F1745">
+        <v>132</v>
+      </c>
+      <c r="H1745" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1746" t="s">
+        <v>635</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1746" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1746">
+        <v>2.5179999999999998</v>
+      </c>
+      <c r="E1746">
+        <v>24</v>
+      </c>
+      <c r="F1746">
+        <v>144</v>
+      </c>
+      <c r="H1746" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1747" t="s">
+        <v>636</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1747" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1747">
+        <v>2.5070000000000001</v>
+      </c>
+      <c r="E1747">
+        <v>21</v>
+      </c>
+      <c r="F1747">
+        <v>126</v>
+      </c>
+      <c r="H1747" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1748" t="s">
+        <v>636</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>197</v>
+      </c>
+      <c r="C1748" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1748">
+        <v>1.2589999999999999</v>
+      </c>
+      <c r="E1748">
+        <v>9</v>
+      </c>
+      <c r="F1748">
+        <v>54</v>
+      </c>
+      <c r="H1748" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1749" t="s">
+        <v>636</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1749" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1749">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="E1749">
+        <v>21</v>
+      </c>
+      <c r="F1749">
+        <v>126</v>
+      </c>
+      <c r="H1749" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1750" t="s">
+        <v>636</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1750" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1750">
+        <v>2.548</v>
+      </c>
+      <c r="E1750">
+        <v>9</v>
+      </c>
+      <c r="F1750">
+        <v>54</v>
+      </c>
+      <c r="H1750" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1751" t="s">
+        <v>637</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1751" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1751">
+        <v>2.5150000000000001</v>
+      </c>
+      <c r="E1751">
+        <v>5</v>
+      </c>
+      <c r="F1751">
+        <v>30</v>
+      </c>
+      <c r="H1751" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1752" t="s">
+        <v>610</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1752" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1752">
+        <v>2.5489999999999999</v>
+      </c>
+      <c r="E1752">
+        <v>8</v>
+      </c>
+      <c r="F1752">
+        <v>48</v>
+      </c>
+      <c r="H1752" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1753" t="s">
+        <v>638</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1753" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1753">
+        <v>2.5049999999999999</v>
+      </c>
+      <c r="E1753">
+        <v>14</v>
+      </c>
+      <c r="F1753">
+        <v>84</v>
+      </c>
+      <c r="H1753" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1754" t="s">
+        <v>639</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>413</v>
+      </c>
+      <c r="C1754" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1754">
+        <v>2.4460000000000002</v>
+      </c>
+      <c r="E1754">
+        <v>7</v>
+      </c>
+      <c r="F1754">
+        <v>42</v>
+      </c>
+      <c r="H1754" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1755" t="s">
+        <v>587</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1755" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1755">
+        <v>2.1850000000000001</v>
+      </c>
+      <c r="E1755">
+        <v>10</v>
+      </c>
+      <c r="F1755">
+        <v>60</v>
+      </c>
+      <c r="H1755" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1756" t="s">
+        <v>586</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1756" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1756">
+        <v>2.1890000000000001</v>
+      </c>
+      <c r="E1756">
+        <v>12</v>
+      </c>
+      <c r="F1756">
+        <v>72</v>
+      </c>
+      <c r="H1756" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1757" t="s">
+        <v>640</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>187</v>
+      </c>
+      <c r="C1757" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1757">
+        <v>2.1840000000000002</v>
+      </c>
+      <c r="E1757">
+        <v>14</v>
+      </c>
+      <c r="F1757">
+        <v>84</v>
+      </c>
+      <c r="H1757" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1758" t="s">
+        <v>584</v>
+      </c>
+      <c r="B1758" t="s">
+        <v>188</v>
+      </c>
+      <c r="C1758" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1758">
+        <v>4.343</v>
+      </c>
+      <c r="E1758">
+        <v>21</v>
+      </c>
+      <c r="F1758">
+        <v>126</v>
+      </c>
+      <c r="H1758" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1759" t="s">
+        <v>585</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1759" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1759">
+        <v>2.1469999999999998</v>
+      </c>
+      <c r="E1759">
+        <v>12</v>
+      </c>
+      <c r="F1759">
+        <v>72</v>
+      </c>
+      <c r="H1759" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1760" t="s">
+        <v>644</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>190</v>
+      </c>
+      <c r="C1760" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1760">
+        <v>2.335</v>
+      </c>
+      <c r="E1760">
+        <v>7</v>
+      </c>
+      <c r="F1760">
+        <v>42</v>
+      </c>
+      <c r="H1760" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1761" t="s">
+        <v>641</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1761" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1761">
+        <v>2.2909999999999999</v>
+      </c>
+      <c r="E1761">
+        <v>12</v>
+      </c>
+      <c r="F1761">
+        <v>72</v>
+      </c>
+      <c r="H1761" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1762" t="s">
+        <v>611</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1762" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1762">
+        <v>2.444</v>
+      </c>
+      <c r="E1762">
+        <v>13</v>
+      </c>
+      <c r="F1762">
+        <v>78</v>
+      </c>
+      <c r="H1762" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1763" t="s">
+        <v>642</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>193</v>
+      </c>
+      <c r="C1763" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1763">
+        <v>2.9380000000000002</v>
+      </c>
+      <c r="E1763">
+        <v>8</v>
+      </c>
+      <c r="F1763">
+        <v>48</v>
+      </c>
+      <c r="H1763" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1764" t="s">
+        <v>643</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1764" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1764">
+        <v>2.15</v>
+      </c>
+      <c r="E1764">
+        <v>7</v>
+      </c>
+      <c r="F1764">
+        <v>42</v>
+      </c>
+      <c r="H1764" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1765" t="s">
+        <v>645</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>182</v>
+      </c>
+      <c r="C1765" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1765">
+        <v>2.1659999999999999</v>
+      </c>
+      <c r="E1765">
+        <v>10</v>
+      </c>
+      <c r="F1765">
+        <v>60</v>
+      </c>
+      <c r="H1765" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1766" t="s">
+        <v>616</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1766" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1766">
+        <v>2.4159999999999999</v>
+      </c>
+      <c r="E1766">
+        <v>19</v>
+      </c>
+      <c r="F1766">
+        <v>114</v>
+      </c>
+      <c r="H1766" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1767" t="s">
+        <v>621</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>184</v>
+      </c>
+      <c r="C1767" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1767">
+        <v>2.863</v>
+      </c>
+      <c r="E1767">
+        <v>19</v>
+      </c>
+      <c r="F1767">
+        <v>114</v>
+      </c>
+      <c r="H1767" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1768" t="s">
+        <v>646</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>509</v>
+      </c>
+      <c r="C1768" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1768">
+        <v>1.27</v>
+      </c>
+      <c r="E1768">
+        <v>2</v>
+      </c>
+      <c r="F1768">
+        <v>12</v>
+      </c>
+      <c r="H1768" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1769" t="s">
+        <v>624</v>
+      </c>
+      <c r="B1769" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1769" t="s">
+        <v>439</v>
+      </c>
+      <c r="D1769">
+        <v>1.548</v>
+      </c>
+      <c r="E1769">
+        <v>6</v>
+      </c>
+      <c r="F1769">
+        <v>36</v>
+      </c>
+      <c r="H1769" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1770" t="s">
+        <v>625</v>
+      </c>
+      <c r="B1770" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1770" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1770">
+        <v>2.008</v>
+      </c>
+      <c r="E1770">
+        <v>4</v>
+      </c>
+      <c r="F1770">
+        <v>24</v>
+      </c>
+      <c r="H1770" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1771" t="s">
+        <v>626</v>
+      </c>
+      <c r="B1771" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1771" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1771">
+        <v>2.028</v>
+      </c>
+      <c r="E1771">
+        <v>10</v>
+      </c>
+      <c r="F1771">
+        <v>60</v>
+      </c>
+      <c r="H1771" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1772" t="s">
+        <v>627</v>
+      </c>
+      <c r="B1772" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1772" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1772">
+        <v>1.6639999999999999</v>
+      </c>
+      <c r="E1772">
+        <v>4</v>
+      </c>
+      <c r="F1772">
+        <v>24</v>
+      </c>
+      <c r="H1772" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1773" t="s">
+        <v>590</v>
+      </c>
+      <c r="B1773" t="s">
+        <v>415</v>
+      </c>
+      <c r="C1773" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1773" s="3">
+        <v>1.89</v>
+      </c>
+      <c r="E1773">
+        <v>3</v>
+      </c>
+      <c r="F1773">
+        <v>18</v>
+      </c>
+      <c r="H1773" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1774" t="s">
+        <v>628</v>
+      </c>
+      <c r="B1774" t="s">
+        <v>414</v>
+      </c>
+      <c r="C1774" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1774" s="3">
+        <v>2.9</v>
+      </c>
+      <c r="E1774">
+        <v>5</v>
+      </c>
+      <c r="F1774">
+        <v>30</v>
+      </c>
+      <c r="H1774" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1775" t="s">
+        <v>629</v>
+      </c>
+      <c r="B1775" t="s">
+        <v>507</v>
+      </c>
+      <c r="C1775" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1775" s="3">
+        <v>1.248</v>
+      </c>
+      <c r="E1775">
+        <v>2</v>
+      </c>
+      <c r="F1775">
+        <v>12</v>
+      </c>
+      <c r="H1775" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1776" t="s">
+        <v>604</v>
+      </c>
+      <c r="B1776" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1776" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1776">
+        <v>1.569</v>
+      </c>
+      <c r="E1776">
+        <v>7</v>
+      </c>
+      <c r="F1776">
+        <v>42</v>
+      </c>
+      <c r="H1776" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1777" t="s">
+        <v>630</v>
+      </c>
+      <c r="B1777" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1777" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1777">
+        <v>0.96</v>
+      </c>
+      <c r="E1777">
+        <v>4</v>
+      </c>
+      <c r="F1777">
+        <v>24</v>
+      </c>
+      <c r="H1777" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1778" t="s">
+        <v>631</v>
+      </c>
+      <c r="B1778" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1778" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1778">
+        <v>1.7889999999999999</v>
+      </c>
+      <c r="E1778">
+        <v>5</v>
+      </c>
+      <c r="F1778">
+        <v>30</v>
+      </c>
+      <c r="H1778" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1779" t="s">
+        <v>632</v>
+      </c>
+      <c r="B1779" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1779" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1779">
+        <v>0.95399999999999996</v>
+      </c>
+      <c r="E1779">
+        <v>2</v>
+      </c>
+      <c r="F1779">
+        <v>12</v>
+      </c>
+      <c r="H1779" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1780" t="s">
+        <v>593</v>
+      </c>
+      <c r="B1780" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1780" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1780">
+        <v>1.0029999999999999</v>
+      </c>
+      <c r="E1780">
+        <v>10</v>
+      </c>
+      <c r="F1780">
+        <v>60</v>
+      </c>
+      <c r="H1780" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1781" t="s">
+        <v>594</v>
+      </c>
+      <c r="B1781" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1781" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1781">
+        <v>1.0389999999999999</v>
+      </c>
+      <c r="E1781">
+        <v>13</v>
+      </c>
+      <c r="F1781">
+        <v>78</v>
+      </c>
+      <c r="H1781" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1782" t="s">
+        <v>595</v>
+      </c>
+      <c r="B1782" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1782" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1782">
+        <v>1.883</v>
+      </c>
+      <c r="E1782">
+        <v>7</v>
+      </c>
+      <c r="F1782">
+        <v>42</v>
+      </c>
+      <c r="H1782" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1783" t="s">
+        <v>596</v>
+      </c>
+      <c r="B1783" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1783" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1783">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="E1783">
+        <v>10</v>
+      </c>
+      <c r="F1783">
+        <v>60</v>
+      </c>
+      <c r="H1783" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1784" t="s">
+        <v>597</v>
+      </c>
+      <c r="B1784" t="s">
+        <v>180</v>
+      </c>
+      <c r="C1784" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1784">
+        <v>2.0350000000000001</v>
+      </c>
+      <c r="E1784">
+        <v>13</v>
+      </c>
+      <c r="F1784">
+        <v>78</v>
+      </c>
+      <c r="H1784" t="s">
         <v>583</v>
       </c>
     </row>

--- a/data/harvesting_records.xlsx
+++ b/data/harvesting_records.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7320"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7317" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7389" uniqueCount="709">
   <si>
     <t>Date</t>
   </si>
@@ -2132,13 +2132,28 @@
   <si>
     <t>2026-07-23</t>
   </si>
+  <si>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-08-02</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -2194,7 +2209,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2497,7 +2512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S1936"/>
+  <dimension ref="A1:S1954"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -75633,6 +75648,1068 @@
         <v>78</v>
       </c>
     </row>
+    <row r="1937" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1937" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1937" t="s">
+        <v>561</v>
+      </c>
+      <c r="C1937" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1937">
+        <v>1.03</v>
+      </c>
+      <c r="E1937">
+        <v>16</v>
+      </c>
+      <c r="F1937">
+        <v>96</v>
+      </c>
+      <c r="G1937">
+        <v>114</v>
+      </c>
+      <c r="H1937" t="s">
+        <v>648</v>
+      </c>
+      <c r="I1937">
+        <v>0</v>
+      </c>
+      <c r="J1937">
+        <v>1</v>
+      </c>
+      <c r="K1937">
+        <v>3</v>
+      </c>
+      <c r="L1937">
+        <v>0</v>
+      </c>
+      <c r="M1937">
+        <v>0</v>
+      </c>
+      <c r="N1937">
+        <v>0</v>
+      </c>
+      <c r="O1937">
+        <v>0</v>
+      </c>
+      <c r="P1937">
+        <v>32</v>
+      </c>
+      <c r="Q1937">
+        <v>0</v>
+      </c>
+      <c r="R1937">
+        <v>0</v>
+      </c>
+      <c r="S1937">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1938" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1938" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1938" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1938">
+        <v>1.75</v>
+      </c>
+      <c r="E1938">
+        <v>22</v>
+      </c>
+      <c r="F1938">
+        <v>132</v>
+      </c>
+      <c r="G1938">
+        <v>59</v>
+      </c>
+      <c r="H1938" t="s">
+        <v>648</v>
+      </c>
+      <c r="I1938">
+        <v>0</v>
+      </c>
+      <c r="J1938">
+        <v>1</v>
+      </c>
+      <c r="K1938">
+        <v>2</v>
+      </c>
+      <c r="L1938">
+        <v>3</v>
+      </c>
+      <c r="M1938">
+        <v>2</v>
+      </c>
+      <c r="N1938">
+        <v>1</v>
+      </c>
+      <c r="O1938">
+        <v>1</v>
+      </c>
+      <c r="P1938">
+        <v>44</v>
+      </c>
+      <c r="Q1938">
+        <v>1</v>
+      </c>
+      <c r="R1938">
+        <v>0</v>
+      </c>
+      <c r="S1938">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1939" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1939" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1939" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1939">
+        <v>3.01</v>
+      </c>
+      <c r="E1939">
+        <v>38</v>
+      </c>
+      <c r="F1939">
+        <v>228</v>
+      </c>
+      <c r="G1939">
+        <v>98</v>
+      </c>
+      <c r="H1939" t="s">
+        <v>648</v>
+      </c>
+      <c r="I1939">
+        <v>0</v>
+      </c>
+      <c r="J1939">
+        <v>1</v>
+      </c>
+      <c r="K1939">
+        <v>4</v>
+      </c>
+      <c r="L1939">
+        <v>4</v>
+      </c>
+      <c r="M1939">
+        <v>4</v>
+      </c>
+      <c r="N1939">
+        <v>2</v>
+      </c>
+      <c r="O1939">
+        <v>1</v>
+      </c>
+      <c r="P1939">
+        <v>76</v>
+      </c>
+      <c r="Q1939">
+        <v>1</v>
+      </c>
+      <c r="R1939">
+        <v>1</v>
+      </c>
+      <c r="S1939">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1940" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1940" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1940" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1940">
+        <v>3.1</v>
+      </c>
+      <c r="E1940">
+        <v>32</v>
+      </c>
+      <c r="F1940">
+        <v>192</v>
+      </c>
+      <c r="G1940">
+        <v>87</v>
+      </c>
+      <c r="H1940" t="s">
+        <v>648</v>
+      </c>
+      <c r="I1940">
+        <v>0</v>
+      </c>
+      <c r="J1940">
+        <v>2</v>
+      </c>
+      <c r="K1940">
+        <v>3</v>
+      </c>
+      <c r="L1940">
+        <v>3</v>
+      </c>
+      <c r="M1940">
+        <v>3</v>
+      </c>
+      <c r="N1940">
+        <v>2</v>
+      </c>
+      <c r="O1940">
+        <v>1</v>
+      </c>
+      <c r="P1940">
+        <v>64</v>
+      </c>
+      <c r="Q1940">
+        <v>1</v>
+      </c>
+      <c r="R1940">
+        <v>1</v>
+      </c>
+      <c r="S1940">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1941" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1941" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1941" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1941">
+        <v>3.11</v>
+      </c>
+      <c r="E1941">
+        <v>30</v>
+      </c>
+      <c r="F1941">
+        <v>180</v>
+      </c>
+      <c r="G1941">
+        <v>90</v>
+      </c>
+      <c r="H1941" t="s">
+        <v>648</v>
+      </c>
+      <c r="I1941">
+        <v>0</v>
+      </c>
+      <c r="J1941">
+        <v>2</v>
+      </c>
+      <c r="K1941">
+        <v>3</v>
+      </c>
+      <c r="L1941">
+        <v>3</v>
+      </c>
+      <c r="M1941">
+        <v>2</v>
+      </c>
+      <c r="N1941">
+        <v>1</v>
+      </c>
+      <c r="O1941">
+        <v>2</v>
+      </c>
+      <c r="P1941">
+        <v>66</v>
+      </c>
+      <c r="Q1941">
+        <v>1</v>
+      </c>
+      <c r="R1941">
+        <v>1</v>
+      </c>
+      <c r="S1941">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1942" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1942" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1942" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1942">
+        <v>3.09</v>
+      </c>
+      <c r="E1942">
+        <v>33</v>
+      </c>
+      <c r="F1942">
+        <v>198</v>
+      </c>
+      <c r="G1942">
+        <v>90</v>
+      </c>
+      <c r="H1942" t="s">
+        <v>648</v>
+      </c>
+      <c r="I1942">
+        <v>0</v>
+      </c>
+      <c r="J1942">
+        <v>1</v>
+      </c>
+      <c r="K1942">
+        <v>3</v>
+      </c>
+      <c r="L1942">
+        <v>3</v>
+      </c>
+      <c r="M1942">
+        <v>3</v>
+      </c>
+      <c r="N1942">
+        <v>1</v>
+      </c>
+      <c r="O1942">
+        <v>2</v>
+      </c>
+      <c r="P1942">
+        <v>66</v>
+      </c>
+      <c r="Q1942">
+        <v>1</v>
+      </c>
+      <c r="R1942">
+        <v>1</v>
+      </c>
+      <c r="S1942">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1943" t="s">
+        <v>707</v>
+      </c>
+      <c r="B1943" t="s">
+        <v>424</v>
+      </c>
+      <c r="C1943" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1943">
+        <v>1.25</v>
+      </c>
+      <c r="E1943">
+        <v>17</v>
+      </c>
+      <c r="F1943">
+        <v>96</v>
+      </c>
+      <c r="G1943">
+        <v>114</v>
+      </c>
+      <c r="H1943" t="s">
+        <v>648</v>
+      </c>
+      <c r="I1943">
+        <v>0</v>
+      </c>
+      <c r="J1943">
+        <v>1</v>
+      </c>
+      <c r="K1943">
+        <v>3</v>
+      </c>
+      <c r="L1943">
+        <v>0</v>
+      </c>
+      <c r="M1943">
+        <v>0</v>
+      </c>
+      <c r="N1943">
+        <v>0</v>
+      </c>
+      <c r="O1943">
+        <v>0</v>
+      </c>
+      <c r="P1943">
+        <v>32</v>
+      </c>
+      <c r="Q1943">
+        <v>0</v>
+      </c>
+      <c r="R1943">
+        <v>0</v>
+      </c>
+      <c r="S1943">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1944" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1944" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1944" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1944">
+        <v>2.15</v>
+      </c>
+      <c r="E1944">
+        <v>16</v>
+      </c>
+      <c r="F1944">
+        <v>96</v>
+      </c>
+      <c r="G1944">
+        <v>114</v>
+      </c>
+      <c r="H1944" t="s">
+        <v>648</v>
+      </c>
+      <c r="I1944">
+        <v>0</v>
+      </c>
+      <c r="J1944">
+        <v>1</v>
+      </c>
+      <c r="K1944">
+        <v>3</v>
+      </c>
+      <c r="L1944">
+        <v>0</v>
+      </c>
+      <c r="M1944">
+        <v>0</v>
+      </c>
+      <c r="N1944">
+        <v>0</v>
+      </c>
+      <c r="O1944">
+        <v>0</v>
+      </c>
+      <c r="P1944">
+        <v>32</v>
+      </c>
+      <c r="Q1944">
+        <v>0</v>
+      </c>
+      <c r="R1944">
+        <v>0</v>
+      </c>
+      <c r="S1944">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1945" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1945" t="s">
+        <v>252</v>
+      </c>
+      <c r="C1945" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1945">
+        <v>0.45</v>
+      </c>
+      <c r="E1945">
+        <v>9</v>
+      </c>
+      <c r="F1945">
+        <v>54</v>
+      </c>
+      <c r="G1945">
+        <v>0</v>
+      </c>
+      <c r="H1945" t="s">
+        <v>648</v>
+      </c>
+      <c r="I1945">
+        <v>0</v>
+      </c>
+      <c r="J1945">
+        <v>0</v>
+      </c>
+      <c r="K1945">
+        <v>0</v>
+      </c>
+      <c r="L1945">
+        <v>0</v>
+      </c>
+      <c r="M1945">
+        <v>0</v>
+      </c>
+      <c r="N1945">
+        <v>0</v>
+      </c>
+      <c r="O1945">
+        <v>0</v>
+      </c>
+      <c r="P1945">
+        <v>0</v>
+      </c>
+      <c r="Q1945">
+        <v>0</v>
+      </c>
+      <c r="R1945">
+        <v>0</v>
+      </c>
+      <c r="S1945">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1946" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1946" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1946" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1946">
+        <v>3.03</v>
+      </c>
+      <c r="E1946">
+        <v>36</v>
+      </c>
+      <c r="F1946">
+        <v>216</v>
+      </c>
+      <c r="G1946">
+        <v>91</v>
+      </c>
+      <c r="H1946" t="s">
+        <v>648</v>
+      </c>
+      <c r="I1946">
+        <v>0</v>
+      </c>
+      <c r="J1946">
+        <v>2</v>
+      </c>
+      <c r="K1946">
+        <v>3</v>
+      </c>
+      <c r="L1946">
+        <v>3</v>
+      </c>
+      <c r="M1946">
+        <v>3</v>
+      </c>
+      <c r="N1946">
+        <v>2</v>
+      </c>
+      <c r="O1946">
+        <v>1</v>
+      </c>
+      <c r="P1946">
+        <v>70</v>
+      </c>
+      <c r="Q1946">
+        <v>1</v>
+      </c>
+      <c r="R1946">
+        <v>1</v>
+      </c>
+      <c r="S1946">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1947" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1947" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1947" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1947">
+        <v>3</v>
+      </c>
+      <c r="E1947">
+        <v>33</v>
+      </c>
+      <c r="F1947">
+        <v>198</v>
+      </c>
+      <c r="G1947">
+        <v>85</v>
+      </c>
+      <c r="H1947" t="s">
+        <v>648</v>
+      </c>
+      <c r="I1947">
+        <v>0</v>
+      </c>
+      <c r="J1947">
+        <v>1</v>
+      </c>
+      <c r="K1947">
+        <v>3</v>
+      </c>
+      <c r="L1947">
+        <v>3</v>
+      </c>
+      <c r="M1947">
+        <v>3</v>
+      </c>
+      <c r="N1947">
+        <v>1</v>
+      </c>
+      <c r="O1947">
+        <v>1</v>
+      </c>
+      <c r="P1947">
+        <v>66</v>
+      </c>
+      <c r="Q1947">
+        <v>1</v>
+      </c>
+      <c r="R1947">
+        <v>1</v>
+      </c>
+      <c r="S1947">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1948" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1948" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1948" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1948">
+        <v>3.04</v>
+      </c>
+      <c r="E1948">
+        <v>36</v>
+      </c>
+      <c r="F1948">
+        <v>216</v>
+      </c>
+      <c r="G1948">
+        <v>94</v>
+      </c>
+      <c r="H1948" t="s">
+        <v>648</v>
+      </c>
+      <c r="I1948">
+        <v>0</v>
+      </c>
+      <c r="J1948">
+        <v>2</v>
+      </c>
+      <c r="K1948">
+        <v>3</v>
+      </c>
+      <c r="L1948">
+        <v>3</v>
+      </c>
+      <c r="M1948">
+        <v>3</v>
+      </c>
+      <c r="N1948">
+        <v>2</v>
+      </c>
+      <c r="O1948">
+        <v>1</v>
+      </c>
+      <c r="P1948">
+        <v>72</v>
+      </c>
+      <c r="Q1948">
+        <v>1</v>
+      </c>
+      <c r="R1948">
+        <v>0</v>
+      </c>
+      <c r="S1948">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1949" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1949" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1949" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1949">
+        <v>3.04</v>
+      </c>
+      <c r="E1949">
+        <v>33</v>
+      </c>
+      <c r="F1949">
+        <v>198</v>
+      </c>
+      <c r="G1949">
+        <v>85</v>
+      </c>
+      <c r="H1949" t="s">
+        <v>648</v>
+      </c>
+      <c r="I1949">
+        <v>0</v>
+      </c>
+      <c r="J1949">
+        <v>1</v>
+      </c>
+      <c r="K1949">
+        <v>3</v>
+      </c>
+      <c r="L1949">
+        <v>3</v>
+      </c>
+      <c r="M1949">
+        <v>3</v>
+      </c>
+      <c r="N1949">
+        <v>1</v>
+      </c>
+      <c r="O1949">
+        <v>1</v>
+      </c>
+      <c r="P1949">
+        <v>66</v>
+      </c>
+      <c r="Q1949">
+        <v>1</v>
+      </c>
+      <c r="R1949">
+        <v>1</v>
+      </c>
+      <c r="S1949">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1950" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1950" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1950" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1950">
+        <v>3.04</v>
+      </c>
+      <c r="E1950">
+        <v>34</v>
+      </c>
+      <c r="F1950">
+        <v>204</v>
+      </c>
+      <c r="G1950">
+        <v>88</v>
+      </c>
+      <c r="H1950" t="s">
+        <v>648</v>
+      </c>
+      <c r="I1950">
+        <v>0</v>
+      </c>
+      <c r="J1950">
+        <v>1</v>
+      </c>
+      <c r="K1950">
+        <v>3</v>
+      </c>
+      <c r="L1950">
+        <v>3</v>
+      </c>
+      <c r="M1950">
+        <v>3</v>
+      </c>
+      <c r="N1950">
+        <v>1</v>
+      </c>
+      <c r="O1950">
+        <v>1</v>
+      </c>
+      <c r="P1950">
+        <v>68</v>
+      </c>
+      <c r="Q1950">
+        <v>1</v>
+      </c>
+      <c r="R1950">
+        <v>1</v>
+      </c>
+      <c r="S1950">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1951" t="s">
+        <v>705</v>
+      </c>
+      <c r="B1951" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1951" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1951">
+        <v>0.04</v>
+      </c>
+      <c r="E1951">
+        <v>5</v>
+      </c>
+      <c r="F1951">
+        <v>30</v>
+      </c>
+      <c r="G1951">
+        <v>15</v>
+      </c>
+      <c r="H1951" t="s">
+        <v>648</v>
+      </c>
+      <c r="I1951">
+        <v>0</v>
+      </c>
+      <c r="J1951">
+        <v>0</v>
+      </c>
+      <c r="K1951">
+        <v>1</v>
+      </c>
+      <c r="L1951">
+        <v>1</v>
+      </c>
+      <c r="M1951">
+        <v>1</v>
+      </c>
+      <c r="N1951">
+        <v>1</v>
+      </c>
+      <c r="O1951">
+        <v>1</v>
+      </c>
+      <c r="P1951">
+        <v>10</v>
+      </c>
+      <c r="Q1951">
+        <v>0</v>
+      </c>
+      <c r="R1951">
+        <v>0</v>
+      </c>
+      <c r="S1951">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1952" t="s">
+        <v>706</v>
+      </c>
+      <c r="B1952" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1952" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1952">
+        <v>3</v>
+      </c>
+      <c r="E1952">
+        <v>30</v>
+      </c>
+      <c r="F1952">
+        <v>180</v>
+      </c>
+      <c r="G1952">
+        <v>79</v>
+      </c>
+      <c r="H1952" t="s">
+        <v>648</v>
+      </c>
+      <c r="I1952">
+        <v>0</v>
+      </c>
+      <c r="J1952">
+        <v>1</v>
+      </c>
+      <c r="K1952">
+        <v>2</v>
+      </c>
+      <c r="L1952">
+        <v>3</v>
+      </c>
+      <c r="M1952">
+        <v>2</v>
+      </c>
+      <c r="N1952">
+        <v>1</v>
+      </c>
+      <c r="O1952">
+        <v>1</v>
+      </c>
+      <c r="P1952">
+        <v>60</v>
+      </c>
+      <c r="Q1952">
+        <v>1</v>
+      </c>
+      <c r="R1952">
+        <v>0</v>
+      </c>
+      <c r="S1952">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1953" t="s">
+        <v>706</v>
+      </c>
+      <c r="B1953" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1953" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1953">
+        <v>3.04</v>
+      </c>
+      <c r="E1953">
+        <v>36</v>
+      </c>
+      <c r="F1953">
+        <v>216</v>
+      </c>
+      <c r="G1953">
+        <v>97</v>
+      </c>
+      <c r="H1953" t="s">
+        <v>648</v>
+      </c>
+      <c r="I1953">
+        <v>0</v>
+      </c>
+      <c r="J1953">
+        <v>2</v>
+      </c>
+      <c r="K1953">
+        <v>3</v>
+      </c>
+      <c r="L1953">
+        <v>3</v>
+      </c>
+      <c r="M1953">
+        <v>3</v>
+      </c>
+      <c r="N1953">
+        <v>2</v>
+      </c>
+      <c r="O1953">
+        <v>1</v>
+      </c>
+      <c r="P1953">
+        <v>72</v>
+      </c>
+      <c r="Q1953">
+        <v>1</v>
+      </c>
+      <c r="R1953">
+        <v>1</v>
+      </c>
+      <c r="S1953">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1954" t="s">
+        <v>706</v>
+      </c>
+      <c r="B1954" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1954" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1954">
+        <v>1.67</v>
+      </c>
+      <c r="E1954">
+        <v>22</v>
+      </c>
+      <c r="F1954">
+        <v>132</v>
+      </c>
+      <c r="G1954">
+        <v>59</v>
+      </c>
+      <c r="H1954" t="s">
+        <v>648</v>
+      </c>
+      <c r="I1954">
+        <v>0</v>
+      </c>
+      <c r="J1954">
+        <v>1</v>
+      </c>
+      <c r="K1954">
+        <v>2</v>
+      </c>
+      <c r="L1954">
+        <v>2</v>
+      </c>
+      <c r="M1954">
+        <v>2</v>
+      </c>
+      <c r="N1954">
+        <v>1</v>
+      </c>
+      <c r="O1954">
+        <v>1</v>
+      </c>
+      <c r="P1954">
+        <v>44</v>
+      </c>
+      <c r="Q1954">
+        <v>1</v>
+      </c>
+      <c r="R1954">
+        <v>1</v>
+      </c>
+      <c r="S1954">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
